--- a/results/job_matches_2026-04-15.xlsx
+++ b/results/job_matches_2026-04-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,87 +643,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Senior Data Engineer 2026 - US,UK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SentiLink</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, SQS, SNS, RDS, Azure, GCP</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1963992b9015fbc</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d01fdc4061dd2a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer 2026 - US,UK</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d01fdc4061dd2a</t>
+          <t>https://www.indeed.com/viewjob?jk=5f9a309f4efa98f8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Information Technology - BI Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>TCC Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Fishers, IN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Spark, Scala, Oracle, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f9a309f4efa98f8</t>
+          <t>https://www.indeed.com/viewjob?jk=ca19ad92abde46c9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Full Stack AI Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>bioMerieux</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hazelwood, MO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Oracle, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=574e10b9b787dc54</t>
+          <t>https://www.indeed.com/viewjob?jk=c2788300e5964c54</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac615cac5200efc9</t>
+          <t>https://www.indeed.com/viewjob?jk=574e10b9b787dc54</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a7de03320b3d487</t>
+          <t>https://www.indeed.com/viewjob?jk=ac615cac5200efc9</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df1418000450ecdb</t>
+          <t>https://www.indeed.com/viewjob?jk=8a7de03320b3d487</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6df75aab0012c038</t>
+          <t>https://www.indeed.com/viewjob?jk=df1418000450ecdb</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Java Developer (Hybrid- Flexible Options)</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Edgewood, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25ccf7fa8d4a5b10</t>
+          <t>https://www.indeed.com/viewjob?jk=6df75aab0012c038</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Java Developer (Hybrid- Flexible Options)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>bioMerieux</t>
+          <t>Broadridge</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hazelwood, MO, US USA</t>
+          <t>Edgewood, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Oracle, PostgreSQL, CI/CD</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2788300e5964c54</t>
+          <t>https://www.indeed.com/viewjob?jk=25ccf7fa8d4a5b10</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Southern Company</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a513718316ea30dd</t>
+          <t>https://www.indeed.com/viewjob?jk=3be194d530456f66</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Operations Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Stifel</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43cfe33e6a3659da</t>
+          <t>https://www.indeed.com/viewjob?jk=d061193f264addea</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, BigQuery, Scala, Snowflake</t>
+          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620e166ed5473039</t>
+          <t>https://www.indeed.com/viewjob?jk=e99b4467c3c6aa55</t>
         </is>
       </c>
     </row>
@@ -1133,25 +1133,25 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>Express</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, ECS, RDS, GCP, BigQuery, Scala, Oracle, MongoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ead7a3e6b1951593</t>
+          <t>https://www.indeed.com/viewjob?jk=27ee634b56d5a4e3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database and Dashboard Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f193a5a41b80d59d</t>
+          <t>https://www.indeed.com/viewjob?jk=fee5a2d73882379c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae18e6a8860be459</t>
+          <t>https://www.indeed.com/viewjob?jk=ead7a3e6b1951593</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data &amp; AI Governance Officer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vantage Bank Texas</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Data Factory, Databricks, ELT, Power BI, Tableau</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c469b183725fde1</t>
+          <t>https://www.indeed.com/viewjob?jk=ae18e6a8860be459</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer 3 - Contingent (contract)</t>
+          <t>Snowflake Data Engineer (contract)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,207 +1301,207 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7051fd3bf67a37ac</t>
+          <t>https://www.indeed.com/viewjob?jk=23956751504b8384</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solution Architect, Enterprise</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Robstown, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=072e6e4e8e025141</t>
+          <t>https://www.indeed.com/viewjob?jk=3f33106731db1775</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mid-Level Data Engineer, Global</t>
+          <t>Solution Architect, Enterprise</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c717630a440c614c</t>
+          <t>https://www.indeed.com/viewjob?jk=90d356ab99a57489</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Solution Architect, Enterprise</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15a32bf71ba33ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=15664632526fabdb</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Senior Solution Architect, Enterprise</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d3db28285f41c46</t>
+          <t>https://www.indeed.com/viewjob?jk=507830f63a6d47c9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Senior Solution Architect, Enterprise</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3989068a8778fb79</t>
+          <t>https://www.indeed.com/viewjob?jk=98d7971656e73b43</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Data &amp; AI Governance Officer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Vantage Bank Texas</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, Glue, S3, RDS, Azure, Data Factory, Databricks, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c70a1cb7dff6fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=5c469b183725fde1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Robstown, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de9b476cdbf12e9</t>
+          <t>https://www.indeed.com/viewjob?jk=072e6e4e8e025141</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Research Engineer II</t>
+          <t>Mid-Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bryan, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb85a1b8d1928fd4</t>
+          <t>https://www.indeed.com/viewjob?jk=c717630a440c614c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ArcGIS Software Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1186a0273eb12d27</t>
+          <t>https://www.indeed.com/viewjob?jk=15a32bf71ba33ffa</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f177704478aadbe</t>
+          <t>https://www.indeed.com/viewjob?jk=4d3db28285f41c46</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Frida</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Star Schema</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8900daeea8c64c35</t>
+          <t>https://www.indeed.com/viewjob?jk=3989068a8778fb79</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Sr. ETL/Python Developer)</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RCR Technology</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4527effc81797bda</t>
+          <t>https://www.indeed.com/viewjob?jk=5c70a1cb7dff6fb6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Support Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Illumen Group</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Stafford, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, Databricks, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92cd661cf5a17182</t>
+          <t>https://www.indeed.com/viewjob?jk=3de9b476cdbf12e9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Engineer II – Big Data / ETL Engineer (Apptio)</t>
+          <t>Research Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bryan, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be9de9e1e7dbc172</t>
+          <t>https://www.indeed.com/viewjob?jk=bb85a1b8d1928fd4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer Oncology Analytics</t>
+          <t>ArcGIS Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, API Gateway, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a8530ac9c848be</t>
+          <t>https://www.indeed.com/viewjob?jk=1186a0273eb12d27</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AllCloud</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a0467416d94bb26</t>
+          <t>https://www.indeed.com/viewjob?jk=9f177704478aadbe</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Development Engineer II (C#/.NET, Azure)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Frida</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6c902472d880e18</t>
+          <t>https://www.indeed.com/viewjob?jk=8900daeea8c64c35</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr Mgr Data Engineering</t>
+          <t>Senior Data Engineer (Sr. ETL/Python Developer)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>RCR Technology</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e707506ab6122a</t>
+          <t>https://www.indeed.com/viewjob?jk=4527effc81797bda</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Data Support Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Illumen Group</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Stafford, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Redshift, Athena, S3, Databricks, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a527d30b5c00d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=92cd661cf5a17182</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer II – Big Data / ETL Engineer (Apptio)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Banner Health</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
+          <t>Databricks, BigQuery, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1bf292f1b43ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=be9de9e1e7dbc172</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cloud Automation Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Vantage Bank Texas</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f9ce6ba5f081b9</t>
+          <t>https://www.indeed.com/viewjob?jk=8a0467416d94bb26</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Software Development Engineer II (C#/.NET, Azure)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62c75d5f8fbde70d</t>
+          <t>https://www.indeed.com/viewjob?jk=b6c902472d880e18</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Sr Mgr Data Engineering</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Medeloop</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a81ed0b08e8f07f7</t>
+          <t>https://www.indeed.com/viewjob?jk=03e707506ab6122a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Intermediate Machine Learning Data Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Spark, Dask, Snowflake, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ccec05543d43588</t>
+          <t>https://www.indeed.com/viewjob?jk=1a527d30b5c00d7d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Banner Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6177a38e86fbab44</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1bf292f1b43ebd</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Cloud Automation Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Vantage Bank Texas</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf17dcf23ea3201f</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f9ce6ba5f081b9</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2722db66dd139366</t>
+          <t>https://www.indeed.com/viewjob?jk=62c75d5f8fbde70d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RJW Logistics</t>
+          <t>Medeloop</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef58fd9ad5dd15ff</t>
+          <t>https://www.indeed.com/viewjob?jk=a81ed0b08e8f07f7</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>adonis</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5621c4e542d4639</t>
+          <t>https://www.indeed.com/viewjob?jk=30ff91e3d3905a73</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38299c9de7d6d6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=17cbee15ac5e5d6a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>NetApp Emerging Talent - Entry Level Software Engineer (Cloud Storage)</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>RJW Logistics</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e07865da969c4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=ef58fd9ad5dd15ff</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Hybrid</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Snowflake, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=745ab30cde1846a7</t>
+          <t>https://www.indeed.com/viewjob?jk=bf17dcf23ea3201f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a27a8acf3bc1bc8</t>
+          <t>https://www.indeed.com/viewjob?jk=766ed066e436eb0c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffb45764baeec647</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c080bdfd0f5497</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02ca8eea8c20d4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=01aefad23a0eebfc</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Consumer Cellular</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93a9ff833b41ef5d</t>
+          <t>https://www.indeed.com/viewjob?jk=b79af965edb52688</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Full-Stack Developer (AWS, TS, React)</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc3a148287061e68</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe099d836f48656</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Rocket Close</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fce91f5c39bd4ed</t>
+          <t>https://www.indeed.com/viewjob?jk=8756dcda438f6959</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>NetApp Emerging Talent - Software Engineer (Cloud Storage)</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b72bdc255bbf6f8</t>
+          <t>https://www.indeed.com/viewjob?jk=3c70b98cc7f980bc</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Databricks Lakehouse, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6e81f16ad428334</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa8671f82044c5a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026009 - Software Engineer</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>John Deere</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Moline, IL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Scala, PostgreSQL, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e1a444de87fc2c</t>
+          <t>https://www.indeed.com/viewjob?jk=9bddaca0e62ee366</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RNGD</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a3ecae4bdb7e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=4177c81ac5d66b2d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MachineMetrics, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, RDS, Scala, Kafka, PostgreSQL, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80173e5fca484063</t>
+          <t>https://www.indeed.com/viewjob?jk=02c32fad4b2ac01d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Microsoft Modern Work Consultant</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11d034c0b8905492</t>
+          <t>https://www.indeed.com/viewjob?jk=964bc462945e695c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer (Information Technology Subject Matter Expert)</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>State of Connecticut</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d267e859d5950f5a</t>
+          <t>https://www.indeed.com/viewjob?jk=7beb81f1fe47bc19</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Developer - Information Governance</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,67 +2911,67 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65cd9651c7e25101</t>
+          <t>https://www.indeed.com/viewjob?jk=a3c6d71a96ee8e3e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Tester (Python) - 6254091</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Spark, PySpark, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89141221ea154795</t>
+          <t>https://www.indeed.com/viewjob?jk=85e48e8aee6232ce</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085872f73883326c</t>
+          <t>https://www.indeed.com/viewjob?jk=26cc56905b519e4a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa79af047e73dc3e</t>
+          <t>https://www.indeed.com/viewjob?jk=416163a4caa0a101</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,67 +3051,67 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34987f860a590c53</t>
+          <t>https://www.indeed.com/viewjob?jk=6b314b34d858c384</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4296ca379ce33eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=3d26c232b74cd8f7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Angular / JAVA Full Stack Engineer</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcfd60088aef43d3</t>
+          <t>https://www.indeed.com/viewjob?jk=0461589d526a9a5c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer: $150-160,000, MN Based, Hybrid - 2 Days in Office</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GovDocs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, MongoDB, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8acefc49a07f2d39</t>
+          <t>https://www.indeed.com/viewjob?jk=a01db0a34a1698ca</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AI Enablement)</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48c5c7e7de56c6fb</t>
+          <t>https://www.indeed.com/viewjob?jk=1d2979409c83f2a4</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Java)</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Decatur, GA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=338db949c564e874</t>
+          <t>https://www.indeed.com/viewjob?jk=19292a33d87f477b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb067c7ee9c6e671</t>
+          <t>https://www.indeed.com/viewjob?jk=1c45b67d1782f41c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4543a914df9789</t>
+          <t>https://www.indeed.com/viewjob?jk=28e0fdb2d1d8365c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Geospatial Solutions Architect</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>S R International Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4968b1c75b8ea91</t>
+          <t>https://www.indeed.com/viewjob?jk=50082798bb6a8951</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Geospatial Solutions Architect</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,42 +3366,2072 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f71870dc0f7bc53</t>
+          <t>https://www.indeed.com/viewjob?jk=ff4b550996831857</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>AI Data Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7a140e56c36bd8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>AI Data Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7177f3e2822442b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>AI Data Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1f786bfc01c412f</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>AI Data Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c31b397857f539a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>AI Data Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df2a59301082a549</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>AI Data Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=abd442131644c2ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>AI Data Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ac49610be5f7c22</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>AI Data Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2bd327a6115535e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>AI Data Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Jericho, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6fdf53b11b630cb7</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>AI Data Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Dayton, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe7ce02753b98a7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>AI Data Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48e68a3d2a669f96</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>AI Data Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=715a8a81ec1663c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>AI Data Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c61b7a4534477b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>AI Data Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=714987b40a626f2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>AI Data Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc2483f2dc10aa24</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>AI Data Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=41f3867fb9d5fca1</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>AI Data Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e14441426c0e5912</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>AI Data Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de87959267d1c1a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>AI Data Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Boca Raton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=157307b309906617</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>AI Data Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd2a0badba0820e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>AI Data Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Davenport, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a1077e0bf1888ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>AI Data Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Gilbert, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c0316b1d2e51b16</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>AI Data Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91b58529dba10c91</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>AI Data Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bbe26208741cfd88</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>AI Data Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a4deeb487a12f72a</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Engineer II, AWS Connect</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Concentra</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Addison, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16d1c8d1b8c5a8bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Senior Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>adonis</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5621c4e542d4639</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Bounteous</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38299c9de7d6d6a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>NetApp Emerging Talent - Entry Level Software Engineer (Cloud Storage)</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>NetApp</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e07865da969c4a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer - Hybrid</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Snowflake, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=745ab30cde1846a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Sr Data Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Disney Experiences</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7a27a8acf3bc1bc8</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Full-Stack Developer (AWS, TS, React)</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc3a148287061e68</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Engineer III, Machine Learning Software</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Samsung Electronics</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, S3, Spark, Scala, Snowflake, ETL, CI/CD, Airflow, Git, Python</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e38b030f65d339e</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Platform</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Rocket Close</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9fce91f5c39bd4ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>NetApp Emerging Talent - Software Engineer (Cloud Storage)</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>NetApp</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b72bdc255bbf6f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer in Test</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Empirx Health</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Databricks Lakehouse, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6e81f16ad428334</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026009 - Software Engineer</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>John Deere</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Moline, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, Databricks, Scala, PostgreSQL, Docker, Kubernetes, SonarQube</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45e1a444de87fc2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Cloud Data Engineer (Onsite)</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Colony Brands</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Monroe, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f935defc4a70c87e</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>RNGD</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Metairie, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1a3ecae4bdb7e4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>MachineMetrics, Inc.</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, RDS, Scala, Kafka, PostgreSQL, Terraform, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80173e5fca484063</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Microsoft Modern Work Consultant</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Citrin Cooperman</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Carlsbad, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=11d034c0b8905492</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Senior DevOps Cloud Engineer (Information Technology Subject Matter Expert)</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>State of Connecticut</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d267e859d5950f5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Software Developer - Information Governance</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Epiq</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Overland Park, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=65cd9651c7e25101</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Claims Data Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4296ca379ce33eb3</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Sr Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f710f05a18efb3e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Sr Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>MO, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ad148596751872e</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>CapTech Consulting</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=085872f73883326c</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>CapTech Consulting</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa79af047e73dc3e</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>CapTech Consulting</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34987f860a590c53</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Angular / JAVA Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Charles Schwab</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fcfd60088aef43d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer: $150-160,000, MN Based, Hybrid - 2 Days in Office</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>GovDocs</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, MongoDB, ETL, ELT, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8acefc49a07f2d39</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (AI Enablement)</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Redwood Logistics</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48c5c7e7de56c6fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer ( Java)</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Press Ganey</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Decatur, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=338db949c564e874</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Salesforce Data Cloud Architect</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>EPAM Systems</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb067c7ee9c6e671</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Salesforce Data Cloud Architect</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>EPAM Systems</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de4543a914df9789</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
           <t>Data Product Owner</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>Gallagher</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C140" t="inlineStr">
         <is>
           <t>Rolling Meadows, IL, US USA</t>
         </is>
       </c>
-      <c r="D85" t="n">
+      <c r="D140" t="n">
         <v>10.4</v>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E140" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a33815bde90512ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Senior Geospatial Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>S R International Inc</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4968b1c75b8ea91</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Senior Geospatial Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>American business solutions inc</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f71870dc0f7bc53</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Cloud Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>CleanSlate Technology Group</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Carmel, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=478788964e131867</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-15.xlsx
+++ b/results/job_matches_2026-04-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G143"/>
+  <dimension ref="A1:G149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Cons - TC - AI and Data - Enterp Data - Data Eng and Arch - Data Eng - Mgr - MP - 1688246</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AmeriLife</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,104 +626,104 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Google Cloud Platform, GCP, Hadoop, HDFS, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d10f6b2d0d1b341d</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdf2a5f30bbe80a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer 2026 - US,UK</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>AmeriLife</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d01fdc4061dd2a</t>
+          <t>https://www.indeed.com/viewjob?jk=d10f6b2d0d1b341d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Data Engineer 2026 - US,UK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f9a309f4efa98f8</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d01fdc4061dd2a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Information Technology - BI Developer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TCC Verizon Authorized Retailer</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fishers, IN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca19ad92abde46c9</t>
+          <t>https://www.indeed.com/viewjob?jk=5f9a309f4efa98f8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Information Technology - BI Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bioMerieux</t>
+          <t>TCC Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hazelwood, MO, US USA</t>
+          <t>Fishers, IN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Oracle, PostgreSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2788300e5964c54</t>
+          <t>https://www.indeed.com/viewjob?jk=ca19ad92abde46c9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Full Stack AI Engineer</t>
+          <t>Data Warehouse Analyst Seniors: Cloud Engineering</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=574e10b9b787dc54</t>
+          <t>https://www.indeed.com/viewjob?jk=d87aa04a7733264b</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac615cac5200efc9</t>
+          <t>https://www.indeed.com/viewjob?jk=574e10b9b787dc54</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a7de03320b3d487</t>
+          <t>https://www.indeed.com/viewjob?jk=ac615cac5200efc9</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df1418000450ecdb</t>
+          <t>https://www.indeed.com/viewjob?jk=8a7de03320b3d487</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6df75aab0012c038</t>
+          <t>https://www.indeed.com/viewjob?jk=df1418000450ecdb</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Java Developer (Hybrid- Flexible Options)</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Edgewood, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25ccf7fa8d4a5b10</t>
+          <t>https://www.indeed.com/viewjob?jk=6df75aab0012c038</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Java Developer (Hybrid- Flexible Options)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Southern Company</t>
+          <t>Broadridge</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Edgewood, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be194d530456f66</t>
+          <t>https://www.indeed.com/viewjob?jk=25ccf7fa8d4a5b10</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Operations Engineer (Cloud)</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Stifel</t>
+          <t>Southern Company</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d061193f264addea</t>
+          <t>https://www.indeed.com/viewjob?jk=3be194d530456f66</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Operations Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>Stifel</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99b4467c3c6aa55</t>
+          <t>https://www.indeed.com/viewjob?jk=d061193f264addea</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Architect I</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Azure, Data Factory, Databricks</t>
+          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6d97da40a8da560</t>
+          <t>https://www.indeed.com/viewjob?jk=e99b4467c3c6aa55</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Architect I</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Express</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,77 +1151,77 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, BigQuery, Scala, Oracle, MongoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Azure, Data Factory, Databricks</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27ee634b56d5a4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=c6d97da40a8da560</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Database and Dashboard Developer</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Oracle</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Azure, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fee5a2d73882379c</t>
+          <t>https://www.indeed.com/viewjob?jk=fcd17ae9e035b9a9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>Express</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, ECS, RDS, GCP, BigQuery, Scala, Oracle, MongoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ead7a3e6b1951593</t>
+          <t>https://www.indeed.com/viewjob?jk=27ee634b56d5a4e3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Database and Dashboard Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,19 +1266,19 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae18e6a8860be459</t>
+          <t>https://www.indeed.com/viewjob?jk=fee5a2d73882379c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer (contract)</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Oracle, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23956751504b8384</t>
+          <t>https://www.indeed.com/viewjob?jk=ead7a3e6b1951593</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Solution Architect, Enterprise</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,29 +1326,29 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f33106731db1775</t>
+          <t>https://www.indeed.com/viewjob?jk=ae18e6a8860be459</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Solution Architect, Enterprise</t>
+          <t>Snowflake Data Engineer (contract)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90d356ab99a57489</t>
+          <t>https://www.indeed.com/viewjob?jk=23956751504b8384</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Solution Architect, Enterprise</t>
+          <t>Senior Data &amp; AI Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Olson Kundig</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15664632526fabdb</t>
+          <t>https://www.indeed.com/viewjob?jk=d831e0d8e2c5553f</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data &amp; AI Governance Officer</t>
+          <t>Solution Architect, Enterprise</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Vantage Bank Texas</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,112 +1501,112 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Data Factory, Databricks, ELT, Power BI, Tableau</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c469b183725fde1</t>
+          <t>https://www.indeed.com/viewjob?jk=3f33106731db1775</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solution Architect, Enterprise</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Robstown, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=072e6e4e8e025141</t>
+          <t>https://www.indeed.com/viewjob?jk=90d356ab99a57489</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Mid-Level Data Engineer, Global</t>
+          <t>Solution Architect, Enterprise</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c717630a440c614c</t>
+          <t>https://www.indeed.com/viewjob?jk=15664632526fabdb</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Data &amp; AI Governance Officer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Vantage Bank Texas</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Glue, S3, RDS, Azure, Data Factory, Databricks, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15a32bf71ba33ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=5c469b183725fde1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Robstown, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d3db28285f41c46</t>
+          <t>https://www.indeed.com/viewjob?jk=072e6e4e8e025141</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Mid-Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3989068a8778fb79</t>
+          <t>https://www.indeed.com/viewjob?jk=c717630a440c614c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c70a1cb7dff6fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=15a32bf71ba33ffa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de9b476cdbf12e9</t>
+          <t>https://www.indeed.com/viewjob?jk=4d3db28285f41c46</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Research Engineer II</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bryan, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb85a1b8d1928fd4</t>
+          <t>https://www.indeed.com/viewjob?jk=3989068a8778fb79</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ArcGIS Software Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1186a0273eb12d27</t>
+          <t>https://www.indeed.com/viewjob?jk=5c70a1cb7dff6fb6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f177704478aadbe</t>
+          <t>https://www.indeed.com/viewjob?jk=3de9b476cdbf12e9</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Research Engineer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Frida</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Bryan, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8900daeea8c64c35</t>
+          <t>https://www.indeed.com/viewjob?jk=09b3207da19db4ee</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Sr. ETL/Python Developer)</t>
+          <t>Research Engineer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RCR Technology</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bryan, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4527effc81797bda</t>
+          <t>https://www.indeed.com/viewjob?jk=bb85a1b8d1928fd4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Support Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Illumen Group</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Stafford, VA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, Databricks, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92cd661cf5a17182</t>
+          <t>https://www.indeed.com/viewjob?jk=9f177704478aadbe</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Engineer II – Big Data / ETL Engineer (Apptio)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Frida</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling</t>
+          <t>AWS, IAM, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be9de9e1e7dbc172</t>
+          <t>https://www.indeed.com/viewjob?jk=8900daeea8c64c35</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>ArcGIS Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AllCloud</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, API Gateway, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a0467416d94bb26</t>
+          <t>https://www.indeed.com/viewjob?jk=1186a0273eb12d27</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Development Engineer II (C#/.NET, Azure)</t>
+          <t>Senior Data Engineer (Sr. ETL/Python Developer)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>RCR Technology</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6c902472d880e18</t>
+          <t>https://www.indeed.com/viewjob?jk=4527effc81797bda</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Mgr Data Engineering</t>
+          <t>Data Support Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Illumen Group</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Stafford, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, Athena, S3, Databricks, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e707506ab6122a</t>
+          <t>https://www.indeed.com/viewjob?jk=92cd661cf5a17182</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a527d30b5c00d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=8a0467416d94bb26</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer II (C#/.NET, Azure)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Banner Health</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1bf292f1b43ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=b6c902472d880e18</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cloud Automation Engineer</t>
+          <t>Sr Mgr Data Engineering</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Vantage Bank Texas</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f9ce6ba5f081b9</t>
+          <t>https://www.indeed.com/viewjob?jk=03e707506ab6122a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62c75d5f8fbde70d</t>
+          <t>https://www.indeed.com/viewjob?jk=1a527d30b5c00d7d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Medeloop</t>
+          <t>Banner Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a81ed0b08e8f07f7</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1bf292f1b43ebd</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Cloud Automation Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>Vantage Bank Texas</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ff91e3d3905a73</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f9ce6ba5f081b9</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cbee15ac5e5d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=62c75d5f8fbde70d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RJW Logistics</t>
+          <t>Medeloop</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef58fd9ad5dd15ff</t>
+          <t>https://www.indeed.com/viewjob?jk=a81ed0b08e8f07f7</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf17dcf23ea3201f</t>
+          <t>https://www.indeed.com/viewjob?jk=30ff91e3d3905a73</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,67 +2456,67 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766ed066e436eb0c</t>
+          <t>https://www.indeed.com/viewjob?jk=17cbee15ac5e5d6a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Backend Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c080bdfd0f5497</t>
+          <t>https://www.indeed.com/viewjob?jk=ae2342b890625b11</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>RJW Logistics</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01aefad23a0eebfc</t>
+          <t>https://www.indeed.com/viewjob?jk=ef58fd9ad5dd15ff</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b79af965edb52688</t>
+          <t>https://www.indeed.com/viewjob?jk=bf17dcf23ea3201f</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe099d836f48656</t>
+          <t>https://www.indeed.com/viewjob?jk=766ed066e436eb0c</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8756dcda438f6959</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c080bdfd0f5497</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c70b98cc7f980bc</t>
+          <t>https://www.indeed.com/viewjob?jk=01aefad23a0eebfc</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa8671f82044c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=b79af965edb52688</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bddaca0e62ee366</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe099d836f48656</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4177c81ac5d66b2d</t>
+          <t>https://www.indeed.com/viewjob?jk=8756dcda438f6959</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02c32fad4b2ac01d</t>
+          <t>https://www.indeed.com/viewjob?jk=3c70b98cc7f980bc</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=964bc462945e695c</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa8671f82044c5a</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7beb81f1fe47bc19</t>
+          <t>https://www.indeed.com/viewjob?jk=9bddaca0e62ee366</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3c6d71a96ee8e3e</t>
+          <t>https://www.indeed.com/viewjob?jk=4177c81ac5d66b2d</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e48e8aee6232ce</t>
+          <t>https://www.indeed.com/viewjob?jk=02c32fad4b2ac01d</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26cc56905b519e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=964bc462945e695c</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=416163a4caa0a101</t>
+          <t>https://www.indeed.com/viewjob?jk=7beb81f1fe47bc19</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b314b34d858c384</t>
+          <t>https://www.indeed.com/viewjob?jk=a3c6d71a96ee8e3e</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d26c232b74cd8f7</t>
+          <t>https://www.indeed.com/viewjob?jk=85e48e8aee6232ce</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0461589d526a9a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=26cc56905b519e4a</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a01db0a34a1698ca</t>
+          <t>https://www.indeed.com/viewjob?jk=416163a4caa0a101</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d2979409c83f2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=6b314b34d858c384</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19292a33d87f477b</t>
+          <t>https://www.indeed.com/viewjob?jk=3d26c232b74cd8f7</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c45b67d1782f41c</t>
+          <t>https://www.indeed.com/viewjob?jk=0461589d526a9a5c</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e0fdb2d1d8365c</t>
+          <t>https://www.indeed.com/viewjob?jk=a01db0a34a1698ca</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50082798bb6a8951</t>
+          <t>https://www.indeed.com/viewjob?jk=1d2979409c83f2a4</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff4b550996831857</t>
+          <t>https://www.indeed.com/viewjob?jk=19292a33d87f477b</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7a140e56c36bd8e</t>
+          <t>https://www.indeed.com/viewjob?jk=1c45b67d1782f41c</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7177f3e2822442b8</t>
+          <t>https://www.indeed.com/viewjob?jk=28e0fdb2d1d8365c</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f786bfc01c412f</t>
+          <t>https://www.indeed.com/viewjob?jk=50082798bb6a8951</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c31b397857f539a8</t>
+          <t>https://www.indeed.com/viewjob?jk=ff4b550996831857</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2a59301082a549</t>
+          <t>https://www.indeed.com/viewjob?jk=e7a140e56c36bd8e</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd442131644c2ae</t>
+          <t>https://www.indeed.com/viewjob?jk=7177f3e2822442b8</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac49610be5f7c22</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f786bfc01c412f</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd327a6115535e1</t>
+          <t>https://www.indeed.com/viewjob?jk=c31b397857f539a8</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fdf53b11b630cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=df2a59301082a549</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7ce02753b98a7f</t>
+          <t>https://www.indeed.com/viewjob?jk=abd442131644c2ae</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48e68a3d2a669f96</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac49610be5f7c22</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=715a8a81ec1663c0</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd327a6115535e1</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c61b7a4534477b1</t>
+          <t>https://www.indeed.com/viewjob?jk=6fdf53b11b630cb7</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=714987b40a626f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7ce02753b98a7f</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc2483f2dc10aa24</t>
+          <t>https://www.indeed.com/viewjob?jk=48e68a3d2a669f96</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f3867fb9d5fca1</t>
+          <t>https://www.indeed.com/viewjob?jk=715a8a81ec1663c0</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e14441426c0e5912</t>
+          <t>https://www.indeed.com/viewjob?jk=8c61b7a4534477b1</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de87959267d1c1a1</t>
+          <t>https://www.indeed.com/viewjob?jk=714987b40a626f2c</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157307b309906617</t>
+          <t>https://www.indeed.com/viewjob?jk=bc2483f2dc10aa24</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd2a0badba0820e7</t>
+          <t>https://www.indeed.com/viewjob?jk=41f3867fb9d5fca1</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a1077e0bf1888ba</t>
+          <t>https://www.indeed.com/viewjob?jk=e14441426c0e5912</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c0316b1d2e51b16</t>
+          <t>https://www.indeed.com/viewjob?jk=de87959267d1c1a1</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91b58529dba10c91</t>
+          <t>https://www.indeed.com/viewjob?jk=157307b309906617</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbe26208741cfd88</t>
+          <t>https://www.indeed.com/viewjob?jk=fd2a0badba0820e7</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4deeb487a12f72a</t>
+          <t>https://www.indeed.com/viewjob?jk=3a1077e0bf1888ba</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Engineer II, AWS Connect</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d1c8d1b8c5a8bd</t>
+          <t>https://www.indeed.com/viewjob?jk=8c0316b1d2e51b16</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>adonis</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5621c4e542d4639</t>
+          <t>https://www.indeed.com/viewjob?jk=91b58529dba10c91</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38299c9de7d6d6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=bbe26208741cfd88</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>NetApp Emerging Talent - Entry Level Software Engineer (Cloud Storage)</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e07865da969c4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=a4deeb487a12f72a</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Hybrid</t>
+          <t>Engineer II, AWS Connect</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Snowflake, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=745ab30cde1846a7</t>
+          <t>https://www.indeed.com/viewjob?jk=16d1c8d1b8c5a8bd</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>adonis</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a27a8acf3bc1bc8</t>
+          <t>https://www.indeed.com/viewjob?jk=e5621c4e542d4639</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Full-Stack Developer (AWS, TS, React)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc3a148287061e68</t>
+          <t>https://www.indeed.com/viewjob?jk=38299c9de7d6d6a0</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Engineer III, Machine Learning Software</t>
+          <t>NetApp Emerging Talent - Entry Level Software Engineer (Cloud Storage)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, S3, Spark, Scala, Snowflake, ETL, CI/CD, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e38b030f65d339e</t>
+          <t>https://www.indeed.com/viewjob?jk=7e07865da969c4a3</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform</t>
+          <t>Sr. Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Rocket Close</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Snowflake, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fce91f5c39bd4ed</t>
+          <t>https://www.indeed.com/viewjob?jk=745ab30cde1846a7</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>NetApp Emerging Talent - Software Engineer (Cloud Storage)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b72bdc255bbf6f8</t>
+          <t>https://www.indeed.com/viewjob?jk=7a27a8acf3bc1bc8</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test</t>
+          <t>Full-Stack Developer (AWS, TS, React)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Databricks Lakehouse, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6e81f16ad428334</t>
+          <t>https://www.indeed.com/viewjob?jk=cc3a148287061e68</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026009 - Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>John Deere</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Moline, IL, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,42 +4651,42 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Scala, PostgreSQL, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e1a444de87fc2c</t>
+          <t>https://www.indeed.com/viewjob?jk=10b635a4480602f9</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer (Onsite)</t>
+          <t>Engineer III, Machine Learning Software</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Colony Brands</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Monroe, WI, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, S3, Spark, Scala, Snowflake, ETL, CI/CD, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f935defc4a70c87e</t>
+          <t>https://www.indeed.com/viewjob?jk=4e38b030f65d339e</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>RNGD</t>
+          <t>BillGO, Inc.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, DynamoDB, Star Schema, ELT, Tableau, GitHub Actions</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a3ecae4bdb7e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=69713d6be44a4b67</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>MachineMetrics, Inc.</t>
+          <t>Rocket Close</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, RDS, Scala, Kafka, PostgreSQL, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80173e5fca484063</t>
+          <t>https://www.indeed.com/viewjob?jk=9fce91f5c39bd4ed</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Microsoft Modern Work Consultant</t>
+          <t>NetApp Emerging Talent - Software Engineer (Cloud Storage)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11d034c0b8905492</t>
+          <t>https://www.indeed.com/viewjob?jk=4b72bdc255bbf6f8</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer (Information Technology Subject Matter Expert)</t>
+          <t>Senior Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>State of Connecticut</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Databricks Lakehouse, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d267e859d5950f5a</t>
+          <t>https://www.indeed.com/viewjob?jk=a6e81f16ad428334</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Software Developer - Information Governance</t>
+          <t>2026009 - Software Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>John Deere</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Moline, IL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Scala, PostgreSQL, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65cd9651c7e25101</t>
+          <t>https://www.indeed.com/viewjob?jk=45e1a444de87fc2c</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>Cloud Data Engineer (Onsite)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Colony Brands</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Monroe, WI, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>AWS, Redshift, RDS, Azure, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4296ca379ce33eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=f935defc4a70c87e</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>RNGD</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
+          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f710f05a18efb3e1</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a3ecae4bdb7e4b</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>MachineMetrics, Inc.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Kinesis, RDS, Scala, Kafka, PostgreSQL, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ad148596751872e</t>
+          <t>https://www.indeed.com/viewjob?jk=80173e5fca484063</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Microsoft Modern Work Consultant</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085872f73883326c</t>
+          <t>https://www.indeed.com/viewjob?jk=11d034c0b8905492</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior DevOps Cloud Engineer (Information Technology Subject Matter Expert)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>State of Connecticut</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa79af047e73dc3e</t>
+          <t>https://www.indeed.com/viewjob?jk=d267e859d5950f5a</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Software Developer - Information Governance</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,19 +5081,19 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34987f860a590c53</t>
+          <t>https://www.indeed.com/viewjob?jk=65cd9651c7e25101</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Angular / JAVA Full Stack Engineer</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcfd60088aef43d3</t>
+          <t>https://www.indeed.com/viewjob?jk=f710f05a18efb3e1</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Data Engineer: $150-160,000, MN Based, Hybrid - 2 Days in Office</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>GovDocs</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, MongoDB, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8acefc49a07f2d39</t>
+          <t>https://www.indeed.com/viewjob?jk=6ad148596751872e</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AI Enablement)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48c5c7e7de56c6fb</t>
+          <t>https://www.indeed.com/viewjob?jk=085872f73883326c</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Java)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Decatur, GA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=338db949c564e874</t>
+          <t>https://www.indeed.com/viewjob?jk=fa79af047e73dc3e</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb067c7ee9c6e671</t>
+          <t>https://www.indeed.com/viewjob?jk=34987f860a590c53</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4543a914df9789</t>
+          <t>https://www.indeed.com/viewjob?jk=4296ca379ce33eb3</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Data Product Owner</t>
+          <t>Angular / JAVA Full Stack Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Gallagher</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Rolling Meadows, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, Azure, GCP, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33815bde90512ef</t>
+          <t>https://www.indeed.com/viewjob?jk=fcfd60088aef43d3</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Geospatial Solutions Architect</t>
+          <t>Senior Data Engineer: $150-160,000, MN Based, Hybrid - 2 Days in Office</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>S R International Inc</t>
+          <t>GovDocs</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, MongoDB, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4968b1c75b8ea91</t>
+          <t>https://www.indeed.com/viewjob?jk=8acefc49a07f2d39</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Geospatial Solutions Architect</t>
+          <t>Senior Software Engineer (AI Enablement)</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f71870dc0f7bc53</t>
+          <t>https://www.indeed.com/viewjob?jk=48c5c7e7de56c6fb</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior Software Engineer ( Java)</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>CleanSlate Technology Group</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Decatur, GA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,15 +5421,225 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=338db949c564e874</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Salesforce Data Cloud Architect</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>EPAM Systems</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb067c7ee9c6e671</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Salesforce Data Cloud Architect</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>EPAM Systems</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de4543a914df9789</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Data Product Owner</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Gallagher</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Rolling Meadows, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a33815bde90512ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Senior Geospatial Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>S R International Inc</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4968b1c75b8ea91</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Senior Geospatial Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>American business solutions inc</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f71870dc0f7bc53</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Cloud Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>CleanSlate Technology Group</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Carmel, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
           <t>AWS, Azure, Scala, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation, Jenkins, Git</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
+      <c r="F149" t="inlineStr">
         <is>
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
+      <c r="G149" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=478788964e131867</t>
         </is>

--- a/results/job_matches_2026-04-15.xlsx
+++ b/results/job_matches_2026-04-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G149"/>
+  <dimension ref="A1:G155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>TargetPath Solutions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4478c55d459f6590</t>
+          <t>https://www.indeed.com/viewjob?jk=ddaefa90999433c3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud Engineer-Associate-Dallas</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS, Spark</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=452922c279cc36e9</t>
+          <t>https://www.indeed.com/viewjob?jk=4478c55d459f6590</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Remote)</t>
+          <t>Asset &amp; Wealth Management-Cloud Engineer-Associate-Dallas</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Universal Background Screening</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,69 +556,69 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c305c75d9c817c14</t>
+          <t>https://www.indeed.com/viewjob?jk=452922c279cc36e9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI/ML Data Engineer</t>
+          <t>DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Marvell Technology</t>
+          <t>Universal Background Screening</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Kafka</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db6fecac436797a9</t>
+          <t>https://www.indeed.com/viewjob?jk=c305c75d9c817c14</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cons - TC - AI and Data - Enterp Data - Data Eng and Arch - Data Eng - Mgr - MP - 1688246</t>
+          <t>AI/ML Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Marvell Technology</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Google Cloud Platform, GCP, Hadoop, HDFS, Oracle</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdf2a5f30bbe80a</t>
+          <t>https://www.indeed.com/viewjob?jk=db6fecac436797a9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Cons - TC - AI and Data - Enterp Data - Data Eng and Arch - Data Eng - Mgr - MP - 1688246</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AmeriLife</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,104 +661,104 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Google Cloud Platform, GCP, Hadoop, HDFS, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d10f6b2d0d1b341d</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdf2a5f30bbe80a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer 2026 - US,UK</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>AmeriLife</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d01fdc4061dd2a</t>
+          <t>https://www.indeed.com/viewjob?jk=d10f6b2d0d1b341d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Data Engineer 2026 - US,UK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f9a309f4efa98f8</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d01fdc4061dd2a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Information Technology - BI Developer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TCC Verizon Authorized Retailer</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fishers, IN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca19ad92abde46c9</t>
+          <t>https://www.indeed.com/viewjob?jk=5f9a309f4efa98f8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Warehouse Analyst Seniors: Cloud Engineering</t>
+          <t>Information Technology - BI Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>TCC Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Fishers, IN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, ETL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d87aa04a7733264b</t>
+          <t>https://www.indeed.com/viewjob?jk=ca19ad92abde46c9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Full Stack AI Engineer</t>
+          <t>Data Warehouse Analyst Seniors: Cloud Engineering</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=574e10b9b787dc54</t>
+          <t>https://www.indeed.com/viewjob?jk=d87aa04a7733264b</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac615cac5200efc9</t>
+          <t>https://www.indeed.com/viewjob?jk=574e10b9b787dc54</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a7de03320b3d487</t>
+          <t>https://www.indeed.com/viewjob?jk=ac615cac5200efc9</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df1418000450ecdb</t>
+          <t>https://www.indeed.com/viewjob?jk=8a7de03320b3d487</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6df75aab0012c038</t>
+          <t>https://www.indeed.com/viewjob?jk=df1418000450ecdb</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Java Developer (Hybrid- Flexible Options)</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Edgewood, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25ccf7fa8d4a5b10</t>
+          <t>https://www.indeed.com/viewjob?jk=6df75aab0012c038</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Java Developer (Hybrid- Flexible Options)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Southern Company</t>
+          <t>Broadridge</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Edgewood, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be194d530456f66</t>
+          <t>https://www.indeed.com/viewjob?jk=25ccf7fa8d4a5b10</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Operations Engineer (Cloud)</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Stifel</t>
+          <t>Southern Company</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d061193f264addea</t>
+          <t>https://www.indeed.com/viewjob?jk=3be194d530456f66</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Operations Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>Stifel</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99b4467c3c6aa55</t>
+          <t>https://www.indeed.com/viewjob?jk=d061193f264addea</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Architect I</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Ignite Insurance Systems</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Azure, Data Factory, Databricks</t>
+          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6d97da40a8da560</t>
+          <t>https://www.indeed.com/viewjob?jk=560d14506d8aa36b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Azure, GCP, Scala, Kafka</t>
+          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcd17ae9e035b9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=e99b4467c3c6aa55</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Architect I</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Express</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,77 +1221,77 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, BigQuery, Scala, Oracle, MongoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Azure, Data Factory, Databricks</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27ee634b56d5a4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=c6d97da40a8da560</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Database and Dashboard Developer</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Oracle</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Azure, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fee5a2d73882379c</t>
+          <t>https://www.indeed.com/viewjob?jk=fcd17ae9e035b9a9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>Express</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, ECS, RDS, GCP, BigQuery, Scala, Oracle, MongoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ead7a3e6b1951593</t>
+          <t>https://www.indeed.com/viewjob?jk=27ee634b56d5a4e3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Database and Dashboard Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,19 +1336,19 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae18e6a8860be459</t>
+          <t>https://www.indeed.com/viewjob?jk=fee5a2d73882379c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer (contract)</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Oracle, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23956751504b8384</t>
+          <t>https://www.indeed.com/viewjob?jk=ead7a3e6b1951593</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Developer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Olson Kundig</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,19 +1406,19 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d831e0d8e2c5553f</t>
+          <t>https://www.indeed.com/viewjob?jk=ae18e6a8860be459</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Solution Architect, Enterprise</t>
+          <t>Snowflake Data Engineer (contract)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1431,24 +1431,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=507830f63a6d47c9</t>
+          <t>https://www.indeed.com/viewjob?jk=23956751504b8384</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Solution Architect, Enterprise</t>
+          <t>Solution Architect, Enterprise</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98d7971656e73b43</t>
+          <t>https://www.indeed.com/viewjob?jk=3f33106731db1775</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f33106731db1775</t>
+          <t>https://www.indeed.com/viewjob?jk=90d356ab99a57489</t>
         </is>
       </c>
     </row>
@@ -1546,14 +1546,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90d356ab99a57489</t>
+          <t>https://www.indeed.com/viewjob?jk=15664632526fabdb</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Solution Architect, Enterprise</t>
+          <t>Senior Solution Architect, Enterprise</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15664632526fabdb</t>
+          <t>https://www.indeed.com/viewjob?jk=507830f63a6d47c9</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data &amp; AI Governance Officer</t>
+          <t>Senior Solution Architect, Enterprise</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Vantage Bank Texas</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,42 +1606,42 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Data Factory, Databricks, ELT, Power BI, Tableau</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c469b183725fde1</t>
+          <t>https://www.indeed.com/viewjob?jk=98d7971656e73b43</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data &amp; AI Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Olson Kundig</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Robstown, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=072e6e4e8e025141</t>
+          <t>https://www.indeed.com/viewjob?jk=d831e0d8e2c5553f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Mid-Level Data Engineer, Global</t>
+          <t>Data &amp; AI Governance Officer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Vantage Bank Texas</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>AWS, Glue, S3, RDS, Azure, Data Factory, Databricks, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c717630a440c614c</t>
+          <t>https://www.indeed.com/viewjob?jk=5c469b183725fde1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Robstown, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15a32bf71ba33ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=072e6e4e8e025141</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Mid-Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d3db28285f41c46</t>
+          <t>https://www.indeed.com/viewjob?jk=c717630a440c614c</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3989068a8778fb79</t>
+          <t>https://www.indeed.com/viewjob?jk=15a32bf71ba33ffa</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c70a1cb7dff6fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=4d3db28285f41c46</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de9b476cdbf12e9</t>
+          <t>https://www.indeed.com/viewjob?jk=3989068a8778fb79</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Research Engineer II</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bryan, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b3207da19db4ee</t>
+          <t>https://www.indeed.com/viewjob?jk=5c70a1cb7dff6fb6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Research Engineer II</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bryan, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb85a1b8d1928fd4</t>
+          <t>https://www.indeed.com/viewjob?jk=3de9b476cdbf12e9</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Research Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Bryan, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f177704478aadbe</t>
+          <t>https://www.indeed.com/viewjob?jk=09b3207da19db4ee</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Research Engineer II</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Frida</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Bryan, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8900daeea8c64c35</t>
+          <t>https://www.indeed.com/viewjob?jk=bb85a1b8d1928fd4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ArcGIS Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1186a0273eb12d27</t>
+          <t>https://www.indeed.com/viewjob?jk=9f177704478aadbe</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Sr. ETL/Python Developer)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RCR Technology</t>
+          <t>Frida</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, IAM, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4527effc81797bda</t>
+          <t>https://www.indeed.com/viewjob?jk=8900daeea8c64c35</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Support Engineer</t>
+          <t>ArcGIS Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Illumen Group</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Stafford, VA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, Databricks, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, API Gateway, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,19 +2106,19 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92cd661cf5a17182</t>
+          <t>https://www.indeed.com/viewjob?jk=1186a0273eb12d27</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Engineer (Sr. ETL/Python Developer)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AllCloud</t>
+          <t>RCR Technology</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a0467416d94bb26</t>
+          <t>https://www.indeed.com/viewjob?jk=4527effc81797bda</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Development Engineer II (C#/.NET, Azure)</t>
+          <t>Data Support Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Illumen Group</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Stafford, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Glue, Redshift, Athena, S3, Databricks, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6c902472d880e18</t>
+          <t>https://www.indeed.com/viewjob?jk=92cd661cf5a17182</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Mgr Data Engineering</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e707506ab6122a</t>
+          <t>https://www.indeed.com/viewjob?jk=8a0467416d94bb26</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Software Development Engineer II (C#/.NET, Azure)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a527d30b5c00d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=b6c902472d880e18</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Mgr Data Engineering</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Banner Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1bf292f1b43ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=03e707506ab6122a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cloud Automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Vantage Bank Texas</t>
+          <t>Banner Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f9ce6ba5f081b9</t>
+          <t>https://www.indeed.com/viewjob?jk=c8d9928392bc7529</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62c75d5f8fbde70d</t>
+          <t>https://www.indeed.com/viewjob?jk=1a527d30b5c00d7d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Medeloop</t>
+          <t>Banner Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a81ed0b08e8f07f7</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1bf292f1b43ebd</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Cloud Automation Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>Vantage Bank Texas</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ff91e3d3905a73</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f9ce6ba5f081b9</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cbee15ac5e5d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=62c75d5f8fbde70d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Backend Engineer II</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>Medeloop</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae2342b890625b11</t>
+          <t>https://www.indeed.com/viewjob?jk=a81ed0b08e8f07f7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>RJW Logistics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Beacon, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef58fd9ad5dd15ff</t>
+          <t>https://www.indeed.com/viewjob?jk=81ac0513866a1f53</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf17dcf23ea3201f</t>
+          <t>https://www.indeed.com/viewjob?jk=30ff91e3d3905a73</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766ed066e436eb0c</t>
+          <t>https://www.indeed.com/viewjob?jk=17cbee15ac5e5d6a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,67 +2631,67 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c080bdfd0f5497</t>
+          <t>https://www.indeed.com/viewjob?jk=bf17dcf23ea3201f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Backend Engineer II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01aefad23a0eebfc</t>
+          <t>https://www.indeed.com/viewjob?jk=ae2342b890625b11</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>RJW Logistics</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b79af965edb52688</t>
+          <t>https://www.indeed.com/viewjob?jk=ef58fd9ad5dd15ff</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Data Engineer - Dallas, TX</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe099d836f48656</t>
+          <t>https://www.indeed.com/viewjob?jk=865a46cfbc7cc3f4</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8756dcda438f6959</t>
+          <t>https://www.indeed.com/viewjob?jk=766ed066e436eb0c</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c70b98cc7f980bc</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c080bdfd0f5497</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa8671f82044c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=01aefad23a0eebfc</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bddaca0e62ee366</t>
+          <t>https://www.indeed.com/viewjob?jk=b79af965edb52688</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4177c81ac5d66b2d</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe099d836f48656</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02c32fad4b2ac01d</t>
+          <t>https://www.indeed.com/viewjob?jk=8756dcda438f6959</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=964bc462945e695c</t>
+          <t>https://www.indeed.com/viewjob?jk=3c70b98cc7f980bc</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7beb81f1fe47bc19</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa8671f82044c5a</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3c6d71a96ee8e3e</t>
+          <t>https://www.indeed.com/viewjob?jk=9bddaca0e62ee366</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e48e8aee6232ce</t>
+          <t>https://www.indeed.com/viewjob?jk=4177c81ac5d66b2d</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26cc56905b519e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=02c32fad4b2ac01d</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=416163a4caa0a101</t>
+          <t>https://www.indeed.com/viewjob?jk=964bc462945e695c</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b314b34d858c384</t>
+          <t>https://www.indeed.com/viewjob?jk=7beb81f1fe47bc19</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d26c232b74cd8f7</t>
+          <t>https://www.indeed.com/viewjob?jk=a3c6d71a96ee8e3e</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0461589d526a9a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=85e48e8aee6232ce</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a01db0a34a1698ca</t>
+          <t>https://www.indeed.com/viewjob?jk=26cc56905b519e4a</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d2979409c83f2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=416163a4caa0a101</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19292a33d87f477b</t>
+          <t>https://www.indeed.com/viewjob?jk=6b314b34d858c384</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c45b67d1782f41c</t>
+          <t>https://www.indeed.com/viewjob?jk=3d26c232b74cd8f7</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e0fdb2d1d8365c</t>
+          <t>https://www.indeed.com/viewjob?jk=0461589d526a9a5c</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50082798bb6a8951</t>
+          <t>https://www.indeed.com/viewjob?jk=a01db0a34a1698ca</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff4b550996831857</t>
+          <t>https://www.indeed.com/viewjob?jk=1d2979409c83f2a4</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7a140e56c36bd8e</t>
+          <t>https://www.indeed.com/viewjob?jk=19292a33d87f477b</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7177f3e2822442b8</t>
+          <t>https://www.indeed.com/viewjob?jk=1c45b67d1782f41c</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f786bfc01c412f</t>
+          <t>https://www.indeed.com/viewjob?jk=28e0fdb2d1d8365c</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c31b397857f539a8</t>
+          <t>https://www.indeed.com/viewjob?jk=50082798bb6a8951</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2a59301082a549</t>
+          <t>https://www.indeed.com/viewjob?jk=ff4b550996831857</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd442131644c2ae</t>
+          <t>https://www.indeed.com/viewjob?jk=e7a140e56c36bd8e</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac49610be5f7c22</t>
+          <t>https://www.indeed.com/viewjob?jk=7177f3e2822442b8</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd327a6115535e1</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f786bfc01c412f</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fdf53b11b630cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=c31b397857f539a8</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7ce02753b98a7f</t>
+          <t>https://www.indeed.com/viewjob?jk=df2a59301082a549</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48e68a3d2a669f96</t>
+          <t>https://www.indeed.com/viewjob?jk=abd442131644c2ae</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=715a8a81ec1663c0</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac49610be5f7c22</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c61b7a4534477b1</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd327a6115535e1</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=714987b40a626f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=6fdf53b11b630cb7</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc2483f2dc10aa24</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7ce02753b98a7f</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f3867fb9d5fca1</t>
+          <t>https://www.indeed.com/viewjob?jk=48e68a3d2a669f96</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e14441426c0e5912</t>
+          <t>https://www.indeed.com/viewjob?jk=715a8a81ec1663c0</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de87959267d1c1a1</t>
+          <t>https://www.indeed.com/viewjob?jk=8c61b7a4534477b1</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157307b309906617</t>
+          <t>https://www.indeed.com/viewjob?jk=714987b40a626f2c</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd2a0badba0820e7</t>
+          <t>https://www.indeed.com/viewjob?jk=bc2483f2dc10aa24</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a1077e0bf1888ba</t>
+          <t>https://www.indeed.com/viewjob?jk=41f3867fb9d5fca1</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c0316b1d2e51b16</t>
+          <t>https://www.indeed.com/viewjob?jk=e14441426c0e5912</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91b58529dba10c91</t>
+          <t>https://www.indeed.com/viewjob?jk=de87959267d1c1a1</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbe26208741cfd88</t>
+          <t>https://www.indeed.com/viewjob?jk=157307b309906617</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4deeb487a12f72a</t>
+          <t>https://www.indeed.com/viewjob?jk=fd2a0badba0820e7</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Engineer II, AWS Connect</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d1c8d1b8c5a8bd</t>
+          <t>https://www.indeed.com/viewjob?jk=3a1077e0bf1888ba</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>adonis</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5621c4e542d4639</t>
+          <t>https://www.indeed.com/viewjob?jk=8c0316b1d2e51b16</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38299c9de7d6d6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=91b58529dba10c91</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>NetApp Emerging Talent - Entry Level Software Engineer (Cloud Storage)</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e07865da969c4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=bbe26208741cfd88</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Hybrid</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Snowflake, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=745ab30cde1846a7</t>
+          <t>https://www.indeed.com/viewjob?jk=a4deeb487a12f72a</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Engineer II, AWS Connect</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a27a8acf3bc1bc8</t>
+          <t>https://www.indeed.com/viewjob?jk=16d1c8d1b8c5a8bd</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Full-Stack Developer (AWS, TS, React)</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>adonis</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc3a148287061e68</t>
+          <t>https://www.indeed.com/viewjob?jk=e5621c4e542d4639</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b635a4480602f9</t>
+          <t>https://www.indeed.com/viewjob?jk=38299c9de7d6d6a0</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Engineer III, Machine Learning Software</t>
+          <t>NetApp Emerging Talent - Entry Level Software Engineer (Cloud Storage)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, S3, Spark, Scala, Snowflake, ETL, CI/CD, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e38b030f65d339e</t>
+          <t>https://www.indeed.com/viewjob?jk=7e07865da969c4a3</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Sr. Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>BillGO, Inc.</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, DynamoDB, Star Schema, ELT, Tableau, GitHub Actions</t>
+          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Snowflake, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69713d6be44a4b67</t>
+          <t>https://www.indeed.com/viewjob?jk=745ab30cde1846a7</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Rocket Close</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fce91f5c39bd4ed</t>
+          <t>https://www.indeed.com/viewjob?jk=7a27a8acf3bc1bc8</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>NetApp Emerging Talent - Software Engineer (Cloud Storage)</t>
+          <t>Full-Stack Developer (AWS, TS, React)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b72bdc255bbf6f8</t>
+          <t>https://www.indeed.com/viewjob?jk=cc3a148287061e68</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test</t>
+          <t>Engineer III, Machine Learning Software</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Databricks Lakehouse, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, Spark, Scala, Snowflake, ETL, CI/CD, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6e81f16ad428334</t>
+          <t>https://www.indeed.com/viewjob?jk=4e38b030f65d339e</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026009 - Software Engineer</t>
+          <t>Software Development Engineer (AWS)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>John Deere</t>
+          <t>ALTEN</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Moline, IL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Scala, PostgreSQL, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,67 +4871,67 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e1a444de87fc2c</t>
+          <t>https://www.indeed.com/viewjob?jk=0b4b23734e39ac6c</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer (Onsite)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Colony Brands</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Monroe, WI, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f935defc4a70c87e</t>
+          <t>https://www.indeed.com/viewjob?jk=10b635a4480602f9</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>RNGD</t>
+          <t>BillGO, Inc.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, DynamoDB, Star Schema, ELT, Tableau, GitHub Actions</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,32 +4941,32 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a3ecae4bdb7e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=69713d6be44a4b67</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>MachineMetrics, Inc.</t>
+          <t>Rocket Close</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, RDS, Scala, Kafka, PostgreSQL, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,32 +4976,32 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80173e5fca484063</t>
+          <t>https://www.indeed.com/viewjob?jk=9fce91f5c39bd4ed</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Microsoft Modern Work Consultant</t>
+          <t>NetApp Emerging Talent - Software Engineer (Cloud Storage)</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,32 +5011,32 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11d034c0b8905492</t>
+          <t>https://www.indeed.com/viewjob?jk=4b72bdc255bbf6f8</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer (Information Technology Subject Matter Expert)</t>
+          <t>Senior Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>State of Connecticut</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Databricks Lakehouse, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,32 +5046,32 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d267e859d5950f5a</t>
+          <t>https://www.indeed.com/viewjob?jk=a6e81f16ad428334</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Software Developer - Information Governance</t>
+          <t>2026009 - Software Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>John Deere</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Moline, IL, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Scala, PostgreSQL, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65cd9651c7e25101</t>
+          <t>https://www.indeed.com/viewjob?jk=45e1a444de87fc2c</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Cloud Data Engineer (Onsite)</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Colony Brands</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Monroe, WI, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f710f05a18efb3e1</t>
+          <t>https://www.indeed.com/viewjob?jk=f935defc4a70c87e</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>RNGD</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
+          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ad148596751872e</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a3ecae4bdb7e4b</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>MachineMetrics, Inc.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, RDS, Scala, Kafka, PostgreSQL, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085872f73883326c</t>
+          <t>https://www.indeed.com/viewjob?jk=80173e5fca484063</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Microsoft Modern Work Consultant</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa79af047e73dc3e</t>
+          <t>https://www.indeed.com/viewjob?jk=11d034c0b8905492</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior DevOps Cloud Engineer (Information Technology Subject Matter Expert)</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>State of Connecticut</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34987f860a590c53</t>
+          <t>https://www.indeed.com/viewjob?jk=d267e859d5950f5a</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>Software Developer - Information Governance</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,29 +5281,29 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4296ca379ce33eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=65cd9651c7e25101</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Angular / JAVA Full Stack Engineer</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcfd60088aef43d3</t>
+          <t>https://www.indeed.com/viewjob?jk=f710f05a18efb3e1</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Data Engineer: $150-160,000, MN Based, Hybrid - 2 Days in Office</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>GovDocs</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, MongoDB, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8acefc49a07f2d39</t>
+          <t>https://www.indeed.com/viewjob?jk=6ad148596751872e</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AI Enablement)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48c5c7e7de56c6fb</t>
+          <t>https://www.indeed.com/viewjob?jk=085872f73883326c</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Java)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Decatur, GA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=338db949c564e874</t>
+          <t>https://www.indeed.com/viewjob?jk=fa79af047e73dc3e</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb067c7ee9c6e671</t>
+          <t>https://www.indeed.com/viewjob?jk=34987f860a590c53</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4543a914df9789</t>
+          <t>https://www.indeed.com/viewjob?jk=4296ca379ce33eb3</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Data Product Owner</t>
+          <t>Angular / JAVA Full Stack Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Gallagher</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Rolling Meadows, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, Azure, GCP, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33815bde90512ef</t>
+          <t>https://www.indeed.com/viewjob?jk=fcfd60088aef43d3</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Geospatial Solutions Architect</t>
+          <t>Senior Data Engineer: $150-160,000, MN Based, Hybrid - 2 Days in Office</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>S R International Inc</t>
+          <t>GovDocs</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, MongoDB, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4968b1c75b8ea91</t>
+          <t>https://www.indeed.com/viewjob?jk=8acefc49a07f2d39</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Senior Geospatial Solutions Architect</t>
+          <t>Senior Software Engineer (AI Enablement)</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f71870dc0f7bc53</t>
+          <t>https://www.indeed.com/viewjob?jk=48c5c7e7de56c6fb</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior Software Engineer ( Java)</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CleanSlate Technology Group</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Decatur, GA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,15 +5631,225 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=338db949c564e874</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Salesforce Data Cloud Architect</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>EPAM Systems</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb067c7ee9c6e671</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Salesforce Data Cloud Architect</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>EPAM Systems</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de4543a914df9789</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Senior Geospatial Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>S R International Inc</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4968b1c75b8ea91</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Senior Geospatial Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>American business solutions inc</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f71870dc0f7bc53</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Data Product Owner</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Gallagher</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Rolling Meadows, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a33815bde90512ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Cloud Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>CleanSlate Technology Group</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Carmel, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
           <t>AWS, Azure, Scala, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation, Jenkins, Git</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
+      <c r="F155" t="inlineStr">
         <is>
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
+      <c r="G155" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=478788964e131867</t>
         </is>

--- a/results/job_matches_2026-04-15.xlsx
+++ b/results/job_matches_2026-04-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G155"/>
+  <dimension ref="A1:G149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,52 +573,52 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Remote)</t>
+          <t>AI/ML Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Universal Background Screening</t>
+          <t>Marvell Technology</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c305c75d9c817c14</t>
+          <t>https://www.indeed.com/viewjob?jk=db6fecac436797a9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI/ML Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Marvell Technology</t>
+          <t>AmeriLife</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Kafka</t>
+          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,129 +636,129 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db6fecac436797a9</t>
+          <t>https://www.indeed.com/viewjob?jk=d10f6b2d0d1b341d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cons - TC - AI and Data - Enterp Data - Data Eng and Arch - Data Eng - Mgr - MP - 1688246</t>
+          <t>Software Engineer III - AWS Glue</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Google Cloud Platform, GCP, Hadoop, HDFS, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdf2a5f30bbe80a</t>
+          <t>https://www.indeed.com/viewjob?jk=5f1496d3a0b45451</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Engineer 2026 - US,UK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AmeriLife</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d10f6b2d0d1b341d</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d01fdc4061dd2a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer 2026 - US,UK</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d01fdc4061dd2a</t>
+          <t>https://www.indeed.com/viewjob?jk=5f9a309f4efa98f8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Information Technology - BI Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>TCC Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Fishers, IN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Spark, Scala, Oracle, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f9a309f4efa98f8</t>
+          <t>https://www.indeed.com/viewjob?jk=ca19ad92abde46c9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Information Technology - BI Developer</t>
+          <t>Data Warehouse Analyst Seniors: Cloud Engineering</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TCC Verizon Authorized Retailer</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fishers, IN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca19ad92abde46c9</t>
+          <t>https://www.indeed.com/viewjob?jk=d87aa04a7733264b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Warehouse Analyst Seniors: Cloud Engineering</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, ETL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d87aa04a7733264b</t>
+          <t>https://www.indeed.com/viewjob?jk=574e10b9b787dc54</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=574e10b9b787dc54</t>
+          <t>https://www.indeed.com/viewjob?jk=ac615cac5200efc9</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac615cac5200efc9</t>
+          <t>https://www.indeed.com/viewjob?jk=8a7de03320b3d487</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a7de03320b3d487</t>
+          <t>https://www.indeed.com/viewjob?jk=df1418000450ecdb</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df1418000450ecdb</t>
+          <t>https://www.indeed.com/viewjob?jk=6df75aab0012c038</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Full Stack AI Engineer</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Southern Company</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6df75aab0012c038</t>
+          <t>https://www.indeed.com/viewjob?jk=3be194d530456f66</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Java Developer (Hybrid- Flexible Options)</t>
+          <t>Operations Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>Stifel</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Edgewood, NY, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25ccf7fa8d4a5b10</t>
+          <t>https://www.indeed.com/viewjob?jk=d061193f264addea</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Southern Company</t>
+          <t>Ignite Insurance Systems</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be194d530456f66</t>
+          <t>https://www.indeed.com/viewjob?jk=560d14506d8aa36b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Operations Engineer (Cloud)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Stifel</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d061193f264addea</t>
+          <t>https://www.indeed.com/viewjob?jk=e99b4467c3c6aa55</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Architect I</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ignite Insurance Systems</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Azure, Data Factory, Databricks</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=560d14506d8aa36b</t>
+          <t>https://www.indeed.com/viewjob?jk=c6d97da40a8da560</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Azure, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,102 +1196,102 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99b4467c3c6aa55</t>
+          <t>https://www.indeed.com/viewjob?jk=fcd17ae9e035b9a9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Architect I</t>
+          <t>Database and Dashboard Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Azure, Data Factory, Databricks</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6d97da40a8da560</t>
+          <t>https://www.indeed.com/viewjob?jk=fee5a2d73882379c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Azure, GCP, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcd17ae9e035b9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=ead7a3e6b1951593</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Express</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, BigQuery, Scala, Oracle, MongoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27ee634b56d5a4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=ae18e6a8860be459</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Database and Dashboard Developer</t>
+          <t>Snowflake Data Engineer (contract)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fee5a2d73882379c</t>
+          <t>https://www.indeed.com/viewjob?jk=23956751504b8384</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Senior Data &amp; AI Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>Olson Kundig</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ead7a3e6b1951593</t>
+          <t>https://www.indeed.com/viewjob?jk=d831e0d8e2c5553f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Solution Architect, Enterprise</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,29 +1396,29 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae18e6a8860be459</t>
+          <t>https://www.indeed.com/viewjob?jk=3f33106731db1775</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer (contract)</t>
+          <t>Solution Architect, Enterprise</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23956751504b8384</t>
+          <t>https://www.indeed.com/viewjob?jk=90d356ab99a57489</t>
         </is>
       </c>
     </row>
@@ -1476,14 +1476,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f33106731db1775</t>
+          <t>https://www.indeed.com/viewjob?jk=15664632526fabdb</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Solution Architect, Enterprise</t>
+          <t>Senior Solution Architect, Enterprise</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90d356ab99a57489</t>
+          <t>https://www.indeed.com/viewjob?jk=507830f63a6d47c9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Solution Architect, Enterprise</t>
+          <t>Senior Solution Architect, Enterprise</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15664632526fabdb</t>
+          <t>https://www.indeed.com/viewjob?jk=98d7971656e73b43</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Solution Architect, Enterprise</t>
+          <t>Data &amp; AI Governance Officer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Vantage Bank Texas</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,77 +1571,77 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, Glue, S3, RDS, Azure, Data Factory, Databricks, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=507830f63a6d47c9</t>
+          <t>https://www.indeed.com/viewjob?jk=5c469b183725fde1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Solution Architect, Enterprise</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98d7971656e73b43</t>
+          <t>https://www.indeed.com/viewjob?jk=93144249a4967543</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Olson Kundig</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Robstown, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d831e0d8e2c5553f</t>
+          <t>https://www.indeed.com/viewjob?jk=072e6e4e8e025141</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data &amp; AI Governance Officer</t>
+          <t>Mid-Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Vantage Bank Texas</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Data Factory, Databricks, ELT, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c469b183725fde1</t>
+          <t>https://www.indeed.com/viewjob?jk=c717630a440c614c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Robstown, TX, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=072e6e4e8e025141</t>
+          <t>https://www.indeed.com/viewjob?jk=15a32bf71ba33ffa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Mid-Level Data Engineer, Global</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c717630a440c614c</t>
+          <t>https://www.indeed.com/viewjob?jk=4d3db28285f41c46</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15a32bf71ba33ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=3989068a8778fb79</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d3db28285f41c46</t>
+          <t>https://www.indeed.com/viewjob?jk=5c70a1cb7dff6fb6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3989068a8778fb79</t>
+          <t>https://www.indeed.com/viewjob?jk=3de9b476cdbf12e9</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Research Engineer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Bryan, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c70a1cb7dff6fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=09b3207da19db4ee</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Research Engineer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bryan, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de9b476cdbf12e9</t>
+          <t>https://www.indeed.com/viewjob?jk=bb85a1b8d1928fd4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Research Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bryan, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b3207da19db4ee</t>
+          <t>https://www.indeed.com/viewjob?jk=9f177704478aadbe</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Research Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>Frida</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bryan, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
+          <t>AWS, IAM, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb85a1b8d1928fd4</t>
+          <t>https://www.indeed.com/viewjob?jk=8900daeea8c64c35</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>ArcGIS Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, API Gateway, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f177704478aadbe</t>
+          <t>https://www.indeed.com/viewjob?jk=1186a0273eb12d27</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Sr. ETL/Python Developer)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Frida</t>
+          <t>RCR Technology</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8900daeea8c64c35</t>
+          <t>https://www.indeed.com/viewjob?jk=4527effc81797bda</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ArcGIS Software Engineer</t>
+          <t>Data Support Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Illumen Group</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Stafford, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, Athena, S3, Databricks, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,19 +2106,19 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1186a0273eb12d27</t>
+          <t>https://www.indeed.com/viewjob?jk=92cd661cf5a17182</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Sr. ETL/Python Developer)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RCR Technology</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4527effc81797bda</t>
+          <t>https://www.indeed.com/viewjob?jk=8a0467416d94bb26</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Support Engineer</t>
+          <t>Software Development Engineer II (C#/.NET, Azure)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Illumen Group</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Stafford, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, Databricks, Spark, PySpark, Scala, Oracle</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92cd661cf5a17182</t>
+          <t>https://www.indeed.com/viewjob?jk=b6c902472d880e18</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Sr Mgr Data Engineering</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AllCloud</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a0467416d94bb26</t>
+          <t>https://www.indeed.com/viewjob?jk=03e707506ab6122a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Development Engineer II (C#/.NET, Azure)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Banner Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6c902472d880e18</t>
+          <t>https://www.indeed.com/viewjob?jk=c8d9928392bc7529</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr Mgr Data Engineering</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e707506ab6122a</t>
+          <t>https://www.indeed.com/viewjob?jk=1a527d30b5c00d7d</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8d9928392bc7529</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1bf292f1b43ebd</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Cloud Automation Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vantage Bank Texas</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a527d30b5c00d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f9ce6ba5f081b9</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Banner Health</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1bf292f1b43ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=62c75d5f8fbde70d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cloud Automation Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Vantage Bank Texas</t>
+          <t>Medeloop</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f9ce6ba5f081b9</t>
+          <t>https://www.indeed.com/viewjob?jk=a81ed0b08e8f07f7</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>Beacon, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62c75d5f8fbde70d</t>
+          <t>https://www.indeed.com/viewjob?jk=81ac0513866a1f53</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Backend Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Medeloop</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a81ed0b08e8f07f7</t>
+          <t>https://www.indeed.com/viewjob?jk=ae2342b890625b11</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Beacon, NY, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81ac0513866a1f53</t>
+          <t>https://www.indeed.com/viewjob?jk=30ff91e3d3905a73</t>
         </is>
       </c>
     </row>
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ff91e3d3905a73</t>
+          <t>https://www.indeed.com/viewjob?jk=17cbee15ac5e5d6a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cbee15ac5e5d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=bf17dcf23ea3201f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>RJW Logistics</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf17dcf23ea3201f</t>
+          <t>https://www.indeed.com/viewjob?jk=ef58fd9ad5dd15ff</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Backend Engineer II</t>
+          <t>Data Engineer - Dallas, TX</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae2342b890625b11</t>
+          <t>https://www.indeed.com/viewjob?jk=865a46cfbc7cc3f4</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RJW Logistics</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef58fd9ad5dd15ff</t>
+          <t>https://www.indeed.com/viewjob?jk=766ed066e436eb0c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer - Dallas, TX</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865a46cfbc7cc3f4</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c080bdfd0f5497</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766ed066e436eb0c</t>
+          <t>https://www.indeed.com/viewjob?jk=01aefad23a0eebfc</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c080bdfd0f5497</t>
+          <t>https://www.indeed.com/viewjob?jk=b79af965edb52688</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01aefad23a0eebfc</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe099d836f48656</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b79af965edb52688</t>
+          <t>https://www.indeed.com/viewjob?jk=8756dcda438f6959</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe099d836f48656</t>
+          <t>https://www.indeed.com/viewjob?jk=3c70b98cc7f980bc</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8756dcda438f6959</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa8671f82044c5a</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c70b98cc7f980bc</t>
+          <t>https://www.indeed.com/viewjob?jk=9bddaca0e62ee366</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa8671f82044c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=4177c81ac5d66b2d</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bddaca0e62ee366</t>
+          <t>https://www.indeed.com/viewjob?jk=02c32fad4b2ac01d</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4177c81ac5d66b2d</t>
+          <t>https://www.indeed.com/viewjob?jk=964bc462945e695c</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02c32fad4b2ac01d</t>
+          <t>https://www.indeed.com/viewjob?jk=7beb81f1fe47bc19</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=964bc462945e695c</t>
+          <t>https://www.indeed.com/viewjob?jk=a3c6d71a96ee8e3e</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7beb81f1fe47bc19</t>
+          <t>https://www.indeed.com/viewjob?jk=85e48e8aee6232ce</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3c6d71a96ee8e3e</t>
+          <t>https://www.indeed.com/viewjob?jk=26cc56905b519e4a</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e48e8aee6232ce</t>
+          <t>https://www.indeed.com/viewjob?jk=416163a4caa0a101</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26cc56905b519e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=6b314b34d858c384</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=416163a4caa0a101</t>
+          <t>https://www.indeed.com/viewjob?jk=3d26c232b74cd8f7</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b314b34d858c384</t>
+          <t>https://www.indeed.com/viewjob?jk=0461589d526a9a5c</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d26c232b74cd8f7</t>
+          <t>https://www.indeed.com/viewjob?jk=a01db0a34a1698ca</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0461589d526a9a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=1d2979409c83f2a4</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a01db0a34a1698ca</t>
+          <t>https://www.indeed.com/viewjob?jk=19292a33d87f477b</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d2979409c83f2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=1c45b67d1782f41c</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19292a33d87f477b</t>
+          <t>https://www.indeed.com/viewjob?jk=28e0fdb2d1d8365c</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c45b67d1782f41c</t>
+          <t>https://www.indeed.com/viewjob?jk=50082798bb6a8951</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e0fdb2d1d8365c</t>
+          <t>https://www.indeed.com/viewjob?jk=ff4b550996831857</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50082798bb6a8951</t>
+          <t>https://www.indeed.com/viewjob?jk=e7a140e56c36bd8e</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff4b550996831857</t>
+          <t>https://www.indeed.com/viewjob?jk=7177f3e2822442b8</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7a140e56c36bd8e</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f786bfc01c412f</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7177f3e2822442b8</t>
+          <t>https://www.indeed.com/viewjob?jk=c31b397857f539a8</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f786bfc01c412f</t>
+          <t>https://www.indeed.com/viewjob?jk=df2a59301082a549</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c31b397857f539a8</t>
+          <t>https://www.indeed.com/viewjob?jk=abd442131644c2ae</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2a59301082a549</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac49610be5f7c22</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd442131644c2ae</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd327a6115535e1</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac49610be5f7c22</t>
+          <t>https://www.indeed.com/viewjob?jk=6fdf53b11b630cb7</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd327a6115535e1</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7ce02753b98a7f</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fdf53b11b630cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=48e68a3d2a669f96</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7ce02753b98a7f</t>
+          <t>https://www.indeed.com/viewjob?jk=715a8a81ec1663c0</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48e68a3d2a669f96</t>
+          <t>https://www.indeed.com/viewjob?jk=8c61b7a4534477b1</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=715a8a81ec1663c0</t>
+          <t>https://www.indeed.com/viewjob?jk=714987b40a626f2c</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c61b7a4534477b1</t>
+          <t>https://www.indeed.com/viewjob?jk=bc2483f2dc10aa24</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=714987b40a626f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=41f3867fb9d5fca1</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc2483f2dc10aa24</t>
+          <t>https://www.indeed.com/viewjob?jk=e14441426c0e5912</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f3867fb9d5fca1</t>
+          <t>https://www.indeed.com/viewjob?jk=de87959267d1c1a1</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e14441426c0e5912</t>
+          <t>https://www.indeed.com/viewjob?jk=157307b309906617</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de87959267d1c1a1</t>
+          <t>https://www.indeed.com/viewjob?jk=fd2a0badba0820e7</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157307b309906617</t>
+          <t>https://www.indeed.com/viewjob?jk=3a1077e0bf1888ba</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd2a0badba0820e7</t>
+          <t>https://www.indeed.com/viewjob?jk=8c0316b1d2e51b16</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a1077e0bf1888ba</t>
+          <t>https://www.indeed.com/viewjob?jk=91b58529dba10c91</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c0316b1d2e51b16</t>
+          <t>https://www.indeed.com/viewjob?jk=bbe26208741cfd88</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91b58529dba10c91</t>
+          <t>https://www.indeed.com/viewjob?jk=a4deeb487a12f72a</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Engineer II, AWS Connect</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbe26208741cfd88</t>
+          <t>https://www.indeed.com/viewjob?jk=16d1c8d1b8c5a8bd</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>adonis</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4deeb487a12f72a</t>
+          <t>https://www.indeed.com/viewjob?jk=e5621c4e542d4639</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Engineer II, AWS Connect</t>
+          <t>NetApp Emerging Talent - Entry Level Software Engineer (Cloud Storage)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d1c8d1b8c5a8bd</t>
+          <t>https://www.indeed.com/viewjob?jk=7e07865da969c4a3</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Sr. Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>adonis</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Snowflake, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5621c4e542d4639</t>
+          <t>https://www.indeed.com/viewjob?jk=745ab30cde1846a7</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD, Git</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38299c9de7d6d6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=7a27a8acf3bc1bc8</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>NetApp Emerging Talent - Entry Level Software Engineer (Cloud Storage)</t>
+          <t>Full-Stack Developer (AWS, TS, React)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e07865da969c4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=cc3a148287061e68</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Hybrid</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>BillGO, Inc.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Snowflake, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, DynamoDB, Star Schema, ELT, Tableau, GitHub Actions</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=745ab30cde1846a7</t>
+          <t>https://www.indeed.com/viewjob?jk=69713d6be44a4b67</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
+          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a27a8acf3bc1bc8</t>
+          <t>https://www.indeed.com/viewjob?jk=10b635a4480602f9</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Full-Stack Developer (AWS, TS, React)</t>
+          <t>Senior Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Rocket Close</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc3a148287061e68</t>
+          <t>https://www.indeed.com/viewjob?jk=9fce91f5c39bd4ed</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Engineer III, Machine Learning Software</t>
+          <t>NetApp Emerging Talent - Software Engineer (Cloud Storage)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, S3, Spark, Scala, Snowflake, ETL, CI/CD, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e38b030f65d339e</t>
+          <t>https://www.indeed.com/viewjob?jk=4b72bdc255bbf6f8</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Software Development Engineer (AWS)</t>
+          <t>Senior Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ALTEN</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka</t>
+          <t>RDS, Azure, Databricks, Scala, Databricks Lakehouse, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b4b23734e39ac6c</t>
+          <t>https://www.indeed.com/viewjob?jk=a6e81f16ad428334</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>2026009 - Software Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>John Deere</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Moline, IL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Scala, PostgreSQL, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b635a4480602f9</t>
+          <t>https://www.indeed.com/viewjob?jk=45e1a444de87fc2c</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Engineer III, Machine Learning Software</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>BillGO, Inc.</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, DynamoDB, Star Schema, ELT, Tableau, GitHub Actions</t>
+          <t>AWS, S3, Spark, Scala, Snowflake, ETL, CI/CD, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,32 +4941,32 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69713d6be44a4b67</t>
+          <t>https://www.indeed.com/viewjob?jk=4e38b030f65d339e</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform</t>
+          <t>Cloud Data Engineer (Onsite)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Rocket Close</t>
+          <t>Colony Brands</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Monroe, WI, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, RDS, Azure, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,32 +4976,32 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fce91f5c39bd4ed</t>
+          <t>https://www.indeed.com/viewjob?jk=f935defc4a70c87e</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>NetApp Emerging Talent - Software Engineer (Cloud Storage)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>RNGD</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,19 +5011,19 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b72bdc255bbf6f8</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a3ecae4bdb7e4b</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>MachineMetrics, Inc.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5032,11 +5032,11 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Databricks Lakehouse, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, RDS, Scala, Kafka, PostgreSQL, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,32 +5046,32 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6e81f16ad428334</t>
+          <t>https://www.indeed.com/viewjob?jk=80173e5fca484063</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026009 - Software Engineer</t>
+          <t>Microsoft Modern Work Consultant</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>John Deere</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Moline, IL, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Scala, PostgreSQL, Docker, Kubernetes, SonarQube</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e1a444de87fc2c</t>
+          <t>https://www.indeed.com/viewjob?jk=11d034c0b8905492</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer (Onsite)</t>
+          <t>Software Developer - Information Governance</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Colony Brands</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Monroe, WI, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f935defc4a70c87e</t>
+          <t>https://www.indeed.com/viewjob?jk=65cd9651c7e25101</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>RNGD</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a3ecae4bdb7e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=4296ca379ce33eb3</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>MachineMetrics, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, RDS, Scala, Kafka, PostgreSQL, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80173e5fca484063</t>
+          <t>https://www.indeed.com/viewjob?jk=f710f05a18efb3e1</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Microsoft Modern Work Consultant</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11d034c0b8905492</t>
+          <t>https://www.indeed.com/viewjob?jk=6ad148596751872e</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer (Information Technology Subject Matter Expert)</t>
+          <t>Angular / JAVA Full Stack Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>State of Connecticut</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d267e859d5950f5a</t>
+          <t>https://www.indeed.com/viewjob?jk=fcfd60088aef43d3</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Software Developer - Information Governance</t>
+          <t>Senior Data Engineer: $150-160,000, MN Based, Hybrid - 2 Days in Office</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>GovDocs</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, MongoDB, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65cd9651c7e25101</t>
+          <t>https://www.indeed.com/viewjob?jk=8acefc49a07f2d39</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Senior Software Engineer (AI Enablement)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f710f05a18efb3e1</t>
+          <t>https://www.indeed.com/viewjob?jk=48c5c7e7de56c6fb</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Senior Software Engineer ( Java)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Decatur, GA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ad148596751872e</t>
+          <t>https://www.indeed.com/viewjob?jk=338db949c564e874</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>EPAM Systems</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085872f73883326c</t>
+          <t>https://www.indeed.com/viewjob?jk=eb067c7ee9c6e671</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>EPAM Systems</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa79af047e73dc3e</t>
+          <t>https://www.indeed.com/viewjob?jk=de4543a914df9789</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Geospatial Solutions Architect</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>S R International Inc</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34987f860a590c53</t>
+          <t>https://www.indeed.com/viewjob?jk=b4968b1c75b8ea91</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>Senior Geospatial Solutions Architect</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4296ca379ce33eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=5f71870dc0f7bc53</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Angular / JAVA Full Stack Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcfd60088aef43d3</t>
+          <t>https://www.indeed.com/viewjob?jk=085872f73883326c</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Data Engineer: $150-160,000, MN Based, Hybrid - 2 Days in Office</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>GovDocs</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, MongoDB, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8acefc49a07f2d39</t>
+          <t>https://www.indeed.com/viewjob?jk=fa79af047e73dc3e</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AI Enablement)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48c5c7e7de56c6fb</t>
+          <t>https://www.indeed.com/viewjob?jk=34987f860a590c53</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Java)</t>
+          <t>Data Product Owner</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>Gallagher</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Decatur, GA, US USA</t>
+          <t>Rolling Meadows, IL, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,217 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=338db949c564e874</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Salesforce Data Cloud Architect</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>EPAM Systems</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb067c7ee9c6e671</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Salesforce Data Cloud Architect</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>EPAM Systems</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=de4543a914df9789</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Senior Geospatial Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>S R International Inc</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Harrisburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b4968b1c75b8ea91</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Senior Geospatial Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>American business solutions inc</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Harrisburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5f71870dc0f7bc53</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Data Product Owner</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Gallagher</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Rolling Meadows, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=a33815bde90512ef</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Cloud Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>CleanSlate Technology Group</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Carmel, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=478788964e131867</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-15.xlsx
+++ b/results/job_matches_2026-04-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G149"/>
+  <dimension ref="A1:G147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ignite Insurance Systems</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=560d14506d8aa36b</t>
+          <t>https://www.indeed.com/viewjob?jk=f99034f0e149e6e6</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>Ignite Insurance Systems</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99b4467c3c6aa55</t>
+          <t>https://www.indeed.com/viewjob?jk=560d14506d8aa36b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Architect I</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Azure, Data Factory, Databricks</t>
+          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6d97da40a8da560</t>
+          <t>https://www.indeed.com/viewjob?jk=e99b4467c3c6aa55</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Architect I</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,69 +1186,69 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Azure, GCP, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Azure, Data Factory, Databricks</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcd17ae9e035b9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=c6d97da40a8da560</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Database and Dashboard Developer</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Oracle</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Azure, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fee5a2d73882379c</t>
+          <t>https://www.indeed.com/viewjob?jk=fcd17ae9e035b9a9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Database and Dashboard Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ead7a3e6b1951593</t>
+          <t>https://www.indeed.com/viewjob?jk=fee5a2d73882379c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae18e6a8860be459</t>
+          <t>https://www.indeed.com/viewjob?jk=ead7a3e6b1951593</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer (contract)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Oracle, PostgreSQL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23956751504b8384</t>
+          <t>https://www.indeed.com/viewjob?jk=f193a5a41b80d59d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Developer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Olson Kundig</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,19 +1371,19 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d831e0d8e2c5553f</t>
+          <t>https://www.indeed.com/viewjob?jk=ae18e6a8860be459</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Solution Architect, Enterprise</t>
+          <t>Snowflake Data Engineer (contract)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f33106731db1775</t>
+          <t>https://www.indeed.com/viewjob?jk=23956751504b8384</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Solution Architect, Enterprise</t>
+          <t>Senior Data &amp; AI Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Olson Kundig</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90d356ab99a57489</t>
+          <t>https://www.indeed.com/viewjob?jk=d831e0d8e2c5553f</t>
         </is>
       </c>
     </row>
@@ -1476,14 +1476,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15664632526fabdb</t>
+          <t>https://www.indeed.com/viewjob?jk=3f33106731db1775</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Solution Architect, Enterprise</t>
+          <t>Solution Architect, Enterprise</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=507830f63a6d47c9</t>
+          <t>https://www.indeed.com/viewjob?jk=90d356ab99a57489</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Solution Architect, Enterprise</t>
+          <t>Solution Architect, Enterprise</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98d7971656e73b43</t>
+          <t>https://www.indeed.com/viewjob?jk=15664632526fabdb</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data &amp; AI Governance Officer</t>
+          <t>Senior Solution Architect, Enterprise</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Vantage Bank Texas</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,52 +1571,52 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Data Factory, Databricks, ELT, Power BI, Tableau</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c469b183725fde1</t>
+          <t>https://www.indeed.com/viewjob?jk=507830f63a6d47c9</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Solution Architect, Enterprise</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93144249a4967543</t>
+          <t>https://www.indeed.com/viewjob?jk=98d7971656e73b43</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Robstown, TX, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=072e6e4e8e025141</t>
+          <t>https://www.indeed.com/viewjob?jk=93144249a4967543</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Mid-Level Data Engineer, Global</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Robstown, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c717630a440c614c</t>
+          <t>https://www.indeed.com/viewjob?jk=072e6e4e8e025141</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Mid-Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15a32bf71ba33ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=c717630a440c614c</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d3db28285f41c46</t>
+          <t>https://www.indeed.com/viewjob?jk=15a32bf71ba33ffa</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3989068a8778fb79</t>
+          <t>https://www.indeed.com/viewjob?jk=4d3db28285f41c46</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c70a1cb7dff6fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=3989068a8778fb79</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de9b476cdbf12e9</t>
+          <t>https://www.indeed.com/viewjob?jk=5c70a1cb7dff6fb6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Research Engineer II</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bryan, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b3207da19db4ee</t>
+          <t>https://www.indeed.com/viewjob?jk=3de9b476cdbf12e9</t>
         </is>
       </c>
     </row>
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb85a1b8d1928fd4</t>
+          <t>https://www.indeed.com/viewjob?jk=09b3207da19db4ee</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Research Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Bryan, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f177704478aadbe</t>
+          <t>https://www.indeed.com/viewjob?jk=bb85a1b8d1928fd4</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Frida</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8900daeea8c64c35</t>
+          <t>https://www.indeed.com/viewjob?jk=9f177704478aadbe</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ArcGIS Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Frida</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1186a0273eb12d27</t>
+          <t>https://www.indeed.com/viewjob?jk=8900daeea8c64c35</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Sr. ETL/Python Developer)</t>
+          <t>ArcGIS Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RCR Technology</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4527effc81797bda</t>
+          <t>https://www.indeed.com/viewjob?jk=1186a0273eb12d27</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Support Engineer</t>
+          <t>Senior Data Engineer (Sr. ETL/Python Developer)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Illumen Group</t>
+          <t>RCR Technology</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Stafford, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, Databricks, Spark, PySpark, Scala, Oracle</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92cd661cf5a17182</t>
+          <t>https://www.indeed.com/viewjob?jk=4527effc81797bda</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Support Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AllCloud</t>
+          <t>Illumen Group</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Stafford, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, Glue, Redshift, Athena, S3, Databricks, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a0467416d94bb26</t>
+          <t>https://www.indeed.com/viewjob?jk=92cd661cf5a17182</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Development Engineer II (C#/.NET, Azure)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6c902472d880e18</t>
+          <t>https://www.indeed.com/viewjob?jk=8a0467416d94bb26</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Mgr Data Engineering</t>
+          <t>Software Development Engineer II (C#/.NET, Azure)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e707506ab6122a</t>
+          <t>https://www.indeed.com/viewjob?jk=b6c902472d880e18</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Mgr Data Engineering</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Banner Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8d9928392bc7529</t>
+          <t>https://www.indeed.com/viewjob?jk=03e707506ab6122a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Banner Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a527d30b5c00d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=c8d9928392bc7529</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Banner Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1bf292f1b43ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=1a527d30b5c00d7d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud Automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Vantage Bank Texas</t>
+          <t>Banner Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f9ce6ba5f081b9</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1bf292f1b43ebd</t>
         </is>
       </c>
     </row>
@@ -5368,17 +5368,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Senior Geospatial Solutions Architect</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>S R International Inc</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb067c7ee9c6e671</t>
+          <t>https://www.indeed.com/viewjob?jk=b4968b1c75b8ea91</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Senior Geospatial Solutions Architect</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4543a914df9789</t>
+          <t>https://www.indeed.com/viewjob?jk=5f71870dc0f7bc53</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior Geospatial Solutions Architect</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>S R International Inc</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4968b1c75b8ea91</t>
+          <t>https://www.indeed.com/viewjob?jk=085872f73883326c</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Geospatial Solutions Architect</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f71870dc0f7bc53</t>
+          <t>https://www.indeed.com/viewjob?jk=fa79af047e73dc3e</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085872f73883326c</t>
+          <t>https://www.indeed.com/viewjob?jk=34987f860a590c53</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Data Product Owner</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Gallagher</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Rolling Meadows, IL, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5570,76 +5570,6 @@
         </is>
       </c>
       <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fa79af047e73dc3e</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>CapTech Consulting</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=34987f860a590c53</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Data Product Owner</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Gallagher</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Rolling Meadows, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a33815bde90512ef</t>
         </is>

--- a/results/job_matches_2026-04-15.xlsx
+++ b/results/job_matches_2026-04-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G147"/>
+  <dimension ref="A1:G153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Developer</t>
+          <t>Deal Data Technology &amp; Analytics, Senior Associate</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Olson Kundig</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, GCP, Vertex AI, Scala, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d831e0d8e2c5553f</t>
+          <t>https://www.indeed.com/viewjob?jk=cc13b56a1dadc810</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Solution Architect, Enterprise</t>
+          <t>Deal Data Technology &amp; Analytics, Senior Associate</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, GCP, Vertex AI, Scala, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f33106731db1775</t>
+          <t>https://www.indeed.com/viewjob?jk=42cc0c644ae78852</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Solution Architect, Enterprise</t>
+          <t>Deal Data Technology &amp; Analytics, Senior Associate</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, GCP, Vertex AI, Scala, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90d356ab99a57489</t>
+          <t>https://www.indeed.com/viewjob?jk=46d19923987ef429</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Solution Architect, Enterprise</t>
+          <t>Deal Data Technology &amp; Analytics, Senior Associate</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Silicon Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, GCP, Vertex AI, Scala, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15664632526fabdb</t>
+          <t>https://www.indeed.com/viewjob?jk=fa06155bf991d0f8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Solution Architect, Enterprise</t>
+          <t>Deal Data Technology &amp; Analytics, Senior Associate</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,24 +1571,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, GCP, Vertex AI, Scala, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=507830f63a6d47c9</t>
+          <t>https://www.indeed.com/viewjob?jk=22e6ab66fd67032d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Solution Architect, Enterprise</t>
+          <t>Solution Architect, Enterprise</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1616,172 +1616,172 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98d7971656e73b43</t>
+          <t>https://www.indeed.com/viewjob?jk=3f33106731db1775</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solution Architect, Enterprise</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93144249a4967543</t>
+          <t>https://www.indeed.com/viewjob?jk=90d356ab99a57489</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solution Architect, Enterprise</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Robstown, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=072e6e4e8e025141</t>
+          <t>https://www.indeed.com/viewjob?jk=15664632526fabdb</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Mid-Level Data Engineer, Global</t>
+          <t>Senior Solution Architect, Enterprise</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c717630a440c614c</t>
+          <t>https://www.indeed.com/viewjob?jk=507830f63a6d47c9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Senior Solution Architect, Enterprise</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15a32bf71ba33ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=98d7971656e73b43</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Senior Data &amp; AI Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Olson Kundig</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d3db28285f41c46</t>
+          <t>https://www.indeed.com/viewjob?jk=d831e0d8e2c5553f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>AI Intern</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, dbt, MLflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3989068a8778fb79</t>
+          <t>https://www.indeed.com/viewjob?jk=7bea47ac5f13bd1f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c70a1cb7dff6fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=93144249a4967543</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Robstown, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de9b476cdbf12e9</t>
+          <t>https://www.indeed.com/viewjob?jk=072e6e4e8e025141</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Research Engineer II</t>
+          <t>Mid-Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bryan, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b3207da19db4ee</t>
+          <t>https://www.indeed.com/viewjob?jk=c717630a440c614c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Research Engineer II</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bryan, TX, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb85a1b8d1928fd4</t>
+          <t>https://www.indeed.com/viewjob?jk=15a32bf71ba33ffa</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f177704478aadbe</t>
+          <t>https://www.indeed.com/viewjob?jk=4d3db28285f41c46</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Frida</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Star Schema</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8900daeea8c64c35</t>
+          <t>https://www.indeed.com/viewjob?jk=3989068a8778fb79</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ArcGIS Software Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1186a0273eb12d27</t>
+          <t>https://www.indeed.com/viewjob?jk=5c70a1cb7dff6fb6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Sr. ETL/Python Developer)</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RCR Technology</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4527effc81797bda</t>
+          <t>https://www.indeed.com/viewjob?jk=3de9b476cdbf12e9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Support Engineer</t>
+          <t>Research Engineer II</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Illumen Group</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Stafford, VA, US USA</t>
+          <t>Bryan, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, Databricks, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92cd661cf5a17182</t>
+          <t>https://www.indeed.com/viewjob?jk=09b3207da19db4ee</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Research Engineer II</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AllCloud</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bryan, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a0467416d94bb26</t>
+          <t>https://www.indeed.com/viewjob?jk=bb85a1b8d1928fd4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Development Engineer II (C#/.NET, Azure)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6c902472d880e18</t>
+          <t>https://www.indeed.com/viewjob?jk=9f177704478aadbe</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Mgr Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Frida</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, IAM, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e707506ab6122a</t>
+          <t>https://www.indeed.com/viewjob?jk=8900daeea8c64c35</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ArcGIS Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Banner Health</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, API Gateway, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8d9928392bc7529</t>
+          <t>https://www.indeed.com/viewjob?jk=1186a0273eb12d27</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer (Sr. ETL/Python Developer)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RCR Technology</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a527d30b5c00d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=4527effc81797bda</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Support Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Banner Health</t>
+          <t>Illumen Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Stafford, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Glue, Redshift, Athena, S3, Databricks, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1bf292f1b43ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=92cd661cf5a17182</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62c75d5f8fbde70d</t>
+          <t>https://www.indeed.com/viewjob?jk=8a0467416d94bb26</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Development Engineer II (C#/.NET, Azure)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Medeloop</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a81ed0b08e8f07f7</t>
+          <t>https://www.indeed.com/viewjob?jk=b6c902472d880e18</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Mgr Data Engineering</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Beacon, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81ac0513866a1f53</t>
+          <t>https://www.indeed.com/viewjob?jk=03e707506ab6122a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Backend Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>Banner Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae2342b890625b11</t>
+          <t>https://www.indeed.com/viewjob?jk=c8d9928392bc7529</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ff91e3d3905a73</t>
+          <t>https://www.indeed.com/viewjob?jk=1a527d30b5c00d7d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>Banner Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cbee15ac5e5d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1bf292f1b43ebd</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf17dcf23ea3201f</t>
+          <t>https://www.indeed.com/viewjob?jk=62c75d5f8fbde70d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>RJW Logistics</t>
+          <t>Medeloop</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,102 +2631,102 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef58fd9ad5dd15ff</t>
+          <t>https://www.indeed.com/viewjob?jk=a81ed0b08e8f07f7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer - Dallas, TX</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Beacon, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865a46cfbc7cc3f4</t>
+          <t>https://www.indeed.com/viewjob?jk=81ac0513866a1f53</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Backend Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766ed066e436eb0c</t>
+          <t>https://www.indeed.com/viewjob?jk=ae2342b890625b11</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>RJW Logistics</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c080bdfd0f5497</t>
+          <t>https://www.indeed.com/viewjob?jk=ef58fd9ad5dd15ff</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01aefad23a0eebfc</t>
+          <t>https://www.indeed.com/viewjob?jk=30ff91e3d3905a73</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b79af965edb52688</t>
+          <t>https://www.indeed.com/viewjob?jk=17cbee15ac5e5d6a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe099d836f48656</t>
+          <t>https://www.indeed.com/viewjob?jk=bf17dcf23ea3201f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Data Engineer - Dallas, TX</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8756dcda438f6959</t>
+          <t>https://www.indeed.com/viewjob?jk=865a46cfbc7cc3f4</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c70b98cc7f980bc</t>
+          <t>https://www.indeed.com/viewjob?jk=766ed066e436eb0c</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa8671f82044c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c080bdfd0f5497</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bddaca0e62ee366</t>
+          <t>https://www.indeed.com/viewjob?jk=01aefad23a0eebfc</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4177c81ac5d66b2d</t>
+          <t>https://www.indeed.com/viewjob?jk=b79af965edb52688</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02c32fad4b2ac01d</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe099d836f48656</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=964bc462945e695c</t>
+          <t>https://www.indeed.com/viewjob?jk=8756dcda438f6959</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7beb81f1fe47bc19</t>
+          <t>https://www.indeed.com/viewjob?jk=3c70b98cc7f980bc</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3c6d71a96ee8e3e</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa8671f82044c5a</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e48e8aee6232ce</t>
+          <t>https://www.indeed.com/viewjob?jk=9bddaca0e62ee366</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26cc56905b519e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=4177c81ac5d66b2d</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=416163a4caa0a101</t>
+          <t>https://www.indeed.com/viewjob?jk=02c32fad4b2ac01d</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b314b34d858c384</t>
+          <t>https://www.indeed.com/viewjob?jk=964bc462945e695c</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d26c232b74cd8f7</t>
+          <t>https://www.indeed.com/viewjob?jk=7beb81f1fe47bc19</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0461589d526a9a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=a3c6d71a96ee8e3e</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a01db0a34a1698ca</t>
+          <t>https://www.indeed.com/viewjob?jk=85e48e8aee6232ce</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d2979409c83f2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=26cc56905b519e4a</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19292a33d87f477b</t>
+          <t>https://www.indeed.com/viewjob?jk=416163a4caa0a101</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c45b67d1782f41c</t>
+          <t>https://www.indeed.com/viewjob?jk=6b314b34d858c384</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e0fdb2d1d8365c</t>
+          <t>https://www.indeed.com/viewjob?jk=3d26c232b74cd8f7</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50082798bb6a8951</t>
+          <t>https://www.indeed.com/viewjob?jk=0461589d526a9a5c</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff4b550996831857</t>
+          <t>https://www.indeed.com/viewjob?jk=a01db0a34a1698ca</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7a140e56c36bd8e</t>
+          <t>https://www.indeed.com/viewjob?jk=1d2979409c83f2a4</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7177f3e2822442b8</t>
+          <t>https://www.indeed.com/viewjob?jk=19292a33d87f477b</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f786bfc01c412f</t>
+          <t>https://www.indeed.com/viewjob?jk=1c45b67d1782f41c</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c31b397857f539a8</t>
+          <t>https://www.indeed.com/viewjob?jk=28e0fdb2d1d8365c</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2a59301082a549</t>
+          <t>https://www.indeed.com/viewjob?jk=50082798bb6a8951</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd442131644c2ae</t>
+          <t>https://www.indeed.com/viewjob?jk=ff4b550996831857</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac49610be5f7c22</t>
+          <t>https://www.indeed.com/viewjob?jk=e7a140e56c36bd8e</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd327a6115535e1</t>
+          <t>https://www.indeed.com/viewjob?jk=7177f3e2822442b8</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fdf53b11b630cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f786bfc01c412f</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7ce02753b98a7f</t>
+          <t>https://www.indeed.com/viewjob?jk=c31b397857f539a8</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48e68a3d2a669f96</t>
+          <t>https://www.indeed.com/viewjob?jk=df2a59301082a549</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=715a8a81ec1663c0</t>
+          <t>https://www.indeed.com/viewjob?jk=abd442131644c2ae</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c61b7a4534477b1</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac49610be5f7c22</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=714987b40a626f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd327a6115535e1</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc2483f2dc10aa24</t>
+          <t>https://www.indeed.com/viewjob?jk=6fdf53b11b630cb7</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f3867fb9d5fca1</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7ce02753b98a7f</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e14441426c0e5912</t>
+          <t>https://www.indeed.com/viewjob?jk=48e68a3d2a669f96</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de87959267d1c1a1</t>
+          <t>https://www.indeed.com/viewjob?jk=715a8a81ec1663c0</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157307b309906617</t>
+          <t>https://www.indeed.com/viewjob?jk=8c61b7a4534477b1</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd2a0badba0820e7</t>
+          <t>https://www.indeed.com/viewjob?jk=714987b40a626f2c</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a1077e0bf1888ba</t>
+          <t>https://www.indeed.com/viewjob?jk=bc2483f2dc10aa24</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c0316b1d2e51b16</t>
+          <t>https://www.indeed.com/viewjob?jk=41f3867fb9d5fca1</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91b58529dba10c91</t>
+          <t>https://www.indeed.com/viewjob?jk=e14441426c0e5912</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbe26208741cfd88</t>
+          <t>https://www.indeed.com/viewjob?jk=de87959267d1c1a1</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4deeb487a12f72a</t>
+          <t>https://www.indeed.com/viewjob?jk=157307b309906617</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Engineer II, AWS Connect</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d1c8d1b8c5a8bd</t>
+          <t>https://www.indeed.com/viewjob?jk=fd2a0badba0820e7</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>adonis</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5621c4e542d4639</t>
+          <t>https://www.indeed.com/viewjob?jk=3a1077e0bf1888ba</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>NetApp Emerging Talent - Entry Level Software Engineer (Cloud Storage)</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e07865da969c4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=8c0316b1d2e51b16</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Hybrid</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Snowflake, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=745ab30cde1846a7</t>
+          <t>https://www.indeed.com/viewjob?jk=91b58529dba10c91</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a27a8acf3bc1bc8</t>
+          <t>https://www.indeed.com/viewjob?jk=bbe26208741cfd88</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Full-Stack Developer (AWS, TS, React)</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc3a148287061e68</t>
+          <t>https://www.indeed.com/viewjob?jk=a4deeb487a12f72a</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Engineer II, AWS Connect</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>BillGO, Inc.</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, DynamoDB, Star Schema, ELT, Tableau, GitHub Actions</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69713d6be44a4b67</t>
+          <t>https://www.indeed.com/viewjob?jk=16d1c8d1b8c5a8bd</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>adonis</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b635a4480602f9</t>
+          <t>https://www.indeed.com/viewjob?jk=e5621c4e542d4639</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform</t>
+          <t>NetApp Emerging Talent - Entry Level Software Engineer (Cloud Storage)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Rocket Close</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fce91f5c39bd4ed</t>
+          <t>https://www.indeed.com/viewjob?jk=7e07865da969c4a3</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>NetApp Emerging Talent - Software Engineer (Cloud Storage)</t>
+          <t>Sr. Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Snowflake, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b72bdc255bbf6f8</t>
+          <t>https://www.indeed.com/viewjob?jk=745ab30cde1846a7</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Databricks Lakehouse, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6e81f16ad428334</t>
+          <t>https://www.indeed.com/viewjob?jk=7a27a8acf3bc1bc8</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026009 - Software Engineer</t>
+          <t>Full-Stack Developer (AWS, TS, React)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>John Deere</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Moline, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Scala, PostgreSQL, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e1a444de87fc2c</t>
+          <t>https://www.indeed.com/viewjob?jk=cc3a148287061e68</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Engineer III, Machine Learning Software</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>BillGO, Inc.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, S3, Spark, Scala, Snowflake, ETL, CI/CD, Airflow, Git, Python</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, DynamoDB, Star Schema, ELT, Tableau, GitHub Actions</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,67 +4941,67 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e38b030f65d339e</t>
+          <t>https://www.indeed.com/viewjob?jk=69713d6be44a4b67</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer (Onsite)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Colony Brands</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Monroe, WI, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f935defc4a70c87e</t>
+          <t>https://www.indeed.com/viewjob?jk=10b635a4480602f9</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>RNGD</t>
+          <t>Rocket Close</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,32 +5011,32 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a3ecae4bdb7e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=9fce91f5c39bd4ed</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>NetApp Emerging Talent - Software Engineer (Cloud Storage)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>MachineMetrics, Inc.</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, RDS, Scala, Kafka, PostgreSQL, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,32 +5046,32 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80173e5fca484063</t>
+          <t>https://www.indeed.com/viewjob?jk=4b72bdc255bbf6f8</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Microsoft Modern Work Consultant</t>
+          <t>Engineer III, Machine Learning Software</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, S3, Spark, Scala, Snowflake, ETL, CI/CD, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,32 +5081,32 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11d034c0b8905492</t>
+          <t>https://www.indeed.com/viewjob?jk=4e38b030f65d339e</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Software Developer - Information Governance</t>
+          <t>Senior Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
+          <t>RDS, Azure, Databricks, Scala, Databricks Lakehouse, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,59 +5116,59 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65cd9651c7e25101</t>
+          <t>https://www.indeed.com/viewjob?jk=a6e81f16ad428334</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>2026009 - Software Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>John Deere</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Moline, IL, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Scala, PostgreSQL, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4296ca379ce33eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=45e1a444de87fc2c</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Cloud Data Engineer (Onsite)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Colony Brands</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Monroe, WI, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f710f05a18efb3e1</t>
+          <t>https://www.indeed.com/viewjob?jk=f935defc4a70c87e</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>RNGD</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
+          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ad148596751872e</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a3ecae4bdb7e4b</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Angular / JAVA Full Stack Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>MachineMetrics, Inc.</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, RDS, Scala, Kafka, PostgreSQL, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcfd60088aef43d3</t>
+          <t>https://www.indeed.com/viewjob?jk=80173e5fca484063</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Data Engineer: $150-160,000, MN Based, Hybrid - 2 Days in Office</t>
+          <t>Microsoft Modern Work Consultant</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>GovDocs</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, MongoDB, ETL, ELT, Power BI, CI/CD</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8acefc49a07f2d39</t>
+          <t>https://www.indeed.com/viewjob?jk=11d034c0b8905492</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AI Enablement)</t>
+          <t>Software Developer - Information Governance</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
+          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48c5c7e7de56c6fb</t>
+          <t>https://www.indeed.com/viewjob?jk=65cd9651c7e25101</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Java)</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Decatur, GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=338db949c564e874</t>
+          <t>https://www.indeed.com/viewjob?jk=4296ca379ce33eb3</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Geospatial Solutions Architect</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>S R International Inc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4968b1c75b8ea91</t>
+          <t>https://www.indeed.com/viewjob?jk=f710f05a18efb3e1</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Geospatial Solutions Architect</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f71870dc0f7bc53</t>
+          <t>https://www.indeed.com/viewjob?jk=6ad148596751872e</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Angular / JAVA Full Stack Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085872f73883326c</t>
+          <t>https://www.indeed.com/viewjob?jk=fcfd60088aef43d3</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Data Engineer: $150-160,000, MN Based, Hybrid - 2 Days in Office</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>GovDocs</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, MongoDB, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa79af047e73dc3e</t>
+          <t>https://www.indeed.com/viewjob?jk=8acefc49a07f2d39</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Software Engineer (AI Enablement)</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34987f860a590c53</t>
+          <t>https://www.indeed.com/viewjob?jk=48c5c7e7de56c6fb</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Data Product Owner</t>
+          <t>Senior Software Engineer ( Java)</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Gallagher</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Rolling Meadows, IL, US USA</t>
+          <t>Decatur, GA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,17 +5561,227 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=338db949c564e874</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>CapTech Consulting</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=085872f73883326c</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>CapTech Consulting</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa79af047e73dc3e</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>CapTech Consulting</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34987f860a590c53</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Data Product Owner</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Gallagher</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Rolling Meadows, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a33815bde90512ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Senior Geospatial Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>S R International Inc</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4968b1c75b8ea91</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Senior Geospatial Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>American business solutions inc</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f71870dc0f7bc53</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-15.xlsx
+++ b/results/job_matches_2026-04-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G153"/>
+  <dimension ref="A1:G158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TargetPath Solutions</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddaefa90999433c3</t>
+          <t>https://www.indeed.com/viewjob?jk=4478c55d459f6590</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Asset &amp; Wealth Management-Cloud Engineer-Associate-Dallas</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4478c55d459f6590</t>
+          <t>https://www.indeed.com/viewjob?jk=452922c279cc36e9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud Engineer-Associate-Dallas</t>
+          <t>AI/ML Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Marvell Technology</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS, Spark</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=452922c279cc36e9</t>
+          <t>https://www.indeed.com/viewjob?jk=db6fecac436797a9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI/ML Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Marvell Technology</t>
+          <t>AmeriLife</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Kafka</t>
+          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db6fecac436797a9</t>
+          <t>https://www.indeed.com/viewjob?jk=d10f6b2d0d1b341d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer III - AWS Glue</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AmeriLife</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d10f6b2d0d1b341d</t>
+          <t>https://www.indeed.com/viewjob?jk=5f1496d3a0b45451</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS Glue</t>
+          <t>Senior Data Engineer 2026 - US,UK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,69 +661,69 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f1496d3a0b45451</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d01fdc4061dd2a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer 2026 - US,UK</t>
+          <t>Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d01fdc4061dd2a</t>
+          <t>https://www.indeed.com/viewjob?jk=8a711c2fcb36b6cf</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Sr. Data Engineer (ON-SITE)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f9a309f4efa98f8</t>
+          <t>https://www.indeed.com/viewjob?jk=038b96d69cecd888</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Warehouse Analyst Seniors: Cloud Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, ETL, CI/CD</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d87aa04a7733264b</t>
+          <t>https://www.indeed.com/viewjob?jk=cb699a2e3bdbb440</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Full Stack AI Engineer</t>
+          <t>Data Warehouse Analyst Seniors: Cloud Engineering</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=574e10b9b787dc54</t>
+          <t>https://www.indeed.com/viewjob?jk=d87aa04a7733264b</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac615cac5200efc9</t>
+          <t>https://www.indeed.com/viewjob?jk=574e10b9b787dc54</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a7de03320b3d487</t>
+          <t>https://www.indeed.com/viewjob?jk=ac615cac5200efc9</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df1418000450ecdb</t>
+          <t>https://www.indeed.com/viewjob?jk=8a7de03320b3d487</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6df75aab0012c038</t>
+          <t>https://www.indeed.com/viewjob?jk=df1418000450ecdb</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Southern Company</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be194d530456f66</t>
+          <t>https://www.indeed.com/viewjob?jk=6df75aab0012c038</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Operations Engineer (Cloud)</t>
+          <t>Java Developer (Hybrid- Flexible Options)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Stifel</t>
+          <t>Broadridge</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Edgewood, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,59 +1056,59 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d061193f264addea</t>
+          <t>https://www.indeed.com/viewjob?jk=25ccf7fa8d4a5b10</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>bioMerieux</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hazelwood, MO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
+          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Oracle, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f99034f0e149e6e6</t>
+          <t>https://www.indeed.com/viewjob?jk=c2788300e5964c54</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Operations Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ignite Insurance Systems</t>
+          <t>Stifel</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=560d14506d8aa36b</t>
+          <t>https://www.indeed.com/viewjob?jk=d061193f264addea</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99b4467c3c6aa55</t>
+          <t>https://www.indeed.com/viewjob?jk=f99034f0e149e6e6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Architect I</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Ignite Insurance Systems</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Azure, Data Factory, Databricks</t>
+          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6d97da40a8da560</t>
+          <t>https://www.indeed.com/viewjob?jk=560d14506d8aa36b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Azure, GCP, Scala, Kafka</t>
+          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,102 +1231,102 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcd17ae9e035b9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=e99b4467c3c6aa55</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Database and Dashboard Developer</t>
+          <t>Architect I</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Oracle</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Azure, Data Factory, Databricks</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fee5a2d73882379c</t>
+          <t>https://www.indeed.com/viewjob?jk=c6d97da40a8da560</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Azure, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ead7a3e6b1951593</t>
+          <t>https://www.indeed.com/viewjob?jk=fcd17ae9e035b9a9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Express</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, ECS, RDS, GCP, BigQuery, Scala, Oracle, MongoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f193a5a41b80d59d</t>
+          <t>https://www.indeed.com/viewjob?jk=27ee634b56d5a4e3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Database and Dashboard Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae18e6a8860be459</t>
+          <t>https://www.indeed.com/viewjob?jk=fee5a2d73882379c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer (contract)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Oracle, PostgreSQL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23956751504b8384</t>
+          <t>https://www.indeed.com/viewjob?jk=f193a5a41b80d59d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Deal Data Technology &amp; Analytics, Senior Associate</t>
+          <t>Snowflake Data Engineer (contract)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, GCP, Vertex AI, Scala, SQL Server, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc13b56a1dadc810</t>
+          <t>https://www.indeed.com/viewjob?jk=23956751504b8384</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Deal Data Technology &amp; Analytics, Senior Associate</t>
+          <t>Senior Solution Architect, Enterprise</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, GCP, Vertex AI, Scala, SQL Server, dbt</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42cc0c644ae78852</t>
+          <t>https://www.indeed.com/viewjob?jk=507830f63a6d47c9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Deal Data Technology &amp; Analytics, Senior Associate</t>
+          <t>Senior Solution Architect, Enterprise</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, GCP, Vertex AI, Scala, SQL Server, dbt</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46d19923987ef429</t>
+          <t>https://www.indeed.com/viewjob?jk=98d7971656e73b43</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Deal Data Technology &amp; Analytics, Senior Associate</t>
+          <t>Senior Data &amp; AI Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>Olson Kundig</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Silicon Valley, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, GCP, Vertex AI, Scala, SQL Server, dbt</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa06155bf991d0f8</t>
+          <t>https://www.indeed.com/viewjob?jk=d831e0d8e2c5553f</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22e6ab66fd67032d</t>
+          <t>https://www.indeed.com/viewjob?jk=cc13b56a1dadc810</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Solution Architect, Enterprise</t>
+          <t>Deal Data Technology &amp; Analytics, Senior Associate</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, GCP, Vertex AI, Scala, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f33106731db1775</t>
+          <t>https://www.indeed.com/viewjob?jk=42cc0c644ae78852</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Solution Architect, Enterprise</t>
+          <t>Deal Data Technology &amp; Analytics, Senior Associate</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, GCP, Vertex AI, Scala, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90d356ab99a57489</t>
+          <t>https://www.indeed.com/viewjob?jk=46d19923987ef429</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Solution Architect, Enterprise</t>
+          <t>Deal Data Technology &amp; Analytics, Senior Associate</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Silicon Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, GCP, Vertex AI, Scala, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15664632526fabdb</t>
+          <t>https://www.indeed.com/viewjob?jk=fa06155bf991d0f8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Solution Architect, Enterprise</t>
+          <t>Deal Data Technology &amp; Analytics, Senior Associate</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,24 +1711,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, GCP, Vertex AI, Scala, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=507830f63a6d47c9</t>
+          <t>https://www.indeed.com/viewjob?jk=22e6ab66fd67032d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Solution Architect, Enterprise</t>
+          <t>Solution Architect, Enterprise</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98d7971656e73b43</t>
+          <t>https://www.indeed.com/viewjob?jk=3f33106731db1775</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Developer</t>
+          <t>Solution Architect, Enterprise</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Olson Kundig</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,69 +1781,69 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d831e0d8e2c5553f</t>
+          <t>https://www.indeed.com/viewjob?jk=90d356ab99a57489</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Intern</t>
+          <t>Solution Architect, Enterprise</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, dbt, MLflow</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bea47ac5f13bd1f</t>
+          <t>https://www.indeed.com/viewjob?jk=15664632526fabdb</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability Engineer (Cloud Enablement)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Flexera</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93144249a4967543</t>
+          <t>https://www.indeed.com/viewjob?jk=72d1842ef3999b1d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Intern</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Robstown, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, dbt, MLflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=072e6e4e8e025141</t>
+          <t>https://www.indeed.com/viewjob?jk=7bea47ac5f13bd1f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Mid-Level Data Engineer, Global</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c717630a440c614c</t>
+          <t>https://www.indeed.com/viewjob?jk=93144249a4967543</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Robstown, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15a32bf71ba33ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=072e6e4e8e025141</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Mid-Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d3db28285f41c46</t>
+          <t>https://www.indeed.com/viewjob?jk=c717630a440c614c</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3989068a8778fb79</t>
+          <t>https://www.indeed.com/viewjob?jk=15a32bf71ba33ffa</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c70a1cb7dff6fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=4d3db28285f41c46</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de9b476cdbf12e9</t>
+          <t>https://www.indeed.com/viewjob?jk=3989068a8778fb79</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Research Engineer II</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bryan, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b3207da19db4ee</t>
+          <t>https://www.indeed.com/viewjob?jk=5c70a1cb7dff6fb6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Research Engineer II</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bryan, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb85a1b8d1928fd4</t>
+          <t>https://www.indeed.com/viewjob?jk=3de9b476cdbf12e9</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Research Engineer II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Bryan, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f177704478aadbe</t>
+          <t>https://www.indeed.com/viewjob?jk=09b3207da19db4ee</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Research Engineer II</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Frida</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Bryan, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8900daeea8c64c35</t>
+          <t>https://www.indeed.com/viewjob?jk=bb85a1b8d1928fd4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ArcGIS Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1186a0273eb12d27</t>
+          <t>https://www.indeed.com/viewjob?jk=9f177704478aadbe</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Sr. ETL/Python Developer)</t>
+          <t>ArcGIS Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RCR Technology</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4527effc81797bda</t>
+          <t>https://www.indeed.com/viewjob?jk=1186a0273eb12d27</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Support Engineer</t>
+          <t>Senior Data Engineer (Sr. ETL/Python Developer)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Illumen Group</t>
+          <t>RCR Technology</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Stafford, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, Databricks, Spark, PySpark, Scala, Oracle</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92cd661cf5a17182</t>
+          <t>https://www.indeed.com/viewjob?jk=4527effc81797bda</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Support Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>AllCloud</t>
+          <t>Illumen Group</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Stafford, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, Glue, Redshift, Athena, S3, Databricks, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a0467416d94bb26</t>
+          <t>https://www.indeed.com/viewjob?jk=92cd661cf5a17182</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Development Engineer II (C#/.NET, Azure)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6c902472d880e18</t>
+          <t>https://www.indeed.com/viewjob?jk=8a0467416d94bb26</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr Mgr Data Engineering</t>
+          <t>Software Development Engineer II (C#/.NET, Azure)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e707506ab6122a</t>
+          <t>https://www.indeed.com/viewjob?jk=b6c902472d880e18</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Mgr Data Engineering</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Banner Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8d9928392bc7529</t>
+          <t>https://www.indeed.com/viewjob?jk=03e707506ab6122a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Banner Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a527d30b5c00d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=c8d9928392bc7529</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Banner Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1bf292f1b43ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=1a527d30b5c00d7d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>Banner Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62c75d5f8fbde70d</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1bf292f1b43ebd</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Medeloop</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a81ed0b08e8f07f7</t>
+          <t>https://www.indeed.com/viewjob?jk=62c75d5f8fbde70d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Medeloop</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Beacon, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81ac0513866a1f53</t>
+          <t>https://www.indeed.com/viewjob?jk=a81ed0b08e8f07f7</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Backend Engineer II</t>
+          <t>Machine Learning Engineer (171680)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae2342b890625b11</t>
+          <t>https://www.indeed.com/viewjob?jk=a860d07867e70be2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RJW Logistics</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef58fd9ad5dd15ff</t>
+          <t>https://www.indeed.com/viewjob?jk=30ff91e3d3905a73</t>
         </is>
       </c>
     </row>
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ff91e3d3905a73</t>
+          <t>https://www.indeed.com/viewjob?jk=17cbee15ac5e5d6a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Backend Engineer II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cbee15ac5e5d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=ae2342b890625b11</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>RJW Logistics</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,59 +2841,59 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf17dcf23ea3201f</t>
+          <t>https://www.indeed.com/viewjob?jk=ef58fd9ad5dd15ff</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer - Dallas, TX</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865a46cfbc7cc3f4</t>
+          <t>https://www.indeed.com/viewjob?jk=bf17dcf23ea3201f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Cloud Software Engineer 3 - III</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766ed066e436eb0c</t>
+          <t>https://www.indeed.com/viewjob?jk=16ddbf61e3ea0b92</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Cloud Software Engineer 3 - II</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c080bdfd0f5497</t>
+          <t>https://www.indeed.com/viewjob?jk=43bfe7ca1f6eddb7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Cloud Software Engineer 3 - I</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01aefad23a0eebfc</t>
+          <t>https://www.indeed.com/viewjob?jk=2124d09922154cc4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>GIS Support Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b79af965edb52688</t>
+          <t>https://www.indeed.com/viewjob?jk=e24b40c19089ff90</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Data Engineer - Dallas, TX</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe099d836f48656</t>
+          <t>https://www.indeed.com/viewjob?jk=865a46cfbc7cc3f4</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8756dcda438f6959</t>
+          <t>https://www.indeed.com/viewjob?jk=766ed066e436eb0c</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c70b98cc7f980bc</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c080bdfd0f5497</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa8671f82044c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=01aefad23a0eebfc</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bddaca0e62ee366</t>
+          <t>https://www.indeed.com/viewjob?jk=b79af965edb52688</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4177c81ac5d66b2d</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe099d836f48656</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02c32fad4b2ac01d</t>
+          <t>https://www.indeed.com/viewjob?jk=8756dcda438f6959</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=964bc462945e695c</t>
+          <t>https://www.indeed.com/viewjob?jk=3c70b98cc7f980bc</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7beb81f1fe47bc19</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa8671f82044c5a</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3c6d71a96ee8e3e</t>
+          <t>https://www.indeed.com/viewjob?jk=9bddaca0e62ee366</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e48e8aee6232ce</t>
+          <t>https://www.indeed.com/viewjob?jk=4177c81ac5d66b2d</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26cc56905b519e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=02c32fad4b2ac01d</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=416163a4caa0a101</t>
+          <t>https://www.indeed.com/viewjob?jk=964bc462945e695c</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b314b34d858c384</t>
+          <t>https://www.indeed.com/viewjob?jk=7beb81f1fe47bc19</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d26c232b74cd8f7</t>
+          <t>https://www.indeed.com/viewjob?jk=a3c6d71a96ee8e3e</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0461589d526a9a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=85e48e8aee6232ce</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a01db0a34a1698ca</t>
+          <t>https://www.indeed.com/viewjob?jk=26cc56905b519e4a</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d2979409c83f2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=416163a4caa0a101</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19292a33d87f477b</t>
+          <t>https://www.indeed.com/viewjob?jk=6b314b34d858c384</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c45b67d1782f41c</t>
+          <t>https://www.indeed.com/viewjob?jk=3d26c232b74cd8f7</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e0fdb2d1d8365c</t>
+          <t>https://www.indeed.com/viewjob?jk=0461589d526a9a5c</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50082798bb6a8951</t>
+          <t>https://www.indeed.com/viewjob?jk=a01db0a34a1698ca</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff4b550996831857</t>
+          <t>https://www.indeed.com/viewjob?jk=1d2979409c83f2a4</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7a140e56c36bd8e</t>
+          <t>https://www.indeed.com/viewjob?jk=19292a33d87f477b</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7177f3e2822442b8</t>
+          <t>https://www.indeed.com/viewjob?jk=1c45b67d1782f41c</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f786bfc01c412f</t>
+          <t>https://www.indeed.com/viewjob?jk=28e0fdb2d1d8365c</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c31b397857f539a8</t>
+          <t>https://www.indeed.com/viewjob?jk=50082798bb6a8951</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2a59301082a549</t>
+          <t>https://www.indeed.com/viewjob?jk=ff4b550996831857</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd442131644c2ae</t>
+          <t>https://www.indeed.com/viewjob?jk=e7a140e56c36bd8e</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac49610be5f7c22</t>
+          <t>https://www.indeed.com/viewjob?jk=7177f3e2822442b8</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd327a6115535e1</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f786bfc01c412f</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fdf53b11b630cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=c31b397857f539a8</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7ce02753b98a7f</t>
+          <t>https://www.indeed.com/viewjob?jk=df2a59301082a549</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48e68a3d2a669f96</t>
+          <t>https://www.indeed.com/viewjob?jk=abd442131644c2ae</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=715a8a81ec1663c0</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac49610be5f7c22</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c61b7a4534477b1</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd327a6115535e1</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=714987b40a626f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=6fdf53b11b630cb7</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc2483f2dc10aa24</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7ce02753b98a7f</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f3867fb9d5fca1</t>
+          <t>https://www.indeed.com/viewjob?jk=48e68a3d2a669f96</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e14441426c0e5912</t>
+          <t>https://www.indeed.com/viewjob?jk=715a8a81ec1663c0</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de87959267d1c1a1</t>
+          <t>https://www.indeed.com/viewjob?jk=8c61b7a4534477b1</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157307b309906617</t>
+          <t>https://www.indeed.com/viewjob?jk=714987b40a626f2c</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd2a0badba0820e7</t>
+          <t>https://www.indeed.com/viewjob?jk=bc2483f2dc10aa24</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a1077e0bf1888ba</t>
+          <t>https://www.indeed.com/viewjob?jk=41f3867fb9d5fca1</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c0316b1d2e51b16</t>
+          <t>https://www.indeed.com/viewjob?jk=e14441426c0e5912</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91b58529dba10c91</t>
+          <t>https://www.indeed.com/viewjob?jk=de87959267d1c1a1</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbe26208741cfd88</t>
+          <t>https://www.indeed.com/viewjob?jk=157307b309906617</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4deeb487a12f72a</t>
+          <t>https://www.indeed.com/viewjob?jk=fd2a0badba0820e7</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Engineer II, AWS Connect</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d1c8d1b8c5a8bd</t>
+          <t>https://www.indeed.com/viewjob?jk=3a1077e0bf1888ba</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>adonis</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5621c4e542d4639</t>
+          <t>https://www.indeed.com/viewjob?jk=8c0316b1d2e51b16</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>NetApp Emerging Talent - Entry Level Software Engineer (Cloud Storage)</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e07865da969c4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=91b58529dba10c91</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Hybrid</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Snowflake, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=745ab30cde1846a7</t>
+          <t>https://www.indeed.com/viewjob?jk=bbe26208741cfd88</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, Spark, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a27a8acf3bc1bc8</t>
+          <t>https://www.indeed.com/viewjob?jk=a4deeb487a12f72a</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Full-Stack Developer (AWS, TS, React)</t>
+          <t>Engineer II, AWS Connect</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc3a148287061e68</t>
+          <t>https://www.indeed.com/viewjob?jk=16d1c8d1b8c5a8bd</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>BillGO, Inc.</t>
+          <t>adonis</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, DynamoDB, Star Schema, ELT, Tableau, GitHub Actions</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69713d6be44a4b67</t>
+          <t>https://www.indeed.com/viewjob?jk=e5621c4e542d4639</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b635a4480602f9</t>
+          <t>https://www.indeed.com/viewjob?jk=38299c9de7d6d6a0</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform</t>
+          <t>NetApp Emerging Talent - Entry Level Software Engineer (Cloud Storage)</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Rocket Close</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fce91f5c39bd4ed</t>
+          <t>https://www.indeed.com/viewjob?jk=7e07865da969c4a3</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>NetApp Emerging Talent - Software Engineer (Cloud Storage)</t>
+          <t>Sr. Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Snowflake, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b72bdc255bbf6f8</t>
+          <t>https://www.indeed.com/viewjob?jk=745ab30cde1846a7</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Engineer III, Machine Learning Software</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, S3, Spark, Scala, Snowflake, ETL, CI/CD, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e38b030f65d339e</t>
+          <t>https://www.indeed.com/viewjob?jk=10b635a4480602f9</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test</t>
+          <t>Software Development Engineer (AWS)</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>ALTEN</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Databricks Lakehouse, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6e81f16ad428334</t>
+          <t>https://www.indeed.com/viewjob?jk=0b4b23734e39ac6c</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026009 - Software Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>John Deere</t>
+          <t>BillGO, Inc.</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Moline, IL, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Scala, PostgreSQL, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, DynamoDB, Star Schema, ELT, Tableau, GitHub Actions</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e1a444de87fc2c</t>
+          <t>https://www.indeed.com/viewjob?jk=69713d6be44a4b67</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer (Onsite)</t>
+          <t>Senior Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Colony Brands</t>
+          <t>Rocket Close</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Monroe, WI, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,32 +5186,32 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f935defc4a70c87e</t>
+          <t>https://www.indeed.com/viewjob?jk=9fce91f5c39bd4ed</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>NetApp Emerging Talent - Software Engineer (Cloud Storage)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>RNGD</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,19 +5221,19 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a3ecae4bdb7e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=4b72bdc255bbf6f8</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>MachineMetrics, Inc.</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5242,11 +5242,11 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, RDS, Scala, Kafka, PostgreSQL, Terraform, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Databricks Lakehouse, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,32 +5256,32 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80173e5fca484063</t>
+          <t>https://www.indeed.com/viewjob?jk=a6e81f16ad428334</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Microsoft Modern Work Consultant</t>
+          <t>2026009 - Software Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>John Deere</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Moline, IL, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Scala, PostgreSQL, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,32 +5291,32 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11d034c0b8905492</t>
+          <t>https://www.indeed.com/viewjob?jk=45e1a444de87fc2c</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Software Developer - Information Governance</t>
+          <t>Engineer III, Machine Learning Software</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
+          <t>AWS, S3, Spark, Scala, Snowflake, ETL, CI/CD, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65cd9651c7e25101</t>
+          <t>https://www.indeed.com/viewjob?jk=4e38b030f65d339e</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>Cloud Data Engineer (Onsite)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Colony Brands</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Monroe, WI, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>AWS, Redshift, RDS, Azure, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4296ca379ce33eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=f935defc4a70c87e</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>RNGD</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
+          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f710f05a18efb3e1</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a3ecae4bdb7e4b</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>MachineMetrics, Inc.</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Kinesis, RDS, Scala, Kafka, PostgreSQL, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ad148596751872e</t>
+          <t>https://www.indeed.com/viewjob?jk=80173e5fca484063</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Angular / JAVA Full Stack Engineer</t>
+          <t>Microsoft Modern Work Consultant</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcfd60088aef43d3</t>
+          <t>https://www.indeed.com/viewjob?jk=11d034c0b8905492</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Data Engineer: $150-160,000, MN Based, Hybrid - 2 Days in Office</t>
+          <t>Software Developer - Information Governance</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>GovDocs</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, MongoDB, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8acefc49a07f2d39</t>
+          <t>https://www.indeed.com/viewjob?jk=65cd9651c7e25101</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AI Enablement)</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48c5c7e7de56c6fb</t>
+          <t>https://www.indeed.com/viewjob?jk=f710f05a18efb3e1</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Java)</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Decatur, GA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=338db949c564e874</t>
+          <t>https://www.indeed.com/viewjob?jk=6ad148596751872e</t>
         </is>
       </c>
     </row>
@@ -5683,17 +5683,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Data Product Owner</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Gallagher</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Rolling Meadows, IL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,34 +5701,34 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33815bde90512ef</t>
+          <t>https://www.indeed.com/viewjob?jk=4296ca379ce33eb3</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Senior Geospatial Solutions Architect</t>
+          <t>Angular / JAVA Full Stack Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>S R International Inc</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, S3, Azure, GCP, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,24 +5746,24 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4968b1c75b8ea91</t>
+          <t>https://www.indeed.com/viewjob?jk=fcfd60088aef43d3</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Senior Geospatial Solutions Architect</t>
+          <t>Senior Data Engineer: $150-160,000, MN Based, Hybrid - 2 Days in Office</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>GovDocs</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,17 +5771,192 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, MongoDB, ETL, ELT, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8acefc49a07f2d39</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (AI Enablement)</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Redwood Logistics</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48c5c7e7de56c6fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer ( Java)</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Press Ganey</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Decatur, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=338db949c564e874</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Senior Geospatial Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>S R International Inc</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
           <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5f71870dc0f7bc53</t>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4968b1c75b8ea91</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Data Product Owner</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Gallagher</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Rolling Meadows, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a33815bde90512ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Cloud Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>CleanSlate Technology Group</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Carmel, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=478788964e131867</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-15.xlsx
+++ b/results/job_matches_2026-04-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G158"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1028,25 +1028,25 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Java Developer (Hybrid- Flexible Options)</t>
+          <t>Operations Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>Stifel</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Edgewood, NY, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,59 +1056,59 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25ccf7fa8d4a5b10</t>
+          <t>https://www.indeed.com/viewjob?jk=d061193f264addea</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>bioMerieux</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hazelwood, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Oracle, PostgreSQL, CI/CD</t>
+          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2788300e5964c54</t>
+          <t>https://www.indeed.com/viewjob?jk=f99034f0e149e6e6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Operations Engineer (Cloud)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Stifel</t>
+          <t>Ignite Insurance Systems</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d061193f264addea</t>
+          <t>https://www.indeed.com/viewjob?jk=560d14506d8aa36b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
+          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f99034f0e149e6e6</t>
+          <t>https://www.indeed.com/viewjob?jk=e99b4467c3c6aa55</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Architect I</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ignite Insurance Systems</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Azure, Data Factory, Databricks</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=560d14506d8aa36b</t>
+          <t>https://www.indeed.com/viewjob?jk=c6d97da40a8da560</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Azure, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,129 +1231,129 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99b4467c3c6aa55</t>
+          <t>https://www.indeed.com/viewjob?jk=fcd17ae9e035b9a9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Architect I</t>
+          <t>Database and Dashboard Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Azure, Data Factory, Databricks</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6d97da40a8da560</t>
+          <t>https://www.indeed.com/viewjob?jk=fee5a2d73882379c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Azure, GCP, Scala, Kafka</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcd17ae9e035b9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=f193a5a41b80d59d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Snowflake Data Engineer (contract)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Express</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, BigQuery, Scala, Oracle, MongoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27ee634b56d5a4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=23956751504b8384</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Database and Dashboard Developer</t>
+          <t>Solution Architect, Enterprise</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Oracle</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fee5a2d73882379c</t>
+          <t>https://www.indeed.com/viewjob?jk=3f33106731db1775</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solution Architect, Enterprise</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,29 +1396,29 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f193a5a41b80d59d</t>
+          <t>https://www.indeed.com/viewjob?jk=90d356ab99a57489</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer (contract)</t>
+          <t>Solution Architect, Enterprise</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23956751504b8384</t>
+          <t>https://www.indeed.com/viewjob?jk=15664632526fabdb</t>
         </is>
       </c>
     </row>
@@ -1553,60 +1553,60 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Deal Data Technology &amp; Analytics, Senior Associate</t>
+          <t>Site Reliability Engineer (Cloud Enablement)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>Flexera</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, GCP, Vertex AI, Scala, SQL Server, dbt</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc13b56a1dadc810</t>
+          <t>https://www.indeed.com/viewjob?jk=72d1842ef3999b1d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Deal Data Technology &amp; Analytics, Senior Associate</t>
+          <t>AI Intern</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, GCP, Vertex AI, Scala, SQL Server, dbt</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, dbt, MLflow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42cc0c644ae78852</t>
+          <t>https://www.indeed.com/viewjob?jk=7bea47ac5f13bd1f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Deal Data Technology &amp; Analytics, Senior Associate</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, GCP, Vertex AI, Scala, SQL Server, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46d19923987ef429</t>
+          <t>https://www.indeed.com/viewjob?jk=93144249a4967543</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Deal Data Technology &amp; Analytics, Senior Associate</t>
+          <t>Mid-Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Silicon Valley, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, GCP, Vertex AI, Scala, SQL Server, dbt</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa06155bf991d0f8</t>
+          <t>https://www.indeed.com/viewjob?jk=c717630a440c614c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Deal Data Technology &amp; Analytics, Senior Associate</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, GCP, Vertex AI, Scala, SQL Server, dbt</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,129 +1721,129 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22e6ab66fd67032d</t>
+          <t>https://www.indeed.com/viewjob?jk=15a32bf71ba33ffa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Solution Architect, Enterprise</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f33106731db1775</t>
+          <t>https://www.indeed.com/viewjob?jk=4d3db28285f41c46</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Solution Architect, Enterprise</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90d356ab99a57489</t>
+          <t>https://www.indeed.com/viewjob?jk=3989068a8778fb79</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Solution Architect, Enterprise</t>
+          <t>Research Engineer II</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bryan, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15664632526fabdb</t>
+          <t>https://www.indeed.com/viewjob?jk=09b3207da19db4ee</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (Cloud Enablement)</t>
+          <t>Research Engineer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Flexera</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bryan, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72d1842ef3999b1d</t>
+          <t>https://www.indeed.com/viewjob?jk=bb85a1b8d1928fd4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Intern</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, dbt, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bea47ac5f13bd1f</t>
+          <t>https://www.indeed.com/viewjob?jk=9f177704478aadbe</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ArcGIS Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, API Gateway, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93144249a4967543</t>
+          <t>https://www.indeed.com/viewjob?jk=1186a0273eb12d27</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Sr. ETL/Python Developer)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>RCR Technology</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Robstown, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=072e6e4e8e025141</t>
+          <t>https://www.indeed.com/viewjob?jk=4527effc81797bda</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Mid-Level Data Engineer, Global</t>
+          <t>Data Support Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Illumen Group</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Stafford, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>AWS, Glue, Redshift, Athena, S3, Databricks, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c717630a440c614c</t>
+          <t>https://www.indeed.com/viewjob?jk=92cd661cf5a17182</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15a32bf71ba33ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=8a0467416d94bb26</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Software Development Engineer II (C#/.NET, Azure)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d3db28285f41c46</t>
+          <t>https://www.indeed.com/viewjob?jk=b6c902472d880e18</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Sr Mgr Data Engineering</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3989068a8778fb79</t>
+          <t>https://www.indeed.com/viewjob?jk=03e707506ab6122a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Banner Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c70a1cb7dff6fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=c8d9928392bc7529</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de9b476cdbf12e9</t>
+          <t>https://www.indeed.com/viewjob?jk=1a527d30b5c00d7d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Research Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>Banner Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bryan, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b3207da19db4ee</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1bf292f1b43ebd</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Research Engineer II</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bryan, TX, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb85a1b8d1928fd4</t>
+          <t>https://www.indeed.com/viewjob?jk=62c75d5f8fbde70d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Medeloop</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,67 +2281,67 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f177704478aadbe</t>
+          <t>https://www.indeed.com/viewjob?jk=a81ed0b08e8f07f7</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ArcGIS Software Engineer</t>
+          <t>Backend Engineer II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1186a0273eb12d27</t>
+          <t>https://www.indeed.com/viewjob?jk=ae2342b890625b11</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Sr. ETL/Python Developer)</t>
+          <t>Machine Learning Engineer (171680)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RCR Technology</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4527effc81797bda</t>
+          <t>https://www.indeed.com/viewjob?jk=a860d07867e70be2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Support Engineer</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Illumen Group</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Stafford, VA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, Databricks, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92cd661cf5a17182</t>
+          <t>https://www.indeed.com/viewjob?jk=30ff91e3d3905a73</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AllCloud</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a0467416d94bb26</t>
+          <t>https://www.indeed.com/viewjob?jk=17cbee15ac5e5d6a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Development Engineer II (C#/.NET, Azure)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6c902472d880e18</t>
+          <t>https://www.indeed.com/viewjob?jk=bf17dcf23ea3201f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr Mgr Data Engineering</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>RJW Logistics</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,207 +2491,207 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e707506ab6122a</t>
+          <t>https://www.indeed.com/viewjob?jk=ef58fd9ad5dd15ff</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Software Engineer 3 - III</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Banner Health</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8d9928392bc7529</t>
+          <t>https://www.indeed.com/viewjob?jk=16ddbf61e3ea0b92</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Cloud Software Engineer 3 - II</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a527d30b5c00d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=43bfe7ca1f6eddb7</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Software Engineer 3 - I</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Banner Health</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1bf292f1b43ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=2124d09922154cc4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>GIS Support Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62c75d5f8fbde70d</t>
+          <t>https://www.indeed.com/viewjob?jk=e24b40c19089ff90</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Engineer - Dallas, TX</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Medeloop</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a81ed0b08e8f07f7</t>
+          <t>https://www.indeed.com/viewjob?jk=865a46cfbc7cc3f4</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (171680)</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a860d07867e70be2</t>
+          <t>https://www.indeed.com/viewjob?jk=766ed066e436eb0c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ff91e3d3905a73</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c080bdfd0f5497</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,67 +2771,67 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cbee15ac5e5d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=01aefad23a0eebfc</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Backend Engineer II</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae2342b890625b11</t>
+          <t>https://www.indeed.com/viewjob?jk=b79af965edb52688</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>RJW Logistics</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef58fd9ad5dd15ff</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe099d836f48656</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf17dcf23ea3201f</t>
+          <t>https://www.indeed.com/viewjob?jk=8756dcda438f6959</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - III</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16ddbf61e3ea0b92</t>
+          <t>https://www.indeed.com/viewjob?jk=3c70b98cc7f980bc</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - II</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43bfe7ca1f6eddb7</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa8671f82044c5a</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - I</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2124d09922154cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=9bddaca0e62ee366</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>GIS Support Engineer</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e24b40c19089ff90</t>
+          <t>https://www.indeed.com/viewjob?jk=4177c81ac5d66b2d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer - Dallas, TX</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865a46cfbc7cc3f4</t>
+          <t>https://www.indeed.com/viewjob?jk=02c32fad4b2ac01d</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766ed066e436eb0c</t>
+          <t>https://www.indeed.com/viewjob?jk=964bc462945e695c</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c080bdfd0f5497</t>
+          <t>https://www.indeed.com/viewjob?jk=7beb81f1fe47bc19</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01aefad23a0eebfc</t>
+          <t>https://www.indeed.com/viewjob?jk=a3c6d71a96ee8e3e</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b79af965edb52688</t>
+          <t>https://www.indeed.com/viewjob?jk=85e48e8aee6232ce</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe099d836f48656</t>
+          <t>https://www.indeed.com/viewjob?jk=26cc56905b519e4a</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8756dcda438f6959</t>
+          <t>https://www.indeed.com/viewjob?jk=416163a4caa0a101</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c70b98cc7f980bc</t>
+          <t>https://www.indeed.com/viewjob?jk=6b314b34d858c384</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa8671f82044c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=3d26c232b74cd8f7</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bddaca0e62ee366</t>
+          <t>https://www.indeed.com/viewjob?jk=0461589d526a9a5c</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4177c81ac5d66b2d</t>
+          <t>https://www.indeed.com/viewjob?jk=a01db0a34a1698ca</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02c32fad4b2ac01d</t>
+          <t>https://www.indeed.com/viewjob?jk=1d2979409c83f2a4</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=964bc462945e695c</t>
+          <t>https://www.indeed.com/viewjob?jk=19292a33d87f477b</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7beb81f1fe47bc19</t>
+          <t>https://www.indeed.com/viewjob?jk=1c45b67d1782f41c</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3c6d71a96ee8e3e</t>
+          <t>https://www.indeed.com/viewjob?jk=28e0fdb2d1d8365c</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e48e8aee6232ce</t>
+          <t>https://www.indeed.com/viewjob?jk=50082798bb6a8951</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26cc56905b519e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=ff4b550996831857</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=416163a4caa0a101</t>
+          <t>https://www.indeed.com/viewjob?jk=e7a140e56c36bd8e</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b314b34d858c384</t>
+          <t>https://www.indeed.com/viewjob?jk=7177f3e2822442b8</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d26c232b74cd8f7</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f786bfc01c412f</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0461589d526a9a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=c31b397857f539a8</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a01db0a34a1698ca</t>
+          <t>https://www.indeed.com/viewjob?jk=df2a59301082a549</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d2979409c83f2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=abd442131644c2ae</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19292a33d87f477b</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac49610be5f7c22</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c45b67d1782f41c</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd327a6115535e1</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e0fdb2d1d8365c</t>
+          <t>https://www.indeed.com/viewjob?jk=6fdf53b11b630cb7</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50082798bb6a8951</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7ce02753b98a7f</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff4b550996831857</t>
+          <t>https://www.indeed.com/viewjob?jk=48e68a3d2a669f96</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7a140e56c36bd8e</t>
+          <t>https://www.indeed.com/viewjob?jk=715a8a81ec1663c0</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7177f3e2822442b8</t>
+          <t>https://www.indeed.com/viewjob?jk=8c61b7a4534477b1</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f786bfc01c412f</t>
+          <t>https://www.indeed.com/viewjob?jk=714987b40a626f2c</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c31b397857f539a8</t>
+          <t>https://www.indeed.com/viewjob?jk=bc2483f2dc10aa24</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2a59301082a549</t>
+          <t>https://www.indeed.com/viewjob?jk=41f3867fb9d5fca1</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd442131644c2ae</t>
+          <t>https://www.indeed.com/viewjob?jk=e14441426c0e5912</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac49610be5f7c22</t>
+          <t>https://www.indeed.com/viewjob?jk=de87959267d1c1a1</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd327a6115535e1</t>
+          <t>https://www.indeed.com/viewjob?jk=157307b309906617</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fdf53b11b630cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=fd2a0badba0820e7</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7ce02753b98a7f</t>
+          <t>https://www.indeed.com/viewjob?jk=3a1077e0bf1888ba</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48e68a3d2a669f96</t>
+          <t>https://www.indeed.com/viewjob?jk=8c0316b1d2e51b16</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=715a8a81ec1663c0</t>
+          <t>https://www.indeed.com/viewjob?jk=91b58529dba10c91</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c61b7a4534477b1</t>
+          <t>https://www.indeed.com/viewjob?jk=bbe26208741cfd88</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=714987b40a626f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=a4deeb487a12f72a</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Engineer II, AWS Connect</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc2483f2dc10aa24</t>
+          <t>https://www.indeed.com/viewjob?jk=16d1c8d1b8c5a8bd</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>adonis</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f3867fb9d5fca1</t>
+          <t>https://www.indeed.com/viewjob?jk=e5621c4e542d4639</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e14441426c0e5912</t>
+          <t>https://www.indeed.com/viewjob?jk=38299c9de7d6d6a0</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>NetApp Emerging Talent - Entry Level Software Engineer (Cloud Storage)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de87959267d1c1a1</t>
+          <t>https://www.indeed.com/viewjob?jk=7e07865da969c4a3</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Sr. Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Snowflake, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157307b309906617</t>
+          <t>https://www.indeed.com/viewjob?jk=745ab30cde1846a7</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BillGO, Inc.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, DynamoDB, Star Schema, ELT, Tableau, GitHub Actions</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd2a0badba0820e7</t>
+          <t>https://www.indeed.com/viewjob?jk=69713d6be44a4b67</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a1077e0bf1888ba</t>
+          <t>https://www.indeed.com/viewjob?jk=10b635a4480602f9</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Senior Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Rocket Close</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c0316b1d2e51b16</t>
+          <t>https://www.indeed.com/viewjob?jk=9fce91f5c39bd4ed</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>NetApp Emerging Talent - Software Engineer (Cloud Storage)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91b58529dba10c91</t>
+          <t>https://www.indeed.com/viewjob?jk=4b72bdc255bbf6f8</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Senior Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Databricks Lakehouse, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbe26208741cfd88</t>
+          <t>https://www.indeed.com/viewjob?jk=a6e81f16ad428334</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>2026009 - Software Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>John Deere</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Moline, IL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Scala, PostgreSQL, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4deeb487a12f72a</t>
+          <t>https://www.indeed.com/viewjob?jk=45e1a444de87fc2c</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Engineer II, AWS Connect</t>
+          <t>Cloud Data Engineer (Onsite)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>Colony Brands</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Monroe, WI, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,32 +4906,32 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d1c8d1b8c5a8bd</t>
+          <t>https://www.indeed.com/viewjob?jk=f935defc4a70c87e</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>adonis</t>
+          <t>RNGD</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,32 +4941,32 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5621c4e542d4639</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a3ecae4bdb7e4b</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>MachineMetrics, Inc.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD, Git</t>
+          <t>AWS, Lambda, Kinesis, RDS, Scala, Kafka, PostgreSQL, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,32 +4976,32 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38299c9de7d6d6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=80173e5fca484063</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>NetApp Emerging Talent - Entry Level Software Engineer (Cloud Storage)</t>
+          <t>Microsoft Modern Work Consultant</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,32 +5011,32 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e07865da969c4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=11d034c0b8905492</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Hybrid</t>
+          <t>Software Developer - Information Governance</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Snowflake, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,32 +5046,32 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=745ab30cde1846a7</t>
+          <t>https://www.indeed.com/viewjob?jk=65cd9651c7e25101</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,32 +5081,32 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b635a4480602f9</t>
+          <t>https://www.indeed.com/viewjob?jk=4296ca379ce33eb3</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Software Development Engineer (AWS)</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ALTEN</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,32 +5116,32 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b4b23734e39ac6c</t>
+          <t>https://www.indeed.com/viewjob?jk=f710f05a18efb3e1</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>BillGO, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, DynamoDB, Star Schema, ELT, Tableau, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69713d6be44a4b67</t>
+          <t>https://www.indeed.com/viewjob?jk=6ad148596751872e</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform</t>
+          <t>Angular / JAVA Full Stack Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Rocket Close</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, Azure, GCP, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,32 +5186,32 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fce91f5c39bd4ed</t>
+          <t>https://www.indeed.com/viewjob?jk=fcfd60088aef43d3</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>NetApp Emerging Talent - Software Engineer (Cloud Storage)</t>
+          <t>Senior Data Engineer: $150-160,000, MN Based, Hybrid - 2 Days in Office</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>GovDocs</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, MongoDB, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,32 +5221,32 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b72bdc255bbf6f8</t>
+          <t>https://www.indeed.com/viewjob?jk=8acefc49a07f2d39</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test</t>
+          <t>Senior Software Engineer (AI Enablement)</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Databricks Lakehouse, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,32 +5256,32 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6e81f16ad428334</t>
+          <t>https://www.indeed.com/viewjob?jk=48c5c7e7de56c6fb</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026009 - Software Engineer</t>
+          <t>Senior Software Engineer ( Java)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>John Deere</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Moline, IL, US USA</t>
+          <t>Decatur, GA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Scala, PostgreSQL, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,32 +5291,32 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e1a444de87fc2c</t>
+          <t>https://www.indeed.com/viewjob?jk=338db949c564e874</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Engineer III, Machine Learning Software</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, S3, Spark, Scala, Snowflake, ETL, CI/CD, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e38b030f65d339e</t>
+          <t>https://www.indeed.com/viewjob?jk=085872f73883326c</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer (Onsite)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Colony Brands</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Monroe, WI, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f935defc4a70c87e</t>
+          <t>https://www.indeed.com/viewjob?jk=fa79af047e73dc3e</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>RNGD</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a3ecae4bdb7e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=34987f860a590c53</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Product Owner</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MachineMetrics, Inc.</t>
+          <t>Gallagher</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rolling Meadows, IL, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, RDS, Scala, Kafka, PostgreSQL, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80173e5fca484063</t>
+          <t>https://www.indeed.com/viewjob?jk=a33815bde90512ef</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Microsoft Modern Work Consultant</t>
+          <t>Senior Geospatial Solutions Architect</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>S R International Inc</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,497 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11d034c0b8905492</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Software Developer - Information Governance</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Epiq</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Overland Park, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=65cd9651c7e25101</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Sr Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f710f05a18efb3e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Sr Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>MO, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ad148596751872e</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>CapTech Consulting</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=085872f73883326c</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>CapTech Consulting</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fa79af047e73dc3e</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>CapTech Consulting</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=34987f860a590c53</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Claims Data Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4296ca379ce33eb3</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Angular / JAVA Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Charles Schwab</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, GCP, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fcfd60088aef43d3</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer: $150-160,000, MN Based, Hybrid - 2 Days in Office</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>GovDocs</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Saint Paul, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, MongoDB, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8acefc49a07f2d39</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (AI Enablement)</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Redwood Logistics</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48c5c7e7de56c6fb</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer ( Java)</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Press Ganey</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Decatur, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=338db949c564e874</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Senior Geospatial Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>S R International Inc</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Harrisburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=b4968b1c75b8ea91</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Data Product Owner</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Gallagher</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Rolling Meadows, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a33815bde90512ef</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Cloud Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>CleanSlate Technology Group</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Carmel, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=478788964e131867</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-15.xlsx
+++ b/results/job_matches_2026-04-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G144"/>
+  <dimension ref="A1:G142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,95 +538,95 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI/ML Data Engineer</t>
+          <t>Software Engineer III - AWS Glue</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Marvell Technology</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db6fecac436797a9</t>
+          <t>https://www.indeed.com/viewjob?jk=5f1496d3a0b45451</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Engineer 2026 - US,UK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AmeriLife</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d10f6b2d0d1b341d</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d01fdc4061dd2a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS Glue</t>
+          <t>Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f1496d3a0b45451</t>
+          <t>https://www.indeed.com/viewjob?jk=8a711c2fcb36b6cf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer 2026 - US,UK</t>
+          <t>Sr. Data Engineer (ON-SITE)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d01fdc4061dd2a</t>
+          <t>https://www.indeed.com/viewjob?jk=038b96d69cecd888</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer/Data Scientist</t>
+          <t>Information Technology - BI Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>TCC Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Fishers, IN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,77 +696,77 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a711c2fcb36b6cf</t>
+          <t>https://www.indeed.com/viewjob?jk=ca19ad92abde46c9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (ON-SITE)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Equinox</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, Snowflake, DynamoDB</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=038b96d69cecd888</t>
+          <t>https://www.indeed.com/viewjob?jk=cb699a2e3bdbb440</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Information Technology - BI Developer</t>
+          <t>Data Warehouse Analyst Seniors: Cloud Engineering</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TCC Verizon Authorized Retailer</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fishers, IN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca19ad92abde46c9</t>
+          <t>https://www.indeed.com/viewjob?jk=d87aa04a7733264b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb699a2e3bdbb440</t>
+          <t>https://www.indeed.com/viewjob?jk=574e10b9b787dc54</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Warehouse Analyst Seniors: Cloud Engineering</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, ETL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d87aa04a7733264b</t>
+          <t>https://www.indeed.com/viewjob?jk=ac615cac5200efc9</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=574e10b9b787dc54</t>
+          <t>https://www.indeed.com/viewjob?jk=8a7de03320b3d487</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac615cac5200efc9</t>
+          <t>https://www.indeed.com/viewjob?jk=df1418000450ecdb</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a7de03320b3d487</t>
+          <t>https://www.indeed.com/viewjob?jk=6df75aab0012c038</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Full Stack AI Engineer</t>
+          <t>Operations Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Stifel</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df1418000450ecdb</t>
+          <t>https://www.indeed.com/viewjob?jk=d061193f264addea</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Full Stack AI Engineer</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6df75aab0012c038</t>
+          <t>https://www.indeed.com/viewjob?jk=f99034f0e149e6e6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Operations Engineer (Cloud)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Stifel</t>
+          <t>Ignite Insurance Systems</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d061193f264addea</t>
+          <t>https://www.indeed.com/viewjob?jk=560d14506d8aa36b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
+          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f99034f0e149e6e6</t>
+          <t>https://www.indeed.com/viewjob?jk=e99b4467c3c6aa55</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Architect I</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ignite Insurance Systems</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Azure, Data Factory, Databricks</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=560d14506d8aa36b</t>
+          <t>https://www.indeed.com/viewjob?jk=c6d97da40a8da560</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Azure, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,19 +1161,19 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99b4467c3c6aa55</t>
+          <t>https://www.indeed.com/viewjob?jk=fcd17ae9e035b9a9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Architect I</t>
+          <t>Data Engineer- OrderlyMeds</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>OrderlyMeds</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1182,46 +1182,46 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Azure, Data Factory, Databricks</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6d97da40a8da560</t>
+          <t>https://www.indeed.com/viewjob?jk=4f563cb4be7b9221</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Azure, GCP, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcd17ae9e035b9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=aa4d88005315e7ba</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1693,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Research Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Bryan, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15a32bf71ba33ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=09b3207da19db4ee</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Research Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bryan, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d3db28285f41c46</t>
+          <t>https://www.indeed.com/viewjob?jk=bb85a1b8d1928fd4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3989068a8778fb79</t>
+          <t>https://www.indeed.com/viewjob?jk=a5acecf0e4305790</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Research Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bryan, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b3207da19db4ee</t>
+          <t>https://www.indeed.com/viewjob?jk=9f177704478aadbe</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Research Engineer II</t>
+          <t>ArcGIS Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bryan, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
+          <t>AWS, API Gateway, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb85a1b8d1928fd4</t>
+          <t>https://www.indeed.com/viewjob?jk=1186a0273eb12d27</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer (Sr. ETL/Python Developer)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>RCR Technology</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f177704478aadbe</t>
+          <t>https://www.indeed.com/viewjob?jk=4527effc81797bda</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ArcGIS Software Engineer</t>
+          <t>Data Support Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Illumen Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Stafford, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, Athena, S3, Databricks, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1186a0273eb12d27</t>
+          <t>https://www.indeed.com/viewjob?jk=92cd661cf5a17182</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Sr. ETL/Python Developer)</t>
+          <t>AI/ML Engineering Intern (Summer 2026)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RCR Technology</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>Redshift, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4527effc81797bda</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd3431b51acd4b5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Support Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Illumen Group</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Stafford, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, Databricks, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92cd661cf5a17182</t>
+          <t>https://www.indeed.com/viewjob?jk=8a0467416d94bb26</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Development Engineer II (C#/.NET, Azure)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AllCloud</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a0467416d94bb26</t>
+          <t>https://www.indeed.com/viewjob?jk=b6c902472d880e18</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Development Engineer II (C#/.NET, Azure)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Banner Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6c902472d880e18</t>
+          <t>https://www.indeed.com/viewjob?jk=c8d9928392bc7529</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Mgr Data Engineering</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e707506ab6122a</t>
+          <t>https://www.indeed.com/viewjob?jk=1a527d30b5c00d7d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Banner Health</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8d9928392bc7529</t>
+          <t>https://www.indeed.com/viewjob?jk=62c75d5f8fbde70d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Medeloop</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a527d30b5c00d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=a81ed0b08e8f07f7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend Engineer II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Banner Health</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1bf292f1b43ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=ae2342b890625b11</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>RJW Logistics</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62c75d5f8fbde70d</t>
+          <t>https://www.indeed.com/viewjob?jk=ef58fd9ad5dd15ff</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Machine Learning Engineer (171680)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Medeloop</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a81ed0b08e8f07f7</t>
+          <t>https://www.indeed.com/viewjob?jk=a860d07867e70be2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Backend Engineer II</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae2342b890625b11</t>
+          <t>https://www.indeed.com/viewjob?jk=30ff91e3d3905a73</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (171680)</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a860d07867e70be2</t>
+          <t>https://www.indeed.com/viewjob?jk=17cbee15ac5e5d6a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,119 +2386,119 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ff91e3d3905a73</t>
+          <t>https://www.indeed.com/viewjob?jk=bf17dcf23ea3201f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>Holland &amp; Knight</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Brandon, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, Airflow, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cbee15ac5e5d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=3abb3ed211255b11</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf17dcf23ea3201f</t>
+          <t>https://www.indeed.com/viewjob?jk=766f2f5e9a7201f1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Cloud Software Engineer 3 - III</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>RJW Logistics</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef58fd9ad5dd15ff</t>
+          <t>https://www.indeed.com/viewjob?jk=16ddbf61e3ea0b92</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - III</t>
+          <t>Cloud Software Engineer 3 - II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2526,14 +2526,14 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16ddbf61e3ea0b92</t>
+          <t>https://www.indeed.com/viewjob?jk=43bfe7ca1f6eddb7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - II</t>
+          <t>Cloud Software Engineer 3 - I</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43bfe7ca1f6eddb7</t>
+          <t>https://www.indeed.com/viewjob?jk=2124d09922154cc4</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - I</t>
+          <t>GIS Support Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
+          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2124d09922154cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=e24b40c19089ff90</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>GIS Support Engineer</t>
+          <t>Data Engineer - Dallas, TX</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e24b40c19089ff90</t>
+          <t>https://www.indeed.com/viewjob?jk=865a46cfbc7cc3f4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer - Dallas, TX</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,17 +2656,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865a46cfbc7cc3f4</t>
+          <t>https://www.indeed.com/viewjob?jk=766ed066e436eb0c</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766ed066e436eb0c</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c080bdfd0f5497</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c080bdfd0f5497</t>
+          <t>https://www.indeed.com/viewjob?jk=01aefad23a0eebfc</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01aefad23a0eebfc</t>
+          <t>https://www.indeed.com/viewjob?jk=b79af965edb52688</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b79af965edb52688</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe099d836f48656</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe099d836f48656</t>
+          <t>https://www.indeed.com/viewjob?jk=8756dcda438f6959</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8756dcda438f6959</t>
+          <t>https://www.indeed.com/viewjob?jk=3c70b98cc7f980bc</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c70b98cc7f980bc</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa8671f82044c5a</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa8671f82044c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=9bddaca0e62ee366</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bddaca0e62ee366</t>
+          <t>https://www.indeed.com/viewjob?jk=4177c81ac5d66b2d</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4177c81ac5d66b2d</t>
+          <t>https://www.indeed.com/viewjob?jk=02c32fad4b2ac01d</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02c32fad4b2ac01d</t>
+          <t>https://www.indeed.com/viewjob?jk=964bc462945e695c</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=964bc462945e695c</t>
+          <t>https://www.indeed.com/viewjob?jk=7beb81f1fe47bc19</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7beb81f1fe47bc19</t>
+          <t>https://www.indeed.com/viewjob?jk=a3c6d71a96ee8e3e</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3c6d71a96ee8e3e</t>
+          <t>https://www.indeed.com/viewjob?jk=85e48e8aee6232ce</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e48e8aee6232ce</t>
+          <t>https://www.indeed.com/viewjob?jk=26cc56905b519e4a</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26cc56905b519e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=416163a4caa0a101</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=416163a4caa0a101</t>
+          <t>https://www.indeed.com/viewjob?jk=6b314b34d858c384</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b314b34d858c384</t>
+          <t>https://www.indeed.com/viewjob?jk=3d26c232b74cd8f7</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d26c232b74cd8f7</t>
+          <t>https://www.indeed.com/viewjob?jk=0461589d526a9a5c</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0461589d526a9a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=a01db0a34a1698ca</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a01db0a34a1698ca</t>
+          <t>https://www.indeed.com/viewjob?jk=1d2979409c83f2a4</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d2979409c83f2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=19292a33d87f477b</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19292a33d87f477b</t>
+          <t>https://www.indeed.com/viewjob?jk=1c45b67d1782f41c</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c45b67d1782f41c</t>
+          <t>https://www.indeed.com/viewjob?jk=28e0fdb2d1d8365c</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e0fdb2d1d8365c</t>
+          <t>https://www.indeed.com/viewjob?jk=50082798bb6a8951</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50082798bb6a8951</t>
+          <t>https://www.indeed.com/viewjob?jk=ff4b550996831857</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff4b550996831857</t>
+          <t>https://www.indeed.com/viewjob?jk=e7a140e56c36bd8e</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7a140e56c36bd8e</t>
+          <t>https://www.indeed.com/viewjob?jk=7177f3e2822442b8</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7177f3e2822442b8</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f786bfc01c412f</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f786bfc01c412f</t>
+          <t>https://www.indeed.com/viewjob?jk=c31b397857f539a8</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c31b397857f539a8</t>
+          <t>https://www.indeed.com/viewjob?jk=df2a59301082a549</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2a59301082a549</t>
+          <t>https://www.indeed.com/viewjob?jk=abd442131644c2ae</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd442131644c2ae</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac49610be5f7c22</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac49610be5f7c22</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd327a6115535e1</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd327a6115535e1</t>
+          <t>https://www.indeed.com/viewjob?jk=6fdf53b11b630cb7</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fdf53b11b630cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7ce02753b98a7f</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7ce02753b98a7f</t>
+          <t>https://www.indeed.com/viewjob?jk=48e68a3d2a669f96</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48e68a3d2a669f96</t>
+          <t>https://www.indeed.com/viewjob?jk=715a8a81ec1663c0</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=715a8a81ec1663c0</t>
+          <t>https://www.indeed.com/viewjob?jk=8c61b7a4534477b1</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c61b7a4534477b1</t>
+          <t>https://www.indeed.com/viewjob?jk=714987b40a626f2c</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=714987b40a626f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=bc2483f2dc10aa24</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc2483f2dc10aa24</t>
+          <t>https://www.indeed.com/viewjob?jk=41f3867fb9d5fca1</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f3867fb9d5fca1</t>
+          <t>https://www.indeed.com/viewjob?jk=e14441426c0e5912</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e14441426c0e5912</t>
+          <t>https://www.indeed.com/viewjob?jk=de87959267d1c1a1</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de87959267d1c1a1</t>
+          <t>https://www.indeed.com/viewjob?jk=157307b309906617</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157307b309906617</t>
+          <t>https://www.indeed.com/viewjob?jk=fd2a0badba0820e7</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd2a0badba0820e7</t>
+          <t>https://www.indeed.com/viewjob?jk=3a1077e0bf1888ba</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a1077e0bf1888ba</t>
+          <t>https://www.indeed.com/viewjob?jk=8c0316b1d2e51b16</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c0316b1d2e51b16</t>
+          <t>https://www.indeed.com/viewjob?jk=91b58529dba10c91</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91b58529dba10c91</t>
+          <t>https://www.indeed.com/viewjob?jk=bbe26208741cfd88</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbe26208741cfd88</t>
+          <t>https://www.indeed.com/viewjob?jk=a4deeb487a12f72a</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Engineer II, AWS Connect</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4deeb487a12f72a</t>
+          <t>https://www.indeed.com/viewjob?jk=16d1c8d1b8c5a8bd</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Engineer II, AWS Connect</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>adonis</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d1c8d1b8c5a8bd</t>
+          <t>https://www.indeed.com/viewjob?jk=e5621c4e542d4639</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>adonis</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5621c4e542d4639</t>
+          <t>https://www.indeed.com/viewjob?jk=38299c9de7d6d6a0</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>NetApp Emerging Talent - Entry Level Software Engineer (Cloud Storage)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38299c9de7d6d6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=7e07865da969c4a3</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>NetApp Emerging Talent - Entry Level Software Engineer (Cloud Storage)</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e07865da969c4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=30ba9654fc14bac7</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Hybrid</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Customers Bank</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Snowflake, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Databricks, Scala, Polars, Snowflake, Oracle, SQL Server, Dimensional Modeling, Power BI</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=745ab30cde1846a7</t>
+          <t>https://www.indeed.com/viewjob?jk=da13b88eee9db315</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>DevOps Security Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>BillGO, Inc.</t>
+          <t>Decentralized Masters</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, DynamoDB, Star Schema, ELT, Tableau, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69713d6be44a4b67</t>
+          <t>https://www.indeed.com/viewjob?jk=45f290af989badc3</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>BillGO, Inc.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, DynamoDB, Star Schema, ELT, Tableau, GitHub Actions</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b635a4480602f9</t>
+          <t>https://www.indeed.com/viewjob?jk=69713d6be44a4b67</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Rocket Close</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fce91f5c39bd4ed</t>
+          <t>https://www.indeed.com/viewjob?jk=10b635a4480602f9</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>NetApp Emerging Talent - Software Engineer (Cloud Storage)</t>
+          <t>Senior Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Rocket Close</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b72bdc255bbf6f8</t>
+          <t>https://www.indeed.com/viewjob?jk=9fce91f5c39bd4ed</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test</t>
+          <t>NetApp Emerging Talent - Software Engineer (Cloud Storage)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Databricks Lakehouse, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6e81f16ad428334</t>
+          <t>https://www.indeed.com/viewjob?jk=4b72bdc255bbf6f8</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026009 - Software Engineer</t>
+          <t>Senior Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>John Deere</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Moline, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Scala, PostgreSQL, Docker, Kubernetes, SonarQube</t>
+          <t>RDS, Azure, Databricks, Scala, Databricks Lakehouse, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e1a444de87fc2c</t>
+          <t>https://www.indeed.com/viewjob?jk=a6e81f16ad428334</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer (Onsite)</t>
+          <t>2026009 - Software Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Colony Brands</t>
+          <t>John Deere</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Monroe, WI, US USA</t>
+          <t>Moline, IL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Scala, PostgreSQL, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f935defc4a70c87e</t>
+          <t>https://www.indeed.com/viewjob?jk=45e1a444de87fc2c</t>
         </is>
       </c>
     </row>
@@ -4918,12 +4918,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>RNGD</t>
+          <t>Metropolitan Companies</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>Wyomissing, PA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a3ecae4bdb7e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=12c03c3bb6ce8c38</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Cloud Data Engineer (Onsite)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>MachineMetrics, Inc.</t>
+          <t>Colony Brands</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Monroe, WI, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, RDS, Scala, Kafka, PostgreSQL, Terraform, Kubernetes, Git</t>
+          <t>AWS, Redshift, RDS, Azure, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80173e5fca484063</t>
+          <t>https://www.indeed.com/viewjob?jk=f935defc4a70c87e</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Microsoft Modern Work Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>RNGD</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11d034c0b8905492</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a3ecae4bdb7e4b</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Software Developer - Information Governance</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>MachineMetrics, Inc.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
+          <t>AWS, Lambda, Kinesis, RDS, Scala, Kafka, PostgreSQL, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65cd9651c7e25101</t>
+          <t>https://www.indeed.com/viewjob?jk=80173e5fca484063</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>Microsoft Modern Work Consultant</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4296ca379ce33eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=11d034c0b8905492</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Supervisor, Software Engineering</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Energy Systems Group</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Newburgh, IN, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f710f05a18efb3e1</t>
+          <t>https://www.indeed.com/viewjob?jk=9c197f77bdf171e6</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,29 +5141,29 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ad148596751872e</t>
+          <t>https://www.indeed.com/viewjob?jk=4296ca379ce33eb3</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Angular / JAVA Full Stack Engineer</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcfd60088aef43d3</t>
+          <t>https://www.indeed.com/viewjob?jk=f710f05a18efb3e1</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Data Engineer: $150-160,000, MN Based, Hybrid - 2 Days in Office</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>GovDocs</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, MongoDB, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8acefc49a07f2d39</t>
+          <t>https://www.indeed.com/viewjob?jk=6ad148596751872e</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AI Enablement)</t>
+          <t>Angular / JAVA Full Stack Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
+          <t>AWS, S3, Azure, GCP, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48c5c7e7de56c6fb</t>
+          <t>https://www.indeed.com/viewjob?jk=fcfd60088aef43d3</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Java)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Decatur, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=338db949c564e874</t>
+          <t>https://www.indeed.com/viewjob?jk=085872f73883326c</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085872f73883326c</t>
+          <t>https://www.indeed.com/viewjob?jk=fa79af047e73dc3e</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa79af047e73dc3e</t>
+          <t>https://www.indeed.com/viewjob?jk=34987f860a590c53</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Cloud Solution Architect</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Applied Information Sciences</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,87 +5386,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34987f860a590c53</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Data Product Owner</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Gallagher</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Rolling Meadows, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a33815bde90512ef</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Senior Geospatial Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>S R International Inc</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Harrisburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b4968b1c75b8ea91</t>
+          <t>https://www.indeed.com/viewjob?jk=f47703eb8d2843d8</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-15.xlsx
+++ b/results/job_matches_2026-04-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G142"/>
+  <dimension ref="A1:G162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Operations Engineer (Cloud)</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Stifel</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d061193f264addea</t>
+          <t>https://www.indeed.com/viewjob?jk=f99034f0e149e6e6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>Ignite Insurance Systems</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
+          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f99034f0e149e6e6</t>
+          <t>https://www.indeed.com/viewjob?jk=560d14506d8aa36b</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ignite Insurance Systems</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=560d14506d8aa36b</t>
+          <t>https://www.indeed.com/viewjob?jk=e99b4467c3c6aa55</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Architect I</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Azure, Data Factory, Databricks</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99b4467c3c6aa55</t>
+          <t>https://www.indeed.com/viewjob?jk=c6d97da40a8da560</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Architect I</t>
+          <t>Operations Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Stifel</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,17 +1116,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Azure, Data Factory, Databricks</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6d97da40a8da560</t>
+          <t>https://www.indeed.com/viewjob?jk=d061193f264addea</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer- OrderlyMeds</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>OrderlyMeds</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f563cb4be7b9221</t>
+          <t>https://www.indeed.com/viewjob?jk=f193a5a41b80d59d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Data Engineer (Azure/Databricks/Python)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>loanDepot</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
+          <t>Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4d88005315e7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=d4b1df13928e079d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Database and Dashboard Developer</t>
+          <t>Data Engineer- OrderlyMeds</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>OrderlyMeds</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Oracle</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fee5a2d73882379c</t>
+          <t>https://www.indeed.com/viewjob?jk=4f563cb4be7b9221</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f193a5a41b80d59d</t>
+          <t>https://www.indeed.com/viewjob?jk=aa4d88005315e7ba</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer (contract)</t>
+          <t>Database and Dashboard Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,29 +1326,29 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23956751504b8384</t>
+          <t>https://www.indeed.com/viewjob?jk=fee5a2d73882379c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Solution Architect, Enterprise</t>
+          <t>Snowflake Data Engineer (contract)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1361,24 +1361,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f33106731db1775</t>
+          <t>https://www.indeed.com/viewjob?jk=23956751504b8384</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Solution Architect, Enterprise</t>
+          <t>Senior Solution Architect, Enterprise - Eastern Time Zone</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90d356ab99a57489</t>
+          <t>https://www.indeed.com/viewjob?jk=da8ab35096a74f07</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Solution Architect, Enterprise</t>
+          <t>Solution Architect, Enterprise - Eastern Time Zone</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15664632526fabdb</t>
+          <t>https://www.indeed.com/viewjob?jk=3f33106731db1775</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Solution Architect, Enterprise</t>
+          <t>Solution Architect, Enterprise - Eastern Time Zone</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1476,14 +1476,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=507830f63a6d47c9</t>
+          <t>https://www.indeed.com/viewjob?jk=90d356ab99a57489</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Solution Architect, Enterprise</t>
+          <t>Solution Architect, Enterprise - Eastern Time Zone</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98d7971656e73b43</t>
+          <t>https://www.indeed.com/viewjob?jk=15664632526fabdb</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Developer</t>
+          <t>Senior Solution Architect, Enterprise - Eastern Time Zone</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Olson Kundig</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,29 +1536,29 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d831e0d8e2c5553f</t>
+          <t>https://www.indeed.com/viewjob?jk=507830f63a6d47c9</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (Cloud Enablement)</t>
+          <t>Senior Solution Architect, Enterprise - Eastern Time Zone</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Flexera</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1567,11 +1567,11 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72d1842ef3999b1d</t>
+          <t>https://www.indeed.com/viewjob?jk=98d7971656e73b43</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Intern</t>
+          <t>Data &amp; AI Governance Officer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Vantage Bank Texas</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, dbt, MLflow</t>
+          <t>AWS, Glue, S3, RDS, Azure, Data Factory, Databricks, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bea47ac5f13bd1f</t>
+          <t>https://www.indeed.com/viewjob?jk=5c469b183725fde1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data &amp; AI Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Olson Kundig</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93144249a4967543</t>
+          <t>https://www.indeed.com/viewjob?jk=d831e0d8e2c5553f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Mid-Level Data Engineer, Global</t>
+          <t>Senior, Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Cassandra</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c717630a440c614c</t>
+          <t>https://www.indeed.com/viewjob?jk=3fcd1c4e67959eea</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Research Engineer II</t>
+          <t>AI Intern</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bryan, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, dbt, MLflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b3207da19db4ee</t>
+          <t>https://www.indeed.com/viewjob?jk=7bea47ac5f13bd1f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Research Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bryan, TX, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb85a1b8d1928fd4</t>
+          <t>https://www.indeed.com/viewjob?jk=93144249a4967543</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Research Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bryan, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5acecf0e4305790</t>
+          <t>https://www.indeed.com/viewjob?jk=09b3207da19db4ee</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Research Engineer II</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Bryan, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f177704478aadbe</t>
+          <t>https://www.indeed.com/viewjob?jk=bb85a1b8d1928fd4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ArcGIS Software Engineer</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,29 +1851,29 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1186a0273eb12d27</t>
+          <t>https://www.indeed.com/viewjob?jk=b2a1afc987319b9a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Sr. ETL/Python Developer)</t>
+          <t>Site Reliability Engineer (Cloud Enablement)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RCR Technology</t>
+          <t>Flexera</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1882,116 +1882,116 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4527effc81797bda</t>
+          <t>https://www.indeed.com/viewjob?jk=72d1842ef3999b1d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Support Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Illumen Group</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Stafford, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, Databricks, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92cd661cf5a17182</t>
+          <t>https://www.indeed.com/viewjob?jk=a5acecf0e4305790</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI/ML Engineering Intern (Summer 2026)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd3431b51acd4b5</t>
+          <t>https://www.indeed.com/viewjob?jk=9f177704478aadbe</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>ArcGIS Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AllCloud</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, API Gateway, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a0467416d94bb26</t>
+          <t>https://www.indeed.com/viewjob?jk=1186a0273eb12d27</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Development Engineer II (C#/.NET, Azure)</t>
+          <t>AI/ML Engineering Intern (Summer 2026)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,42 +2026,42 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>Redshift, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6c902472d880e18</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd3431b51acd4b5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Banner Health</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8d9928392bc7529</t>
+          <t>https://www.indeed.com/viewjob?jk=8a0467416d94bb26</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ventura Foods</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a527d30b5c00d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=6e93266a037e0c18</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Senior Data Engineer (Sr. ETL/Python Developer)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>RCR Technology</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62c75d5f8fbde70d</t>
+          <t>https://www.indeed.com/viewjob?jk=4527effc81797bda</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Support Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Medeloop</t>
+          <t>Illumen Group</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Stafford, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, Athena, S3, Databricks, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a81ed0b08e8f07f7</t>
+          <t>https://www.indeed.com/viewjob?jk=92cd661cf5a17182</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Backend Engineer II</t>
+          <t>DevOps &amp; AI Automation Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae2342b890625b11</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6b296a0ce2f382</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Software Development Engineer II (C#/.NET, Azure)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RJW Logistics</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef58fd9ad5dd15ff</t>
+          <t>https://www.indeed.com/viewjob?jk=b6c902472d880e18</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (171680)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Banner Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a860d07867e70be2</t>
+          <t>https://www.indeed.com/viewjob?jk=c8d9928392bc7529</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ff91e3d3905a73</t>
+          <t>https://www.indeed.com/viewjob?jk=1a527d30b5c00d7d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Cloud Automation Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>Vantage Bank Texas</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cbee15ac5e5d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f9ce6ba5f081b9</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,67 +2386,67 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf17dcf23ea3201f</t>
+          <t>https://www.indeed.com/viewjob?jk=62c75d5f8fbde70d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Holland &amp; Knight</t>
+          <t>Medeloop</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brandon, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abb3ed211255b11</t>
+          <t>https://www.indeed.com/viewjob?jk=a81ed0b08e8f07f7</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Backend Engineer II</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,207 +2456,207 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766f2f5e9a7201f1</t>
+          <t>https://www.indeed.com/viewjob?jk=ae2342b890625b11</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - III</t>
+          <t>Full Stack Developer (JS/TS, AWS)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>Low Associates</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>South Bend, IN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
+          <t>AWS, Lambda, API Gateway, IAM, Azure, GCP, Cloud Storage, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16ddbf61e3ea0b92</t>
+          <t>https://www.indeed.com/viewjob?jk=45727b1c951a0e5a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - II</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>RJW Logistics</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43bfe7ca1f6eddb7</t>
+          <t>https://www.indeed.com/viewjob?jk=ef58fd9ad5dd15ff</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - I</t>
+          <t>Machine Learning Engineer (171680)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2124d09922154cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=a860d07867e70be2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>GIS Support Engineer</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e24b40c19089ff90</t>
+          <t>https://www.indeed.com/viewjob?jk=30ff91e3d3905a73</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer - Dallas, TX</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865a46cfbc7cc3f4</t>
+          <t>https://www.indeed.com/viewjob?jk=17cbee15ac5e5d6a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766ed066e436eb0c</t>
+          <t>https://www.indeed.com/viewjob?jk=bf17dcf23ea3201f</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c080bdfd0f5497</t>
+          <t>https://www.indeed.com/viewjob?jk=766ed066e436eb0c</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01aefad23a0eebfc</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c080bdfd0f5497</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b79af965edb52688</t>
+          <t>https://www.indeed.com/viewjob?jk=01aefad23a0eebfc</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe099d836f48656</t>
+          <t>https://www.indeed.com/viewjob?jk=b79af965edb52688</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8756dcda438f6959</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe099d836f48656</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c70b98cc7f980bc</t>
+          <t>https://www.indeed.com/viewjob?jk=8756dcda438f6959</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa8671f82044c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=3c70b98cc7f980bc</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bddaca0e62ee366</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa8671f82044c5a</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4177c81ac5d66b2d</t>
+          <t>https://www.indeed.com/viewjob?jk=9bddaca0e62ee366</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02c32fad4b2ac01d</t>
+          <t>https://www.indeed.com/viewjob?jk=4177c81ac5d66b2d</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=964bc462945e695c</t>
+          <t>https://www.indeed.com/viewjob?jk=02c32fad4b2ac01d</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7beb81f1fe47bc19</t>
+          <t>https://www.indeed.com/viewjob?jk=964bc462945e695c</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3c6d71a96ee8e3e</t>
+          <t>https://www.indeed.com/viewjob?jk=7beb81f1fe47bc19</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e48e8aee6232ce</t>
+          <t>https://www.indeed.com/viewjob?jk=a3c6d71a96ee8e3e</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26cc56905b519e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=85e48e8aee6232ce</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=416163a4caa0a101</t>
+          <t>https://www.indeed.com/viewjob?jk=26cc56905b519e4a</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b314b34d858c384</t>
+          <t>https://www.indeed.com/viewjob?jk=416163a4caa0a101</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d26c232b74cd8f7</t>
+          <t>https://www.indeed.com/viewjob?jk=6b314b34d858c384</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0461589d526a9a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=3d26c232b74cd8f7</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a01db0a34a1698ca</t>
+          <t>https://www.indeed.com/viewjob?jk=0461589d526a9a5c</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d2979409c83f2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=a01db0a34a1698ca</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19292a33d87f477b</t>
+          <t>https://www.indeed.com/viewjob?jk=1d2979409c83f2a4</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c45b67d1782f41c</t>
+          <t>https://www.indeed.com/viewjob?jk=19292a33d87f477b</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e0fdb2d1d8365c</t>
+          <t>https://www.indeed.com/viewjob?jk=1c45b67d1782f41c</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50082798bb6a8951</t>
+          <t>https://www.indeed.com/viewjob?jk=28e0fdb2d1d8365c</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff4b550996831857</t>
+          <t>https://www.indeed.com/viewjob?jk=50082798bb6a8951</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7a140e56c36bd8e</t>
+          <t>https://www.indeed.com/viewjob?jk=ff4b550996831857</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7177f3e2822442b8</t>
+          <t>https://www.indeed.com/viewjob?jk=e7a140e56c36bd8e</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f786bfc01c412f</t>
+          <t>https://www.indeed.com/viewjob?jk=7177f3e2822442b8</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c31b397857f539a8</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f786bfc01c412f</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2a59301082a549</t>
+          <t>https://www.indeed.com/viewjob?jk=c31b397857f539a8</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd442131644c2ae</t>
+          <t>https://www.indeed.com/viewjob?jk=df2a59301082a549</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac49610be5f7c22</t>
+          <t>https://www.indeed.com/viewjob?jk=abd442131644c2ae</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd327a6115535e1</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac49610be5f7c22</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fdf53b11b630cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd327a6115535e1</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7ce02753b98a7f</t>
+          <t>https://www.indeed.com/viewjob?jk=6fdf53b11b630cb7</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48e68a3d2a669f96</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7ce02753b98a7f</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=715a8a81ec1663c0</t>
+          <t>https://www.indeed.com/viewjob?jk=48e68a3d2a669f96</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c61b7a4534477b1</t>
+          <t>https://www.indeed.com/viewjob?jk=715a8a81ec1663c0</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=714987b40a626f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=8c61b7a4534477b1</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc2483f2dc10aa24</t>
+          <t>https://www.indeed.com/viewjob?jk=714987b40a626f2c</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f3867fb9d5fca1</t>
+          <t>https://www.indeed.com/viewjob?jk=bc2483f2dc10aa24</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e14441426c0e5912</t>
+          <t>https://www.indeed.com/viewjob?jk=41f3867fb9d5fca1</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de87959267d1c1a1</t>
+          <t>https://www.indeed.com/viewjob?jk=e14441426c0e5912</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157307b309906617</t>
+          <t>https://www.indeed.com/viewjob?jk=de87959267d1c1a1</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd2a0badba0820e7</t>
+          <t>https://www.indeed.com/viewjob?jk=157307b309906617</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a1077e0bf1888ba</t>
+          <t>https://www.indeed.com/viewjob?jk=fd2a0badba0820e7</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c0316b1d2e51b16</t>
+          <t>https://www.indeed.com/viewjob?jk=3a1077e0bf1888ba</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91b58529dba10c91</t>
+          <t>https://www.indeed.com/viewjob?jk=8c0316b1d2e51b16</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbe26208741cfd88</t>
+          <t>https://www.indeed.com/viewjob?jk=91b58529dba10c91</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4deeb487a12f72a</t>
+          <t>https://www.indeed.com/viewjob?jk=bbe26208741cfd88</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Engineer II, AWS Connect</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d1c8d1b8c5a8bd</t>
+          <t>https://www.indeed.com/viewjob?jk=a4deeb487a12f72a</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>adonis</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5621c4e542d4639</t>
+          <t>https://www.indeed.com/viewjob?jk=c20056a5b9ffca80</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Developer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>cloudteam</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, Oozie, YARN</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38299c9de7d6d6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=6ae648cd8fe57362</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>NetApp Emerging Talent - Entry Level Software Engineer (Cloud Storage)</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Holland &amp; Knight</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Brandon, FL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, Airflow, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e07865da969c4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=3abb3ed211255b11</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ba9654fc14bac7</t>
+          <t>https://www.indeed.com/viewjob?jk=766f2f5e9a7201f1</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Cloud Software Engineer 3 - III</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Customers Bank</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Polars, Snowflake, Oracle, SQL Server, Dimensional Modeling, Power BI</t>
+          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da13b88eee9db315</t>
+          <t>https://www.indeed.com/viewjob?jk=16ddbf61e3ea0b92</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>DevOps Security Engineer</t>
+          <t>Cloud Software Engineer 3 - II</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Decentralized Masters</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45f290af989badc3</t>
+          <t>https://www.indeed.com/viewjob?jk=43bfe7ca1f6eddb7</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Cloud Software Engineer 3 - I</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>BillGO, Inc.</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, DynamoDB, Star Schema, ELT, Tableau, GitHub Actions</t>
+          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69713d6be44a4b67</t>
+          <t>https://www.indeed.com/viewjob?jk=2124d09922154cc4</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GIS Support Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b635a4480602f9</t>
+          <t>https://www.indeed.com/viewjob?jk=e24b40c19089ff90</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform</t>
+          <t>Data Engineer - Dallas, TX</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Rocket Close</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fce91f5c39bd4ed</t>
+          <t>https://www.indeed.com/viewjob?jk=865a46cfbc7cc3f4</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>NetApp Emerging Talent - Software Engineer (Cloud Storage)</t>
+          <t>Engineer II, AWS Connect</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, MongoDB, Cassandra, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b72bdc255bbf6f8</t>
+          <t>https://www.indeed.com/viewjob?jk=16d1c8d1b8c5a8bd</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>adonis</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Databricks Lakehouse, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6e81f16ad428334</t>
+          <t>https://www.indeed.com/viewjob?jk=e5621c4e542d4639</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026009 - Software Engineer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>John Deere</t>
+          <t>Customers Bank</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Moline, IL, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,42 +4896,42 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Scala, PostgreSQL, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Databricks, Scala, Polars, Snowflake, Oracle, SQL Server, Dimensional Modeling, Power BI</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e1a444de87fc2c</t>
+          <t>https://www.indeed.com/viewjob?jk=da13b88eee9db315</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Security Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Metropolitan Companies</t>
+          <t>Decentralized Masters</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Wyomissing, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,32 +4941,32 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12c03c3bb6ce8c38</t>
+          <t>https://www.indeed.com/viewjob?jk=45f290af989badc3</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer (Onsite)</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Colony Brands</t>
+          <t>BillGO, Inc.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Monroe, WI, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, DynamoDB, Star Schema, ELT, Tableau, GitHub Actions</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,67 +4976,67 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f935defc4a70c87e</t>
+          <t>https://www.indeed.com/viewjob?jk=69713d6be44a4b67</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>RNGD</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a3ecae4bdb7e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=10b635a4480602f9</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>MachineMetrics, Inc.</t>
+          <t>Rocket Close</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, RDS, Scala, Kafka, PostgreSQL, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,32 +5046,32 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80173e5fca484063</t>
+          <t>https://www.indeed.com/viewjob?jk=9fce91f5c39bd4ed</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Microsoft Modern Work Consultant</t>
+          <t>Senior Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>RDS, Azure, Databricks, Scala, Databricks Lakehouse, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,59 +5081,59 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11d034c0b8905492</t>
+          <t>https://www.indeed.com/viewjob?jk=a6e81f16ad428334</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Supervisor, Software Engineering</t>
+          <t>2026009 - Software Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Energy Systems Group</t>
+          <t>John Deere</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Newburgh, IN, US USA</t>
+          <t>Moline, IL, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Scala, PostgreSQL, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c197f77bdf171e6</t>
+          <t>https://www.indeed.com/viewjob?jk=45e1a444de87fc2c</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>Sr. Software Engineer II</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4296ca379ce33eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=04a1d1c06680e371</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Cloud Data Engineer (Onsite)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Colony Brands</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Monroe, WI, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f710f05a18efb3e1</t>
+          <t>https://www.indeed.com/viewjob?jk=f935defc4a70c87e</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ad148596751872e</t>
+          <t>https://www.indeed.com/viewjob?jk=1a31dfca06d884ad</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Angular / JAVA Full Stack Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcfd60088aef43d3</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b1cb632eed3bcb</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085872f73883326c</t>
+          <t>https://www.indeed.com/viewjob?jk=ec090a150db0c5f8</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,34 +5316,34 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa79af047e73dc3e</t>
+          <t>https://www.indeed.com/viewjob?jk=3fe79bacd5e58f55</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,29 +5351,29 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34987f860a590c53</t>
+          <t>https://www.indeed.com/viewjob?jk=f09282ebd98b3570</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Cloud Solution Architect</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Applied Information Sciences</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5386,15 +5386,715 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa1d73f24fc01af9</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Cloud Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>WILLDAN GROUP</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e4150c94fe908c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Metropolitan Companies</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Wyomissing, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12c03c3bb6ce8c38</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>RNGD</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Metairie, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1a3ecae4bdb7e4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>MachineMetrics, Inc.</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, RDS, Scala, Kafka, PostgreSQL, Terraform, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80173e5fca484063</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Microsoft Modern Work Consultant</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Citrin Cooperman</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Carlsbad, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=11d034c0b8905492</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Supervisor, Software Engineering</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Energy Systems Group</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Newburgh, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c197f77bdf171e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Claims Data Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4296ca379ce33eb3</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Sr Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f710f05a18efb3e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Sr Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>MO, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ad148596751872e</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Angular / JAVA Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Charles Schwab</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fcfd60088aef43d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>CapTech Consulting</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=085872f73883326c</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>CapTech Consulting</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa79af047e73dc3e</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>CapTech Consulting</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34987f860a590c53</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>IS Technical Specialist</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Huntington Bank</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=757269b719268379</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>IS Technical Specialist</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Huntington Bank</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=609b33430f9df835</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>IS Technical Specialist</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Huntington Bank</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef377da6b1a8bbfd</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>IS Technical Specialist</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Huntington Bank</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6aea6ee79779b03b</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>IS Technical Specialist</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Huntington Bank</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Fairlawn, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da070db6e9060b88</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>IS Technical Specialist</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Huntington Bank</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63d188ef103369c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Cloud Solution Architect</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Applied Information Sciences</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
           <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
+      <c r="F162" t="inlineStr">
         <is>
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
+      <c r="G162" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f47703eb8d2843d8</t>
         </is>

--- a/results/job_matches_2026-04-15.xlsx
+++ b/results/job_matches_2026-04-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G162"/>
+  <dimension ref="A1:G157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Software Engineer III - AWS Glue</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4478c55d459f6590</t>
+          <t>https://www.indeed.com/viewjob?jk=5f1496d3a0b45451</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud Engineer-Associate-Dallas</t>
+          <t>Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS, Spark</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=452922c279cc36e9</t>
+          <t>https://www.indeed.com/viewjob?jk=8a711c2fcb36b6cf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS Glue</t>
+          <t>Sr. Data Engineer (ON-SITE)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,137 +566,137 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f1496d3a0b45451</t>
+          <t>https://www.indeed.com/viewjob?jk=038b96d69cecd888</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer 2026 - US,UK</t>
+          <t>Information Technology - BI Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>TCC Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fishers, IN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d01fdc4061dd2a</t>
+          <t>https://www.indeed.com/viewjob?jk=ca19ad92abde46c9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer/Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a711c2fcb36b6cf</t>
+          <t>https://www.indeed.com/viewjob?jk=cb699a2e3bdbb440</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (ON-SITE)</t>
+          <t>Data Warehouse Analyst Seniors: Cloud Engineering</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Equinox</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, Snowflake, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=038b96d69cecd888</t>
+          <t>https://www.indeed.com/viewjob?jk=d87aa04a7733264b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Information Technology - BI Developer</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TCC Verizon Authorized Retailer</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fishers, IN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca19ad92abde46c9</t>
+          <t>https://www.indeed.com/viewjob?jk=574e10b9b787dc54</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb699a2e3bdbb440</t>
+          <t>https://www.indeed.com/viewjob?jk=ac615cac5200efc9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Warehouse Analyst Seniors: Cloud Engineering</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, ETL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d87aa04a7733264b</t>
+          <t>https://www.indeed.com/viewjob?jk=8a7de03320b3d487</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=574e10b9b787dc54</t>
+          <t>https://www.indeed.com/viewjob?jk=df1418000450ecdb</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac615cac5200efc9</t>
+          <t>https://www.indeed.com/viewjob?jk=6df75aab0012c038</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Full Stack AI Engineer</t>
+          <t>Operations Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Stifel</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,94 +881,94 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a7de03320b3d487</t>
+          <t>https://www.indeed.com/viewjob?jk=d061193f264addea</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Full Stack AI Engineer</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df1418000450ecdb</t>
+          <t>https://www.indeed.com/viewjob?jk=f99034f0e149e6e6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Full Stack AI Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Ignite Insurance Systems</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6df75aab0012c038</t>
+          <t>https://www.indeed.com/viewjob?jk=560d14506d8aa36b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
+          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f99034f0e149e6e6</t>
+          <t>https://www.indeed.com/viewjob?jk=e99b4467c3c6aa55</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Architect I</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ignite Insurance Systems</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Azure, Data Factory, Databricks</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=560d14506d8aa36b</t>
+          <t>https://www.indeed.com/viewjob?jk=c6d97da40a8da560</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Azure, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,129 +1056,129 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99b4467c3c6aa55</t>
+          <t>https://www.indeed.com/viewjob?jk=fcd17ae9e035b9a9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Architect I</t>
+          <t>Sr. Data Engineer (Azure/Databricks/Python)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>loanDepot</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Azure, Data Factory, Databricks</t>
+          <t>Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6d97da40a8da560</t>
+          <t>https://www.indeed.com/viewjob?jk=d4b1df13928e079d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Operations Engineer (Cloud)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Stifel</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d061193f264addea</t>
+          <t>https://www.indeed.com/viewjob?jk=aa4d88005315e7ba</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Database and Dashboard Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Azure, GCP, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcd17ae9e035b9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=fee5a2d73882379c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Snowflake Data Engineer (contract)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f193a5a41b80d59d</t>
+          <t>https://www.indeed.com/viewjob?jk=23956751504b8384</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Azure/Databricks/Python)</t>
+          <t>Senior Solution Architect, Enterprise - Eastern Time Zone</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>loanDepot</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,19 +1231,19 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4b1df13928e079d</t>
+          <t>https://www.indeed.com/viewjob?jk=da8ab35096a74f07</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer- OrderlyMeds</t>
+          <t>Solution Architect, Enterprise - Eastern Time Zone</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>OrderlyMeds</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f563cb4be7b9221</t>
+          <t>https://www.indeed.com/viewjob?jk=3f33106731db1775</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Solution Architect, Enterprise - Eastern Time Zone</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4d88005315e7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=90d356ab99a57489</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Database and Dashboard Developer</t>
+          <t>Solution Architect, Enterprise - Eastern Time Zone</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,29 +1326,29 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Oracle</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fee5a2d73882379c</t>
+          <t>https://www.indeed.com/viewjob?jk=15664632526fabdb</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer (contract)</t>
+          <t>Senior Solution Architect, Enterprise - Eastern Time Zone</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23956751504b8384</t>
+          <t>https://www.indeed.com/viewjob?jk=507830f63a6d47c9</t>
         </is>
       </c>
     </row>
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da8ab35096a74f07</t>
+          <t>https://www.indeed.com/viewjob?jk=98d7971656e73b43</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Solution Architect, Enterprise - Eastern Time Zone</t>
+          <t>Data &amp; AI Governance Officer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Vantage Bank Texas</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, Glue, S3, RDS, Azure, Data Factory, Databricks, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f33106731db1775</t>
+          <t>https://www.indeed.com/viewjob?jk=5c469b183725fde1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Solution Architect, Enterprise - Eastern Time Zone</t>
+          <t>Senior Data &amp; AI Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Olson Kundig</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90d356ab99a57489</t>
+          <t>https://www.indeed.com/viewjob?jk=d831e0d8e2c5553f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Solution Architect, Enterprise - Eastern Time Zone</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15664632526fabdb</t>
+          <t>https://www.indeed.com/viewjob?jk=b2a1afc987319b9a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Solution Architect, Enterprise - Eastern Time Zone</t>
+          <t>Senior, Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Cassandra</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,19 +1546,19 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=507830f63a6d47c9</t>
+          <t>https://www.indeed.com/viewjob?jk=3fcd1c4e67959eea</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Solution Architect, Enterprise - Eastern Time Zone</t>
+          <t>Site Reliability Engineer (Cloud Enablement)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Flexera</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1567,11 +1567,11 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98d7971656e73b43</t>
+          <t>https://www.indeed.com/viewjob?jk=72d1842ef3999b1d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data &amp; AI Governance Officer</t>
+          <t>AI Intern</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Vantage Bank Texas</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Data Factory, Databricks, ELT, Power BI, Tableau</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, dbt, MLflow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c469b183725fde1</t>
+          <t>https://www.indeed.com/viewjob?jk=7bea47ac5f13bd1f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Olson Kundig</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d831e0d8e2c5553f</t>
+          <t>https://www.indeed.com/viewjob?jk=93144249a4967543</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior, Software Engineer</t>
+          <t>Research Engineer II</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Bryan, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Cassandra</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fcd1c4e67959eea</t>
+          <t>https://www.indeed.com/viewjob?jk=09b3207da19db4ee</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Intern</t>
+          <t>Research Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Bryan, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, dbt, MLflow</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bea47ac5f13bd1f</t>
+          <t>https://www.indeed.com/viewjob?jk=bb85a1b8d1928fd4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93144249a4967543</t>
+          <t>https://www.indeed.com/viewjob?jk=a5acecf0e4305790</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Research Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bryan, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b3207da19db4ee</t>
+          <t>https://www.indeed.com/viewjob?jk=9f177704478aadbe</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Research Engineer II</t>
+          <t>ArcGIS Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bryan, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
+          <t>AWS, API Gateway, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb85a1b8d1928fd4</t>
+          <t>https://www.indeed.com/viewjob?jk=1186a0273eb12d27</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ventura Foods</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,19 +1861,19 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2a1afc987319b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=6e93266a037e0c18</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (Cloud Enablement)</t>
+          <t>Senior Data Engineer (Sr. ETL/Python Developer)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Flexera</t>
+          <t>RCR Technology</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1882,143 +1882,143 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72d1842ef3999b1d</t>
+          <t>https://www.indeed.com/viewjob?jk=4527effc81797bda</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Data Support Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Illumen Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Stafford, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, Glue, Redshift, Athena, S3, Databricks, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5acecf0e4305790</t>
+          <t>https://www.indeed.com/viewjob?jk=92cd661cf5a17182</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloudera Public Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Plano, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f177704478aadbe</t>
+          <t>https://www.indeed.com/viewjob?jk=ce7428fbc9c89fa9</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ArcGIS Software Engineer</t>
+          <t>AI/ML Engineering Intern (Summer 2026)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
+          <t>Redshift, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1186a0273eb12d27</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd3431b51acd4b5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI/ML Engineering Intern (Summer 2026)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,29 +2026,29 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd3431b51acd4b5</t>
+          <t>https://www.indeed.com/viewjob?jk=8a0467416d94bb26</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>DevOps &amp; AI Automation Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AllCloud</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a0467416d94bb26</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6b296a0ce2f382</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer II (C#/.NET, Azure)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ventura Foods</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,42 +2096,42 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e93266a037e0c18</t>
+          <t>https://www.indeed.com/viewjob?jk=b6c902472d880e18</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Sr. ETL/Python Developer)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RCR Technology</t>
+          <t>Banner Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4527effc81797bda</t>
+          <t>https://www.indeed.com/viewjob?jk=c8d9928392bc7529</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Support Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Illumen Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Stafford, VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, Databricks, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92cd661cf5a17182</t>
+          <t>https://www.indeed.com/viewjob?jk=1a527d30b5c00d7d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DevOps &amp; AI Automation Engineer</t>
+          <t>Cloud Automation Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vantage Bank Texas</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6b296a0ce2f382</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f9ce6ba5f081b9</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Development Engineer II (C#/.NET, Azure)</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6c902472d880e18</t>
+          <t>https://www.indeed.com/viewjob?jk=62c75d5f8fbde70d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Banner Health</t>
+          <t>Medeloop</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8d9928392bc7529</t>
+          <t>https://www.indeed.com/viewjob?jk=a81ed0b08e8f07f7</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Backend Engineer II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a527d30b5c00d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=ae2342b890625b11</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud Automation Engineer</t>
+          <t>Full Stack Developer (JS/TS, AWS)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Vantage Bank Texas</t>
+          <t>Low Associates</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>South Bend, IN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, API Gateway, IAM, Azure, GCP, Cloud Storage, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f9ce6ba5f081b9</t>
+          <t>https://www.indeed.com/viewjob?jk=45727b1c951a0e5a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Machine Learning Engineer (171680)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62c75d5f8fbde70d</t>
+          <t>https://www.indeed.com/viewjob?jk=a860d07867e70be2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Medeloop</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a81ed0b08e8f07f7</t>
+          <t>https://www.indeed.com/viewjob?jk=30ff91e3d3905a73</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Backend Engineer II</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,244 +2446,244 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae2342b890625b11</t>
+          <t>https://www.indeed.com/viewjob?jk=17cbee15ac5e5d6a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Full Stack Developer (JS/TS, AWS)</t>
+          <t>AI Cloud Security and Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Low Associates</t>
+          <t>Troutman Pepper Locke</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>South Bend, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, GCP, Cloud Storage, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45727b1c951a0e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=04325b074eb62665</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>RJW Logistics</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef58fd9ad5dd15ff</t>
+          <t>https://www.indeed.com/viewjob?jk=c20056a5b9ffca80</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (171680)</t>
+          <t>Analytics Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>cloudteam</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, Oozie, YARN</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a860d07867e70be2</t>
+          <t>https://www.indeed.com/viewjob?jk=6ae648cd8fe57362</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>Holland &amp; Knight</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Brandon, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, Airflow, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ff91e3d3905a73</t>
+          <t>https://www.indeed.com/viewjob?jk=3abb3ed211255b11</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cbee15ac5e5d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=766f2f5e9a7201f1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Cloud Software Engineer 3 - III</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf17dcf23ea3201f</t>
+          <t>https://www.indeed.com/viewjob?jk=16ddbf61e3ea0b92</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Cloud Software Engineer 3 - II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766ed066e436eb0c</t>
+          <t>https://www.indeed.com/viewjob?jk=43bfe7ca1f6eddb7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Cloud Software Engineer 3 - I</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c080bdfd0f5497</t>
+          <t>https://www.indeed.com/viewjob?jk=2124d09922154cc4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>GIS Support Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01aefad23a0eebfc</t>
+          <t>https://www.indeed.com/viewjob?jk=e24b40c19089ff90</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Data Engineer - Dallas, TX</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b79af965edb52688</t>
+          <t>https://www.indeed.com/viewjob?jk=865a46cfbc7cc3f4</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe099d836f48656</t>
+          <t>https://www.indeed.com/viewjob?jk=766ed066e436eb0c</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8756dcda438f6959</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c080bdfd0f5497</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c70b98cc7f980bc</t>
+          <t>https://www.indeed.com/viewjob?jk=01aefad23a0eebfc</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa8671f82044c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=b79af965edb52688</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bddaca0e62ee366</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe099d836f48656</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4177c81ac5d66b2d</t>
+          <t>https://www.indeed.com/viewjob?jk=8756dcda438f6959</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02c32fad4b2ac01d</t>
+          <t>https://www.indeed.com/viewjob?jk=3c70b98cc7f980bc</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=964bc462945e695c</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa8671f82044c5a</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7beb81f1fe47bc19</t>
+          <t>https://www.indeed.com/viewjob?jk=9bddaca0e62ee366</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3c6d71a96ee8e3e</t>
+          <t>https://www.indeed.com/viewjob?jk=4177c81ac5d66b2d</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e48e8aee6232ce</t>
+          <t>https://www.indeed.com/viewjob?jk=02c32fad4b2ac01d</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26cc56905b519e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=964bc462945e695c</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=416163a4caa0a101</t>
+          <t>https://www.indeed.com/viewjob?jk=7beb81f1fe47bc19</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b314b34d858c384</t>
+          <t>https://www.indeed.com/viewjob?jk=a3c6d71a96ee8e3e</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d26c232b74cd8f7</t>
+          <t>https://www.indeed.com/viewjob?jk=85e48e8aee6232ce</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0461589d526a9a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=26cc56905b519e4a</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a01db0a34a1698ca</t>
+          <t>https://www.indeed.com/viewjob?jk=416163a4caa0a101</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d2979409c83f2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=6b314b34d858c384</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19292a33d87f477b</t>
+          <t>https://www.indeed.com/viewjob?jk=3d26c232b74cd8f7</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c45b67d1782f41c</t>
+          <t>https://www.indeed.com/viewjob?jk=0461589d526a9a5c</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e0fdb2d1d8365c</t>
+          <t>https://www.indeed.com/viewjob?jk=a01db0a34a1698ca</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50082798bb6a8951</t>
+          <t>https://www.indeed.com/viewjob?jk=1d2979409c83f2a4</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff4b550996831857</t>
+          <t>https://www.indeed.com/viewjob?jk=19292a33d87f477b</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7a140e56c36bd8e</t>
+          <t>https://www.indeed.com/viewjob?jk=1c45b67d1782f41c</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7177f3e2822442b8</t>
+          <t>https://www.indeed.com/viewjob?jk=28e0fdb2d1d8365c</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f786bfc01c412f</t>
+          <t>https://www.indeed.com/viewjob?jk=50082798bb6a8951</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c31b397857f539a8</t>
+          <t>https://www.indeed.com/viewjob?jk=ff4b550996831857</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2a59301082a549</t>
+          <t>https://www.indeed.com/viewjob?jk=e7a140e56c36bd8e</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd442131644c2ae</t>
+          <t>https://www.indeed.com/viewjob?jk=7177f3e2822442b8</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac49610be5f7c22</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f786bfc01c412f</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd327a6115535e1</t>
+          <t>https://www.indeed.com/viewjob?jk=c31b397857f539a8</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fdf53b11b630cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=df2a59301082a549</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7ce02753b98a7f</t>
+          <t>https://www.indeed.com/viewjob?jk=abd442131644c2ae</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48e68a3d2a669f96</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac49610be5f7c22</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=715a8a81ec1663c0</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd327a6115535e1</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c61b7a4534477b1</t>
+          <t>https://www.indeed.com/viewjob?jk=6fdf53b11b630cb7</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=714987b40a626f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7ce02753b98a7f</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc2483f2dc10aa24</t>
+          <t>https://www.indeed.com/viewjob?jk=48e68a3d2a669f96</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f3867fb9d5fca1</t>
+          <t>https://www.indeed.com/viewjob?jk=715a8a81ec1663c0</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e14441426c0e5912</t>
+          <t>https://www.indeed.com/viewjob?jk=8c61b7a4534477b1</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de87959267d1c1a1</t>
+          <t>https://www.indeed.com/viewjob?jk=714987b40a626f2c</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157307b309906617</t>
+          <t>https://www.indeed.com/viewjob?jk=bc2483f2dc10aa24</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd2a0badba0820e7</t>
+          <t>https://www.indeed.com/viewjob?jk=41f3867fb9d5fca1</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a1077e0bf1888ba</t>
+          <t>https://www.indeed.com/viewjob?jk=e14441426c0e5912</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c0316b1d2e51b16</t>
+          <t>https://www.indeed.com/viewjob?jk=de87959267d1c1a1</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91b58529dba10c91</t>
+          <t>https://www.indeed.com/viewjob?jk=157307b309906617</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbe26208741cfd88</t>
+          <t>https://www.indeed.com/viewjob?jk=fd2a0badba0820e7</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4deeb487a12f72a</t>
+          <t>https://www.indeed.com/viewjob?jk=3a1077e0bf1888ba</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c20056a5b9ffca80</t>
+          <t>https://www.indeed.com/viewjob?jk=8c0316b1d2e51b16</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Analytics Developer</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>cloudteam</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, Oozie, YARN</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ae648cd8fe57362</t>
+          <t>https://www.indeed.com/viewjob?jk=91b58529dba10c91</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Holland &amp; Knight</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Brandon, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abb3ed211255b11</t>
+          <t>https://www.indeed.com/viewjob?jk=bbe26208741cfd88</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766f2f5e9a7201f1</t>
+          <t>https://www.indeed.com/viewjob?jk=a4deeb487a12f72a</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - III</t>
+          <t>Engineer II, AWS Connect</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16ddbf61e3ea0b92</t>
+          <t>https://www.indeed.com/viewjob?jk=16d1c8d1b8c5a8bd</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - II</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Bensenville, IL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43bfe7ca1f6eddb7</t>
+          <t>https://www.indeed.com/viewjob?jk=d6412b42f521215b</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - I</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2124d09922154cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=8a467a1fe4bd409c</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>GIS Support Engineer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e24b40c19089ff90</t>
+          <t>https://www.indeed.com/viewjob?jk=cea257394aa611a9</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Data Engineer - Dallas, TX</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Customers Bank</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, Scala, Polars, Snowflake, Oracle, SQL Server, Dimensional Modeling, Power BI</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865a46cfbc7cc3f4</t>
+          <t>https://www.indeed.com/viewjob?jk=da13b88eee9db315</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Engineer II, AWS Connect</t>
+          <t>DevOps Security Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>Decentralized Masters</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d1c8d1b8c5a8bd</t>
+          <t>https://www.indeed.com/viewjob?jk=45f290af989badc3</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>adonis</t>
+          <t>BillGO, Inc.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, DynamoDB, Star Schema, ELT, Tableau, GitHub Actions</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5621c4e542d4639</t>
+          <t>https://www.indeed.com/viewjob?jk=69713d6be44a4b67</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Customers Bank</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Polars, Snowflake, Oracle, SQL Server, Dimensional Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da13b88eee9db315</t>
+          <t>https://www.indeed.com/viewjob?jk=10b635a4480602f9</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>DevOps Security Engineer</t>
+          <t>Senior Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Decentralized Masters</t>
+          <t>Rocket Close</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,77 +4931,77 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45f290af989badc3</t>
+          <t>https://www.indeed.com/viewjob?jk=9fce91f5c39bd4ed</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>BillGO, Inc.</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, DynamoDB, Star Schema, ELT, Tableau, GitHub Actions</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69713d6be44a4b67</t>
+          <t>https://www.indeed.com/viewjob?jk=1a31dfca06d884ad</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,129 +5011,129 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b635a4480602f9</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b1cb632eed3bcb</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Rocket Close</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fce91f5c39bd4ed</t>
+          <t>https://www.indeed.com/viewjob?jk=ec090a150db0c5f8</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Databricks Lakehouse, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6e81f16ad428334</t>
+          <t>https://www.indeed.com/viewjob?jk=3fe79bacd5e58f55</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026009 - Software Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>John Deere</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Moline, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Scala, PostgreSQL, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e1a444de87fc2c</t>
+          <t>https://www.indeed.com/viewjob?jk=f09282ebd98b3570</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04a1d1c06680e371</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1d73f24fc01af9</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer (Onsite)</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Colony Brands</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Monroe, WI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f935defc4a70c87e</t>
+          <t>https://www.indeed.com/viewjob?jk=7e4150c94fe908c8</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Metropolitan Companies</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Wyomissing, PA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a31dfca06d884ad</t>
+          <t>https://www.indeed.com/viewjob?jk=12c03c3bb6ce8c38</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Cloud Data Engineer (Onsite)</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Colony Brands</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Monroe, WI, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b1cb632eed3bcb</t>
+          <t>https://www.indeed.com/viewjob?jk=f935defc4a70c87e</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>RNGD</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec090a150db0c5f8</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a3ecae4bdb7e4b</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>MachineMetrics, Inc.</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,34 +5316,34 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, RDS, Scala, Kafka, PostgreSQL, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fe79bacd5e58f55</t>
+          <t>https://www.indeed.com/viewjob?jk=80173e5fca484063</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Sr. Software Engineer II</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f09282ebd98b3570</t>
+          <t>https://www.indeed.com/viewjob?jk=04a1d1c06680e371</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst/Associate - New York</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1d73f24fc01af9</t>
+          <t>https://www.indeed.com/viewjob?jk=1dd43ffc6d7fda89</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Supervisor, Software Engineering</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Energy Systems Group</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Newburgh, IN, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,34 +5421,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e4150c94fe908c8</t>
+          <t>https://www.indeed.com/viewjob?jk=9c197f77bdf171e6</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Metropolitan Companies</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Wyomissing, PA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12c03c3bb6ce8c38</t>
+          <t>https://www.indeed.com/viewjob?jk=4296ca379ce33eb3</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>RNGD</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a3ecae4bdb7e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=f710f05a18efb3e1</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MachineMetrics, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, RDS, Scala, Kafka, PostgreSQL, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80173e5fca484063</t>
+          <t>https://www.indeed.com/viewjob?jk=6ad148596751872e</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Microsoft Modern Work Consultant</t>
+          <t>Angular / JAVA Full Stack Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, S3, Azure, GCP, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11d034c0b8905492</t>
+          <t>https://www.indeed.com/viewjob?jk=fcfd60088aef43d3</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Supervisor, Software Engineering</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Energy Systems Group</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Newburgh, IN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,34 +5596,34 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c197f77bdf171e6</t>
+          <t>https://www.indeed.com/viewjob?jk=085872f73883326c</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,34 +5631,34 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4296ca379ce33eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=fa79af047e73dc3e</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f710f05a18efb3e1</t>
+          <t>https://www.indeed.com/viewjob?jk=34987f860a590c53</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>IS Technical Specialist</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,34 +5701,34 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ad148596751872e</t>
+          <t>https://www.indeed.com/viewjob?jk=757269b719268379</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Angular / JAVA Full Stack Engineer</t>
+          <t>IS Technical Specialist</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,34 +5736,34 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcfd60088aef43d3</t>
+          <t>https://www.indeed.com/viewjob?jk=609b33430f9df835</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>IS Technical Specialist</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085872f73883326c</t>
+          <t>https://www.indeed.com/viewjob?jk=ef377da6b1a8bbfd</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>IS Technical Specialist</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,34 +5806,34 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa79af047e73dc3e</t>
+          <t>https://www.indeed.com/viewjob?jk=6aea6ee79779b03b</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>IS Technical Specialist</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Fairlawn, OH, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,17 +5841,17 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34987f860a590c53</t>
+          <t>https://www.indeed.com/viewjob?jk=da070db6e9060b88</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=757269b719268379</t>
+          <t>https://www.indeed.com/viewjob?jk=63d188ef103369c5</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>IS Technical Specialist</t>
+          <t>Cloud Solution Architect</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Applied Information Sciences</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5920,181 +5920,6 @@
         </is>
       </c>
       <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=609b33430f9df835</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>IS Technical Specialist</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef377da6b1a8bbfd</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>IS Technical Specialist</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6aea6ee79779b03b</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>IS Technical Specialist</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Fairlawn, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da070db6e9060b88</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>IS Technical Specialist</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=63d188ef103369c5</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Cloud Solution Architect</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Applied Information Sciences</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f47703eb8d2843d8</t>
         </is>

--- a/results/job_matches_2026-04-15.xlsx
+++ b/results/job_matches_2026-04-15.xlsx
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (ON-SITE)</t>
+          <t>Databricks Data Analyst</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Equinox</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,34 +556,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, Snowflake, DynamoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=038b96d69cecd888</t>
+          <t>https://www.indeed.com/viewjob?jk=ce89a36f70a3941b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Information Technology - BI Developer</t>
+          <t>Sr. Data Engineer (ON-SITE)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TCC Verizon Authorized Retailer</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fishers, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,42 +591,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca19ad92abde46c9</t>
+          <t>https://www.indeed.com/viewjob?jk=038b96d69cecd888</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Information Technology - BI Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>TCC Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Fishers, IN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb699a2e3bdbb440</t>
+          <t>https://www.indeed.com/viewjob?jk=ca19ad92abde46c9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Warehouse Analyst Seniors: Cloud Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, ETL, CI/CD</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d87aa04a7733264b</t>
+          <t>https://www.indeed.com/viewjob?jk=cb699a2e3bdbb440</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Full Stack AI Engineer</t>
+          <t>Data Warehouse Analyst Seniors: Cloud Engineering</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=574e10b9b787dc54</t>
+          <t>https://www.indeed.com/viewjob?jk=d87aa04a7733264b</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac615cac5200efc9</t>
+          <t>https://www.indeed.com/viewjob?jk=574e10b9b787dc54</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a7de03320b3d487</t>
+          <t>https://www.indeed.com/viewjob?jk=ac615cac5200efc9</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df1418000450ecdb</t>
+          <t>https://www.indeed.com/viewjob?jk=8a7de03320b3d487</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6df75aab0012c038</t>
+          <t>https://www.indeed.com/viewjob?jk=df1418000450ecdb</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Operations Engineer (Cloud)</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Stifel</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d061193f264addea</t>
+          <t>https://www.indeed.com/viewjob?jk=6df75aab0012c038</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Senior Ad Ops Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f99034f0e149e6e6</t>
+          <t>https://www.indeed.com/viewjob?jk=f14f238cb8b8c5f1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Operations Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ignite Insurance Systems</t>
+          <t>Stifel</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=560d14506d8aa36b</t>
+          <t>https://www.indeed.com/viewjob?jk=d061193f264addea</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99b4467c3c6aa55</t>
+          <t>https://www.indeed.com/viewjob?jk=f99034f0e149e6e6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Architect I</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Ignite Insurance Systems</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Azure, Data Factory, Databricks</t>
+          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6d97da40a8da560</t>
+          <t>https://www.indeed.com/viewjob?jk=560d14506d8aa36b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Azure, GCP, Scala, Kafka</t>
+          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcd17ae9e035b9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=e99b4467c3c6aa55</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Azure/Databricks/Python)</t>
+          <t>Architect I</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>loanDepot</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Azure, Data Factory, Databricks</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4b1df13928e079d</t>
+          <t>https://www.indeed.com/viewjob?jk=c6d97da40a8da560</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Azure, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4d88005315e7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=fcd17ae9e035b9a9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Database and Dashboard Developer</t>
+          <t>Data Engineer- OrderlyMeds</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>OrderlyMeds</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Oracle</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fee5a2d73882379c</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb2a73a0846955d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer (contract)</t>
+          <t>Sr. Data Engineer (Azure/Databricks/Python)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>loanDepot</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Oracle, PostgreSQL</t>
+          <t>Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23956751504b8384</t>
+          <t>https://www.indeed.com/viewjob?jk=d4b1df13928e079d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Solution Architect, Enterprise - Eastern Time Zone</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da8ab35096a74f07</t>
+          <t>https://www.indeed.com/viewjob?jk=aa4d88005315e7ba</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Solution Architect, Enterprise - Eastern Time Zone</t>
+          <t>Database and Dashboard Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,29 +1256,29 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f33106731db1775</t>
+          <t>https://www.indeed.com/viewjob?jk=fee5a2d73882379c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Solution Architect, Enterprise - Eastern Time Zone</t>
+          <t>Snowflake Data Engineer (contract)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90d356ab99a57489</t>
+          <t>https://www.indeed.com/viewjob?jk=23956751504b8384</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Solution Architect, Enterprise - Eastern Time Zone</t>
+          <t>Java Software Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15664632526fabdb</t>
+          <t>https://www.indeed.com/viewjob?jk=4c2cee659fe1d0db</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Solution Architect, Enterprise - Eastern Time Zone</t>
+          <t>Solution Architect, Enterprise - Eastern Time Zone</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=507830f63a6d47c9</t>
+          <t>https://www.indeed.com/viewjob?jk=3f33106731db1775</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Solution Architect, Enterprise - Eastern Time Zone</t>
+          <t>Solution Architect, Enterprise - Eastern Time Zone</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98d7971656e73b43</t>
+          <t>https://www.indeed.com/viewjob?jk=90d356ab99a57489</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data &amp; AI Governance Officer</t>
+          <t>Solution Architect, Enterprise - Eastern Time Zone</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vantage Bank Texas</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Data Factory, Databricks, ELT, Power BI, Tableau</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c469b183725fde1</t>
+          <t>https://www.indeed.com/viewjob?jk=15664632526fabdb</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Developer</t>
+          <t>Senior Solution Architect, Enterprise - Eastern Time Zone</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Olson Kundig</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d831e0d8e2c5553f</t>
+          <t>https://www.indeed.com/viewjob?jk=507830f63a6d47c9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Senior Solution Architect, Enterprise - Eastern Time Zone</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,94 +1511,94 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2a1afc987319b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=98d7971656e73b43</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior, Software Engineer</t>
+          <t>Data &amp; AI Governance Officer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Vantage Bank Texas</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Cassandra</t>
+          <t>AWS, Glue, S3, RDS, Azure, Data Factory, Databricks, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fcd1c4e67959eea</t>
+          <t>https://www.indeed.com/viewjob?jk=5c469b183725fde1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (Cloud Enablement)</t>
+          <t>Senior Data &amp; AI Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Flexera</t>
+          <t>Olson Kundig</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72d1842ef3999b1d</t>
+          <t>https://www.indeed.com/viewjob?jk=d831e0d8e2c5553f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Intern</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, dbt, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bea47ac5f13bd1f</t>
+          <t>https://www.indeed.com/viewjob?jk=b2a1afc987319b9a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior, Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Cassandra</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93144249a4967543</t>
+          <t>https://www.indeed.com/viewjob?jk=3fcd1c4e67959eea</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Research Engineer II</t>
+          <t>Site Reliability Engineer (Cloud Enablement)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>Flexera</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bryan, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b3207da19db4ee</t>
+          <t>https://www.indeed.com/viewjob?jk=72d1842ef3999b1d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Research Engineer II</t>
+          <t>AI Intern</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bryan, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, dbt, MLflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb85a1b8d1928fd4</t>
+          <t>https://www.indeed.com/viewjob?jk=7bea47ac5f13bd1f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5acecf0e4305790</t>
+          <t>https://www.indeed.com/viewjob?jk=93144249a4967543</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Research Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Bryan, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f177704478aadbe</t>
+          <t>https://www.indeed.com/viewjob?jk=09b3207da19db4ee</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ArcGIS Software Engineer</t>
+          <t>Research Engineer II</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Bryan, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1186a0273eb12d27</t>
+          <t>https://www.indeed.com/viewjob?jk=bb85a1b8d1928fd4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ventura Foods</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e93266a037e0c18</t>
+          <t>https://www.indeed.com/viewjob?jk=a5acecf0e4305790</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Sr. ETL/Python Developer)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RCR Technology</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4527effc81797bda</t>
+          <t>https://www.indeed.com/viewjob?jk=9f177704478aadbe</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Support Engineer</t>
+          <t>ArcGIS Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Illumen Group</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Stafford, VA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, Databricks, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, API Gateway, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92cd661cf5a17182</t>
+          <t>https://www.indeed.com/viewjob?jk=1186a0273eb12d27</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cloudera Public Cloud Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Ventura Foods</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Plano, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce7428fbc9c89fa9</t>
+          <t>https://www.indeed.com/viewjob?jk=6e93266a037e0c18</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI/ML Engineering Intern (Summer 2026)</t>
+          <t>Senior Data Engineer (Sr. ETL/Python Developer)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>RCR Technology</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd3431b51acd4b5</t>
+          <t>https://www.indeed.com/viewjob?jk=4527effc81797bda</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Cloudera Public Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AllCloud</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a0467416d94bb26</t>
+          <t>https://www.indeed.com/viewjob?jk=ce7428fbc9c89fa9</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DevOps &amp; AI Automation Engineer</t>
+          <t>AI/ML Engineering Intern (Summer 2026)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>Redshift, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6b296a0ce2f382</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd3431b51acd4b5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Development Engineer II (C#/.NET, Azure)</t>
+          <t>DevOps &amp; AI Automation Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,42 +2096,42 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6c902472d880e18</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6b296a0ce2f382</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer II (C#/.NET, Azure)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Banner Health</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8d9928392bc7529</t>
+          <t>https://www.indeed.com/viewjob?jk=b6c902472d880e18</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Databricks, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a527d30b5c00d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=1834ddbeb8ec8bb3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cloud Automation Engineer</t>
+          <t>Senior Data Engineer - IICS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Vantage Bank Texas</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f9ce6ba5f081b9</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf36b7e279da791</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>Banner Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62c75d5f8fbde70d</t>
+          <t>https://www.indeed.com/viewjob?jk=c8d9928392bc7529</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Medeloop</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a81ed0b08e8f07f7</t>
+          <t>https://www.indeed.com/viewjob?jk=1a527d30b5c00d7d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Backend Engineer II</t>
+          <t>Cloud Automation Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>Vantage Bank Texas</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae2342b890625b11</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f9ce6ba5f081b9</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Full Stack Developer (JS/TS, AWS)</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Low Associates</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>South Bend, IN, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, GCP, Cloud Storage, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45727b1c951a0e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=62c75d5f8fbde70d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (171680)</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Medeloop</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a860d07867e70be2</t>
+          <t>https://www.indeed.com/viewjob?jk=a81ed0b08e8f07f7</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>Sunbit, Inc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ff91e3d3905a73</t>
+          <t>https://www.indeed.com/viewjob?jk=1444a89356fbe315</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Web Application Architect 3</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>Bloomberg Industry Group</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,42 +2446,42 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cbee15ac5e5d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=7846d03774f71aa5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Cloud Security and Infrastructure Engineer</t>
+          <t>Backend Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Troutman Pepper Locke</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,67 +2491,67 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04325b074eb62665</t>
+          <t>https://www.indeed.com/viewjob?jk=ae2342b890625b11</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
+          <t>Full Stack Developer (JS/TS, AWS)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Low Associates</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>South Bend, IN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, API Gateway, IAM, Azure, GCP, Cloud Storage, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c20056a5b9ffca80</t>
+          <t>https://www.indeed.com/viewjob?jk=45727b1c951a0e5a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Analytics Developer</t>
+          <t>Sr Business Intelligence Developer - Onsite</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>cloudteam</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, Oozie, YARN</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,129 +2561,129 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ae648cd8fe57362</t>
+          <t>https://www.indeed.com/viewjob?jk=ba1611f04cfe11a7</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Machine Learning Engineer (171680)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Holland &amp; Knight</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brandon, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, Airflow, Git</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abb3ed211255b11</t>
+          <t>https://www.indeed.com/viewjob?jk=a860d07867e70be2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766f2f5e9a7201f1</t>
+          <t>https://www.indeed.com/viewjob?jk=30ff91e3d3905a73</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - III</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16ddbf61e3ea0b92</t>
+          <t>https://www.indeed.com/viewjob?jk=17cbee15ac5e5d6a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - II</t>
+          <t>AI Cloud Security and Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>Troutman Pepper Locke</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43bfe7ca1f6eddb7</t>
+          <t>https://www.indeed.com/viewjob?jk=04325b074eb62665</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - I</t>
+          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2124d09922154cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=c20056a5b9ffca80</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>GIS Support Engineer</t>
+          <t>Analytics Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>cloudteam</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, Oozie, YARN</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e24b40c19089ff90</t>
+          <t>https://www.indeed.com/viewjob?jk=6ae648cd8fe57362</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer - Dallas, TX</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Holland &amp; Knight</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Brandon, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, Airflow, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865a46cfbc7cc3f4</t>
+          <t>https://www.indeed.com/viewjob?jk=3abb3ed211255b11</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766ed066e436eb0c</t>
+          <t>https://www.indeed.com/viewjob?jk=766f2f5e9a7201f1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Cloud Software Engineer 3 - III</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c080bdfd0f5497</t>
+          <t>https://www.indeed.com/viewjob?jk=16ddbf61e3ea0b92</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Cloud Software Engineer 3 - II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01aefad23a0eebfc</t>
+          <t>https://www.indeed.com/viewjob?jk=43bfe7ca1f6eddb7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Cloud Software Engineer 3 - I</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b79af965edb52688</t>
+          <t>https://www.indeed.com/viewjob?jk=2124d09922154cc4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>GIS Support Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe099d836f48656</t>
+          <t>https://www.indeed.com/viewjob?jk=e24b40c19089ff90</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Data Engineer - Dallas, TX</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,17 +3006,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8756dcda438f6959</t>
+          <t>https://www.indeed.com/viewjob?jk=865a46cfbc7cc3f4</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c70b98cc7f980bc</t>
+          <t>https://www.indeed.com/viewjob?jk=766ed066e436eb0c</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa8671f82044c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c080bdfd0f5497</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bddaca0e62ee366</t>
+          <t>https://www.indeed.com/viewjob?jk=01aefad23a0eebfc</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4177c81ac5d66b2d</t>
+          <t>https://www.indeed.com/viewjob?jk=b79af965edb52688</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02c32fad4b2ac01d</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe099d836f48656</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=964bc462945e695c</t>
+          <t>https://www.indeed.com/viewjob?jk=8756dcda438f6959</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7beb81f1fe47bc19</t>
+          <t>https://www.indeed.com/viewjob?jk=3c70b98cc7f980bc</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3c6d71a96ee8e3e</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa8671f82044c5a</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e48e8aee6232ce</t>
+          <t>https://www.indeed.com/viewjob?jk=9bddaca0e62ee366</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26cc56905b519e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=4177c81ac5d66b2d</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=416163a4caa0a101</t>
+          <t>https://www.indeed.com/viewjob?jk=02c32fad4b2ac01d</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b314b34d858c384</t>
+          <t>https://www.indeed.com/viewjob?jk=964bc462945e695c</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d26c232b74cd8f7</t>
+          <t>https://www.indeed.com/viewjob?jk=7beb81f1fe47bc19</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0461589d526a9a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=a3c6d71a96ee8e3e</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a01db0a34a1698ca</t>
+          <t>https://www.indeed.com/viewjob?jk=85e48e8aee6232ce</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d2979409c83f2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=26cc56905b519e4a</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19292a33d87f477b</t>
+          <t>https://www.indeed.com/viewjob?jk=416163a4caa0a101</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c45b67d1782f41c</t>
+          <t>https://www.indeed.com/viewjob?jk=6b314b34d858c384</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e0fdb2d1d8365c</t>
+          <t>https://www.indeed.com/viewjob?jk=3d26c232b74cd8f7</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50082798bb6a8951</t>
+          <t>https://www.indeed.com/viewjob?jk=0461589d526a9a5c</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff4b550996831857</t>
+          <t>https://www.indeed.com/viewjob?jk=a01db0a34a1698ca</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7a140e56c36bd8e</t>
+          <t>https://www.indeed.com/viewjob?jk=1d2979409c83f2a4</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7177f3e2822442b8</t>
+          <t>https://www.indeed.com/viewjob?jk=19292a33d87f477b</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f786bfc01c412f</t>
+          <t>https://www.indeed.com/viewjob?jk=1c45b67d1782f41c</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c31b397857f539a8</t>
+          <t>https://www.indeed.com/viewjob?jk=28e0fdb2d1d8365c</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2a59301082a549</t>
+          <t>https://www.indeed.com/viewjob?jk=50082798bb6a8951</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd442131644c2ae</t>
+          <t>https://www.indeed.com/viewjob?jk=ff4b550996831857</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac49610be5f7c22</t>
+          <t>https://www.indeed.com/viewjob?jk=e7a140e56c36bd8e</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd327a6115535e1</t>
+          <t>https://www.indeed.com/viewjob?jk=7177f3e2822442b8</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fdf53b11b630cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f786bfc01c412f</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7ce02753b98a7f</t>
+          <t>https://www.indeed.com/viewjob?jk=c31b397857f539a8</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48e68a3d2a669f96</t>
+          <t>https://www.indeed.com/viewjob?jk=df2a59301082a549</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=715a8a81ec1663c0</t>
+          <t>https://www.indeed.com/viewjob?jk=abd442131644c2ae</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c61b7a4534477b1</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac49610be5f7c22</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=714987b40a626f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd327a6115535e1</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc2483f2dc10aa24</t>
+          <t>https://www.indeed.com/viewjob?jk=6fdf53b11b630cb7</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f3867fb9d5fca1</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7ce02753b98a7f</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e14441426c0e5912</t>
+          <t>https://www.indeed.com/viewjob?jk=48e68a3d2a669f96</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de87959267d1c1a1</t>
+          <t>https://www.indeed.com/viewjob?jk=715a8a81ec1663c0</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157307b309906617</t>
+          <t>https://www.indeed.com/viewjob?jk=8c61b7a4534477b1</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd2a0badba0820e7</t>
+          <t>https://www.indeed.com/viewjob?jk=714987b40a626f2c</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a1077e0bf1888ba</t>
+          <t>https://www.indeed.com/viewjob?jk=bc2483f2dc10aa24</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c0316b1d2e51b16</t>
+          <t>https://www.indeed.com/viewjob?jk=41f3867fb9d5fca1</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91b58529dba10c91</t>
+          <t>https://www.indeed.com/viewjob?jk=e14441426c0e5912</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbe26208741cfd88</t>
+          <t>https://www.indeed.com/viewjob?jk=de87959267d1c1a1</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4deeb487a12f72a</t>
+          <t>https://www.indeed.com/viewjob?jk=157307b309906617</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Engineer II, AWS Connect</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d1c8d1b8c5a8bd</t>
+          <t>https://www.indeed.com/viewjob?jk=fd2a0badba0820e7</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bensenville, IL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6412b42f521215b</t>
+          <t>https://www.indeed.com/viewjob?jk=3a1077e0bf1888ba</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a467a1fe4bd409c</t>
+          <t>https://www.indeed.com/viewjob?jk=8c0316b1d2e51b16</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cea257394aa611a9</t>
+          <t>https://www.indeed.com/viewjob?jk=91b58529dba10c91</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Customers Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Polars, Snowflake, Oracle, SQL Server, Dimensional Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da13b88eee9db315</t>
+          <t>https://www.indeed.com/viewjob?jk=bbe26208741cfd88</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>DevOps Security Engineer</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Decentralized Masters</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45f290af989badc3</t>
+          <t>https://www.indeed.com/viewjob?jk=a4deeb487a12f72a</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Engineer II, AWS Connect</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>BillGO, Inc.</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, DynamoDB, Star Schema, ELT, Tableau, GitHub Actions</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69713d6be44a4b67</t>
+          <t>https://www.indeed.com/viewjob?jk=16d1c8d1b8c5a8bd</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Customers Bank</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Databricks, Scala, Polars, Snowflake, Oracle, SQL Server, Dimensional Modeling, Power BI</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b635a4480602f9</t>
+          <t>https://www.indeed.com/viewjob?jk=da13b88eee9db315</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Rocket Close</t>
+          <t>BillGO, Inc.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, DynamoDB, Star Schema, ELT, Tableau, GitHub Actions</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,32 +4941,32 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fce91f5c39bd4ed</t>
+          <t>https://www.indeed.com/viewjob?jk=69713d6be44a4b67</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,42 +4976,42 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a31dfca06d884ad</t>
+          <t>https://www.indeed.com/viewjob?jk=10b635a4480602f9</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Rocket Close</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b1cb632eed3bcb</t>
+          <t>https://www.indeed.com/viewjob?jk=9fce91f5c39bd4ed</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec090a150db0c5f8</t>
+          <t>https://www.indeed.com/viewjob?jk=1a31dfca06d884ad</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fe79bacd5e58f55</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b1cb632eed3bcb</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f09282ebd98b3570</t>
+          <t>https://www.indeed.com/viewjob?jk=ec090a150db0c5f8</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1d73f24fc01af9</t>
+          <t>https://www.indeed.com/viewjob?jk=3fe79bacd5e58f55</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e4150c94fe908c8</t>
+          <t>https://www.indeed.com/viewjob?jk=f09282ebd98b3570</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Metropolitan Companies</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Wyomissing, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12c03c3bb6ce8c38</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1d73f24fc01af9</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer (Onsite)</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Colony Brands</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Monroe, WI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,17 +5246,17 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f935defc4a70c87e</t>
+          <t>https://www.indeed.com/viewjob?jk=7e4150c94fe908c8</t>
         </is>
       </c>
     </row>
@@ -5268,12 +5268,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>RNGD</t>
+          <t>Metropolitan Companies</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>Wyomissing, PA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a3ecae4bdb7e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=12c03c3bb6ce8c38</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Cloud Data Engineer (Onsite)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>MachineMetrics, Inc.</t>
+          <t>Colony Brands</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Monroe, WI, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, RDS, Scala, Kafka, PostgreSQL, Terraform, Kubernetes, Git</t>
+          <t>AWS, Redshift, RDS, Azure, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80173e5fca484063</t>
+          <t>https://www.indeed.com/viewjob?jk=f935defc4a70c87e</t>
         </is>
       </c>
     </row>
@@ -5543,17 +5543,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Angular / JAVA Full Stack Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcfd60088aef43d3</t>
+          <t>https://www.indeed.com/viewjob?jk=085872f73883326c</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085872f73883326c</t>
+          <t>https://www.indeed.com/viewjob?jk=fa79af047e73dc3e</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa79af047e73dc3e</t>
+          <t>https://www.indeed.com/viewjob?jk=34987f860a590c53</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>IS Technical Specialist</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,17 +5666,17 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34987f860a590c53</t>
+          <t>https://www.indeed.com/viewjob?jk=757269b719268379</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=757269b719268379</t>
+          <t>https://www.indeed.com/viewjob?jk=609b33430f9df835</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609b33430f9df835</t>
+          <t>https://www.indeed.com/viewjob?jk=ef377da6b1a8bbfd</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef377da6b1a8bbfd</t>
+          <t>https://www.indeed.com/viewjob?jk=6aea6ee79779b03b</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Fairlawn, OH, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aea6ee79779b03b</t>
+          <t>https://www.indeed.com/viewjob?jk=da070db6e9060b88</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Fairlawn, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da070db6e9060b88</t>
+          <t>https://www.indeed.com/viewjob?jk=63d188ef103369c5</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>IS Technical Specialist</t>
+          <t>Software Engineer I - Full Stack</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,17 +5876,17 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, YARN, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63d188ef103369c5</t>
+          <t>https://www.indeed.com/viewjob?jk=e317b1b40c2e7beb</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-15.xlsx
+++ b/results/job_matches_2026-04-15.xlsx
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS Glue</t>
+          <t>Analytics Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Infoverity</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f1496d3a0b45451</t>
+          <t>https://www.indeed.com/viewjob?jk=ca5a94e3ea76c9da</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer/Data Scientist</t>
+          <t>Software Engineer III - AWS Glue</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a711c2fcb36b6cf</t>
+          <t>https://www.indeed.com/viewjob?jk=5f1496d3a0b45451</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Databricks Data Analyst</t>
+          <t>Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,17 +556,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce89a36f70a3941b</t>
+          <t>https://www.indeed.com/viewjob?jk=8a711c2fcb36b6cf</t>
         </is>
       </c>
     </row>
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Information Technology - BI Developer</t>
+          <t>Databricks Data Analyst</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TCC Verizon Authorized Retailer</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fishers, IN, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca19ad92abde46c9</t>
+          <t>https://www.indeed.com/viewjob?jk=ce89a36f70a3941b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Information Technology - BI Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>TCC Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Fishers, IN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb699a2e3bdbb440</t>
+          <t>https://www.indeed.com/viewjob?jk=ca19ad92abde46c9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Warehouse Analyst Seniors: Cloud Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, ETL, CI/CD</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d87aa04a7733264b</t>
+          <t>https://www.indeed.com/viewjob?jk=cb699a2e3bdbb440</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Full Stack AI Engineer</t>
+          <t>Data Warehouse Analyst Seniors: Cloud Engineering</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=574e10b9b787dc54</t>
+          <t>https://www.indeed.com/viewjob?jk=d87aa04a7733264b</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac615cac5200efc9</t>
+          <t>https://www.indeed.com/viewjob?jk=574e10b9b787dc54</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a7de03320b3d487</t>
+          <t>https://www.indeed.com/viewjob?jk=ac615cac5200efc9</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df1418000450ecdb</t>
+          <t>https://www.indeed.com/viewjob?jk=8a7de03320b3d487</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,59 +881,59 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6df75aab0012c038</t>
+          <t>https://www.indeed.com/viewjob?jk=df1418000450ecdb</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Ad Ops Engineer</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14f238cb8b8c5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=6df75aab0012c038</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Operations Engineer (Cloud)</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Stifel</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d061193f264addea</t>
+          <t>https://www.indeed.com/viewjob?jk=f99034f0e149e6e6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>Ignite Insurance Systems</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
+          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f99034f0e149e6e6</t>
+          <t>https://www.indeed.com/viewjob?jk=560d14506d8aa36b</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ignite Insurance Systems</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=560d14506d8aa36b</t>
+          <t>https://www.indeed.com/viewjob?jk=e99b4467c3c6aa55</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Ad Ops Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99b4467c3c6aa55</t>
+          <t>https://www.indeed.com/viewjob?jk=f14f238cb8b8c5f1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Architect I</t>
+          <t>Operations Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Stifel</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Azure, Data Factory, Databricks</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6d97da40a8da560</t>
+          <t>https://www.indeed.com/viewjob?jk=d061193f264addea</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Solution Architect, Enterprise - Eastern Time Zone</t>
+          <t>Senior Data &amp; AI Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Olson Kundig</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f33106731db1775</t>
+          <t>https://www.indeed.com/viewjob?jk=d831e0d8e2c5553f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Solution Architect, Enterprise - Eastern Time Zone</t>
+          <t>Software Engineer III- DevOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90d356ab99a57489</t>
+          <t>https://www.indeed.com/viewjob?jk=985846920fb69c12</t>
         </is>
       </c>
     </row>
@@ -1441,14 +1441,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15664632526fabdb</t>
+          <t>https://www.indeed.com/viewjob?jk=3f33106731db1775</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Solution Architect, Enterprise - Eastern Time Zone</t>
+          <t>Solution Architect, Enterprise - Eastern Time Zone</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1476,14 +1476,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=507830f63a6d47c9</t>
+          <t>https://www.indeed.com/viewjob?jk=90d356ab99a57489</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Solution Architect, Enterprise - Eastern Time Zone</t>
+          <t>Solution Architect, Enterprise - Eastern Time Zone</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98d7971656e73b43</t>
+          <t>https://www.indeed.com/viewjob?jk=15664632526fabdb</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data &amp; AI Governance Officer</t>
+          <t>Senior Solution Architect, Enterprise - Eastern Time Zone</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Vantage Bank Texas</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Data Factory, Databricks, ELT, Power BI, Tableau</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c469b183725fde1</t>
+          <t>https://www.indeed.com/viewjob?jk=507830f63a6d47c9</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Developer</t>
+          <t>Senior Solution Architect, Enterprise - Eastern Time Zone</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Olson Kundig</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,52 +1571,52 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d831e0d8e2c5553f</t>
+          <t>https://www.indeed.com/viewjob?jk=98d7971656e73b43</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Data &amp; AI Governance Officer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vantage Bank Texas</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Glue, S3, RDS, Azure, Data Factory, Databricks, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2a1afc987319b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=5c469b183725fde1</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (Cloud Enablement)</t>
+          <t>AI Intern</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Flexera</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, dbt, MLflow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72d1842ef3999b1d</t>
+          <t>https://www.indeed.com/viewjob?jk=7bea47ac5f13bd1f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Intern</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, dbt, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bea47ac5f13bd1f</t>
+          <t>https://www.indeed.com/viewjob?jk=93144249a4967543</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Research Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Bryan, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93144249a4967543</t>
+          <t>https://www.indeed.com/viewjob?jk=09b3207da19db4ee</t>
         </is>
       </c>
     </row>
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b3207da19db4ee</t>
+          <t>https://www.indeed.com/viewjob?jk=bb85a1b8d1928fd4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Research Engineer II</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bryan, TX, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb85a1b8d1928fd4</t>
+          <t>https://www.indeed.com/viewjob?jk=b2a1afc987319b9a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Site Reliability Engineer (Cloud Enablement)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Flexera</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5acecf0e4305790</t>
+          <t>https://www.indeed.com/viewjob?jk=72d1842ef3999b1d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f177704478aadbe</t>
+          <t>https://www.indeed.com/viewjob?jk=a5acecf0e4305790</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ArcGIS Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,59 +1931,59 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1186a0273eb12d27</t>
+          <t>https://www.indeed.com/viewjob?jk=9f177704478aadbe</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ArcGIS Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ventura Foods</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, API Gateway, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e93266a037e0c18</t>
+          <t>https://www.indeed.com/viewjob?jk=1186a0273eb12d27</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Sr. ETL/Python Developer)</t>
+          <t>AI/ML Engineering Intern (Summer 2026)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RCR Technology</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>Redshift, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4527effc81797bda</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd3431b51acd4b5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cloudera Public Cloud Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Ventura Foods</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Plano, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce7428fbc9c89fa9</t>
+          <t>https://www.indeed.com/viewjob?jk=6e93266a037e0c18</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI/ML Engineering Intern (Summer 2026)</t>
+          <t>Senior Data Engineer (Sr. ETL/Python Developer)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>RCR Technology</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd3431b51acd4b5</t>
+          <t>https://www.indeed.com/viewjob?jk=4527effc81797bda</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DevOps &amp; AI Automation Engineer</t>
+          <t>Cloudera Public Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6b296a0ce2f382</t>
+          <t>https://www.indeed.com/viewjob?jk=ce7428fbc9c89fa9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Development Engineer II (C#/.NET, Azure)</t>
+          <t>DevOps &amp; AI Automation Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,52 +2131,52 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6c902472d880e18</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6b296a0ce2f382</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Development Engineer II (C#/.NET, Azure)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1834ddbeb8ec8bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=b6c902472d880e18</t>
         </is>
       </c>
     </row>
@@ -2253,17 +2253,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Databricks, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a527d30b5c00d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=1834ddbeb8ec8bb3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cloud Automation Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Vantage Bank Texas</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f9ce6ba5f081b9</t>
+          <t>https://www.indeed.com/viewjob?jk=1a527d30b5c00d7d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Cloud Automation Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>Vantage Bank Texas</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62c75d5f8fbde70d</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f9ce6ba5f081b9</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Medeloop</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a81ed0b08e8f07f7</t>
+          <t>https://www.indeed.com/viewjob?jk=62c75d5f8fbde70d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Sunbit, Inc</t>
+          <t>Medeloop</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1444a89356fbe315</t>
+          <t>https://www.indeed.com/viewjob?jk=a81ed0b08e8f07f7</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Web Application Architect 3</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Bloomberg Industry Group</t>
+          <t>Sunbit, Inc</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7846d03774f71aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=1444a89356fbe315</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Backend Engineer II</t>
+          <t>Web Application Architect 3</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>Bloomberg Industry Group</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae2342b890625b11</t>
+          <t>https://www.indeed.com/viewjob?jk=7846d03774f71aa5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Full Stack Developer (JS/TS, AWS)</t>
+          <t>Machine Learning Engineer (171680)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Low Associates</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>South Bend, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, GCP, Cloud Storage, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45727b1c951a0e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=a860d07867e70be2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr Business Intelligence Developer - Onsite</t>
+          <t>Backend Engineer II</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba1611f04cfe11a7</t>
+          <t>https://www.indeed.com/viewjob?jk=ae2342b890625b11</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (171680)</t>
+          <t>Full Stack Developer (JS/TS, AWS)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Low Associates</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>South Bend, IN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, API Gateway, IAM, Azure, GCP, Cloud Storage, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a860d07867e70be2</t>
+          <t>https://www.indeed.com/viewjob?jk=45727b1c951a0e5a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Sr Business Intelligence Developer - Onsite</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ff91e3d3905a73</t>
+          <t>https://www.indeed.com/viewjob?jk=ba1611f04cfe11a7</t>
         </is>
       </c>
     </row>
@@ -2666,59 +2666,59 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cbee15ac5e5d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=30ff91e3d3905a73</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AI Cloud Security and Infrastructure Engineer</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Troutman Pepper Locke</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04325b074eb62665</t>
+          <t>https://www.indeed.com/viewjob?jk=17cbee15ac5e5d6a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c20056a5b9ffca80</t>
+          <t>https://www.indeed.com/viewjob?jk=766ed066e436eb0c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Analytics Developer</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>cloudteam</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, Oozie, YARN</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ae648cd8fe57362</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c080bdfd0f5497</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Holland &amp; Knight</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brandon, FL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abb3ed211255b11</t>
+          <t>https://www.indeed.com/viewjob?jk=01aefad23a0eebfc</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766f2f5e9a7201f1</t>
+          <t>https://www.indeed.com/viewjob?jk=b79af965edb52688</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - III</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16ddbf61e3ea0b92</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe099d836f48656</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - II</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43bfe7ca1f6eddb7</t>
+          <t>https://www.indeed.com/viewjob?jk=8756dcda438f6959</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - I</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2124d09922154cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=3c70b98cc7f980bc</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>GIS Support Engineer</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e24b40c19089ff90</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa8671f82044c5a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer - Dallas, TX</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,17 +3006,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865a46cfbc7cc3f4</t>
+          <t>https://www.indeed.com/viewjob?jk=9bddaca0e62ee366</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766ed066e436eb0c</t>
+          <t>https://www.indeed.com/viewjob?jk=4177c81ac5d66b2d</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c080bdfd0f5497</t>
+          <t>https://www.indeed.com/viewjob?jk=02c32fad4b2ac01d</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01aefad23a0eebfc</t>
+          <t>https://www.indeed.com/viewjob?jk=964bc462945e695c</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b79af965edb52688</t>
+          <t>https://www.indeed.com/viewjob?jk=7beb81f1fe47bc19</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe099d836f48656</t>
+          <t>https://www.indeed.com/viewjob?jk=a3c6d71a96ee8e3e</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8756dcda438f6959</t>
+          <t>https://www.indeed.com/viewjob?jk=85e48e8aee6232ce</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c70b98cc7f980bc</t>
+          <t>https://www.indeed.com/viewjob?jk=26cc56905b519e4a</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa8671f82044c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=416163a4caa0a101</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bddaca0e62ee366</t>
+          <t>https://www.indeed.com/viewjob?jk=6b314b34d858c384</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4177c81ac5d66b2d</t>
+          <t>https://www.indeed.com/viewjob?jk=3d26c232b74cd8f7</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02c32fad4b2ac01d</t>
+          <t>https://www.indeed.com/viewjob?jk=0461589d526a9a5c</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=964bc462945e695c</t>
+          <t>https://www.indeed.com/viewjob?jk=a01db0a34a1698ca</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7beb81f1fe47bc19</t>
+          <t>https://www.indeed.com/viewjob?jk=1d2979409c83f2a4</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3c6d71a96ee8e3e</t>
+          <t>https://www.indeed.com/viewjob?jk=19292a33d87f477b</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e48e8aee6232ce</t>
+          <t>https://www.indeed.com/viewjob?jk=1c45b67d1782f41c</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26cc56905b519e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=28e0fdb2d1d8365c</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=416163a4caa0a101</t>
+          <t>https://www.indeed.com/viewjob?jk=50082798bb6a8951</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b314b34d858c384</t>
+          <t>https://www.indeed.com/viewjob?jk=ff4b550996831857</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d26c232b74cd8f7</t>
+          <t>https://www.indeed.com/viewjob?jk=e7a140e56c36bd8e</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0461589d526a9a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=7177f3e2822442b8</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a01db0a34a1698ca</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f786bfc01c412f</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d2979409c83f2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=c31b397857f539a8</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19292a33d87f477b</t>
+          <t>https://www.indeed.com/viewjob?jk=df2a59301082a549</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c45b67d1782f41c</t>
+          <t>https://www.indeed.com/viewjob?jk=abd442131644c2ae</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e0fdb2d1d8365c</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac49610be5f7c22</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50082798bb6a8951</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd327a6115535e1</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff4b550996831857</t>
+          <t>https://www.indeed.com/viewjob?jk=6fdf53b11b630cb7</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7a140e56c36bd8e</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7ce02753b98a7f</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7177f3e2822442b8</t>
+          <t>https://www.indeed.com/viewjob?jk=48e68a3d2a669f96</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f786bfc01c412f</t>
+          <t>https://www.indeed.com/viewjob?jk=715a8a81ec1663c0</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c31b397857f539a8</t>
+          <t>https://www.indeed.com/viewjob?jk=8c61b7a4534477b1</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2a59301082a549</t>
+          <t>https://www.indeed.com/viewjob?jk=714987b40a626f2c</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd442131644c2ae</t>
+          <t>https://www.indeed.com/viewjob?jk=bc2483f2dc10aa24</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac49610be5f7c22</t>
+          <t>https://www.indeed.com/viewjob?jk=41f3867fb9d5fca1</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd327a6115535e1</t>
+          <t>https://www.indeed.com/viewjob?jk=e14441426c0e5912</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fdf53b11b630cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=de87959267d1c1a1</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7ce02753b98a7f</t>
+          <t>https://www.indeed.com/viewjob?jk=157307b309906617</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48e68a3d2a669f96</t>
+          <t>https://www.indeed.com/viewjob?jk=fd2a0badba0820e7</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=715a8a81ec1663c0</t>
+          <t>https://www.indeed.com/viewjob?jk=3a1077e0bf1888ba</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c61b7a4534477b1</t>
+          <t>https://www.indeed.com/viewjob?jk=8c0316b1d2e51b16</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=714987b40a626f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=91b58529dba10c91</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc2483f2dc10aa24</t>
+          <t>https://www.indeed.com/viewjob?jk=bbe26208741cfd88</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f3867fb9d5fca1</t>
+          <t>https://www.indeed.com/viewjob?jk=a4deeb487a12f72a</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e14441426c0e5912</t>
+          <t>https://www.indeed.com/viewjob?jk=3088b1f92a7a6242</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>AI Cloud Security and Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Troutman Pepper Locke</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de87959267d1c1a1</t>
+          <t>https://www.indeed.com/viewjob?jk=04325b074eb62665</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157307b309906617</t>
+          <t>https://www.indeed.com/viewjob?jk=c20056a5b9ffca80</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Analytics Developer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>cloudteam</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, Oozie, YARN</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd2a0badba0820e7</t>
+          <t>https://www.indeed.com/viewjob?jk=6ae648cd8fe57362</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Holland &amp; Knight</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Brandon, FL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, Airflow, Git</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a1077e0bf1888ba</t>
+          <t>https://www.indeed.com/viewjob?jk=3abb3ed211255b11</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c0316b1d2e51b16</t>
+          <t>https://www.indeed.com/viewjob?jk=766f2f5e9a7201f1</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Cloud Software Engineer 3 - III</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91b58529dba10c91</t>
+          <t>https://www.indeed.com/viewjob?jk=16ddbf61e3ea0b92</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Cloud Software Engineer 3 - II</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbe26208741cfd88</t>
+          <t>https://www.indeed.com/viewjob?jk=43bfe7ca1f6eddb7</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Cloud Software Engineer 3 - I</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4deeb487a12f72a</t>
+          <t>https://www.indeed.com/viewjob?jk=2124d09922154cc4</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Engineer II, AWS Connect</t>
+          <t>GIS Support Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d1c8d1b8c5a8bd</t>
+          <t>https://www.indeed.com/viewjob?jk=e24b40c19089ff90</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Data Engineer - Dallas, TX</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Customers Bank</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Polars, Snowflake, Oracle, SQL Server, Dimensional Modeling, Power BI</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da13b88eee9db315</t>
+          <t>https://www.indeed.com/viewjob?jk=865a46cfbc7cc3f4</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Engineer II, AWS Connect</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>BillGO, Inc.</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, DynamoDB, Star Schema, ELT, Tableau, GitHub Actions</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69713d6be44a4b67</t>
+          <t>https://www.indeed.com/viewjob?jk=16d1c8d1b8c5a8bd</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>SRE Architect</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b635a4480602f9</t>
+          <t>https://www.indeed.com/viewjob?jk=907826ed55a037a8</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Rocket Close</t>
+          <t>Customers Bank</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,77 +5001,77 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, Scala, Polars, Snowflake, Oracle, SQL Server, Dimensional Modeling, Power BI</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fce91f5c39bd4ed</t>
+          <t>https://www.indeed.com/viewjob?jk=da13b88eee9db315</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>BillGO, Inc.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, DynamoDB, Star Schema, ELT, Tableau, GitHub Actions</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a31dfca06d884ad</t>
+          <t>https://www.indeed.com/viewjob?jk=69713d6be44a4b67</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,59 +5081,59 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b1cb632eed3bcb</t>
+          <t>https://www.indeed.com/viewjob?jk=10b635a4480602f9</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Rocket Close</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec090a150db0c5f8</t>
+          <t>https://www.indeed.com/viewjob?jk=9fce91f5c39bd4ed</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Sr. Software Engineer II</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fe79bacd5e58f55</t>
+          <t>https://www.indeed.com/viewjob?jk=04a1d1c06680e371</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Cloud Data Engineer (Onsite)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Colony Brands</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Monroe, WI, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,17 +5176,17 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f09282ebd98b3570</t>
+          <t>https://www.indeed.com/viewjob?jk=f935defc4a70c87e</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1d73f24fc01af9</t>
+          <t>https://www.indeed.com/viewjob?jk=1a31dfca06d884ad</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e4150c94fe908c8</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b1cb632eed3bcb</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Metropolitan Companies</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Wyomissing, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12c03c3bb6ce8c38</t>
+          <t>https://www.indeed.com/viewjob?jk=ec090a150db0c5f8</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer (Onsite)</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Colony Brands</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Monroe, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,34 +5316,34 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f935defc4a70c87e</t>
+          <t>https://www.indeed.com/viewjob?jk=3fe79bacd5e58f55</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04a1d1c06680e371</t>
+          <t>https://www.indeed.com/viewjob?jk=f09282ebd98b3570</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst/Associate - New York</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dd43ffc6d7fda89</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1d73f24fc01af9</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Supervisor, Software Engineering</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Energy Systems Group</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Newburgh, IN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,34 +5421,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c197f77bdf171e6</t>
+          <t>https://www.indeed.com/viewjob?jk=7e4150c94fe908c8</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Metropolitan Companies</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Wyomissing, PA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4296ca379ce33eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=12c03c3bb6ce8c38</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst/Associate - New York</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f710f05a18efb3e1</t>
+          <t>https://www.indeed.com/viewjob?jk=1dd43ffc6d7fda89</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Supervisor, Software Engineering</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Energy Systems Group</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Newburgh, IN, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ad148596751872e</t>
+          <t>https://www.indeed.com/viewjob?jk=9c197f77bdf171e6</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,34 +5561,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085872f73883326c</t>
+          <t>https://www.indeed.com/viewjob?jk=4296ca379ce33eb3</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa79af047e73dc3e</t>
+          <t>https://www.indeed.com/viewjob?jk=f710f05a18efb3e1</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>IS Technical Specialist</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,17 +5631,17 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34987f860a590c53</t>
+          <t>https://www.indeed.com/viewjob?jk=757269b719268379</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=757269b719268379</t>
+          <t>https://www.indeed.com/viewjob?jk=609b33430f9df835</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609b33430f9df835</t>
+          <t>https://www.indeed.com/viewjob?jk=ef377da6b1a8bbfd</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef377da6b1a8bbfd</t>
+          <t>https://www.indeed.com/viewjob?jk=6aea6ee79779b03b</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Fairlawn, OH, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aea6ee79779b03b</t>
+          <t>https://www.indeed.com/viewjob?jk=da070db6e9060b88</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Fairlawn, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da070db6e9060b88</t>
+          <t>https://www.indeed.com/viewjob?jk=63d188ef103369c5</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>IS Technical Specialist</t>
+          <t>Software Engineer I - Full Stack</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,34 +5841,34 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, YARN, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63d188ef103369c5</t>
+          <t>https://www.indeed.com/viewjob?jk=e317b1b40c2e7beb</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Software Engineer I - Full Stack</t>
+          <t>Cloud Solution Architect</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Applied Information Sciences</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,34 +5876,34 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, YARN, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e317b1b40c2e7beb</t>
+          <t>https://www.indeed.com/viewjob?jk=f47703eb8d2843d8</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Cloud Solution Architect</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Applied Information Sciences</t>
+          <t>CleanSlate Technology Group</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, Scala, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation, Jenkins, Git</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f47703eb8d2843d8</t>
+          <t>https://www.indeed.com/viewjob?jk=478788964e131867</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-15.xlsx
+++ b/results/job_matches_2026-04-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G157"/>
+  <dimension ref="A1:G160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS Glue</t>
+          <t>Data Architect, Senior</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Intermountain Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Murray, UT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f1496d3a0b45451</t>
+          <t>https://www.indeed.com/viewjob?jk=8184ec5fc529fc27</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer/Data Scientist</t>
+          <t>Software Engineer III - AWS Glue</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a711c2fcb36b6cf</t>
+          <t>https://www.indeed.com/viewjob?jk=5f1496d3a0b45451</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (ON-SITE)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Equinox</t>
+          <t>HelioCampus</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, Snowflake, DynamoDB</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=038b96d69cecd888</t>
+          <t>https://www.indeed.com/viewjob?jk=333fbc294a529a0f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Databricks Data Analyst</t>
+          <t>Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce89a36f70a3941b</t>
+          <t>https://www.indeed.com/viewjob?jk=8a711c2fcb36b6cf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Information Technology - BI Developer</t>
+          <t>Sr. Data Engineer (ON-SITE)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TCC Verizon Authorized Retailer</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fishers, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,77 +661,77 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca19ad92abde46c9</t>
+          <t>https://www.indeed.com/viewjob?jk=038b96d69cecd888</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Data Analyst</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb699a2e3bdbb440</t>
+          <t>https://www.indeed.com/viewjob?jk=ce89a36f70a3941b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Warehouse Analyst Seniors: Cloud Engineering</t>
+          <t>Information Technology - BI Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>TCC Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Fishers, IN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, ETL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d87aa04a7733264b</t>
+          <t>https://www.indeed.com/viewjob?jk=ca19ad92abde46c9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Full Stack AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=574e10b9b787dc54</t>
+          <t>https://www.indeed.com/viewjob?jk=cb699a2e3bdbb440</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Full Stack AI Engineer</t>
+          <t>Data Warehouse Analyst Seniors: Cloud Engineering</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac615cac5200efc9</t>
+          <t>https://www.indeed.com/viewjob?jk=d87aa04a7733264b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Full Stack AI Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Live Nation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,17 +836,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, API Gateway, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a7de03320b3d487</t>
+          <t>https://www.indeed.com/viewjob?jk=31ca2baaf21560e8</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df1418000450ecdb</t>
+          <t>https://www.indeed.com/viewjob?jk=574e10b9b787dc54</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,129 +916,129 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6df75aab0012c038</t>
+          <t>https://www.indeed.com/viewjob?jk=ac615cac5200efc9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f99034f0e149e6e6</t>
+          <t>https://www.indeed.com/viewjob?jk=8a7de03320b3d487</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ignite Insurance Systems</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=560d14506d8aa36b</t>
+          <t>https://www.indeed.com/viewjob?jk=df1418000450ecdb</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99b4467c3c6aa55</t>
+          <t>https://www.indeed.com/viewjob?jk=6df75aab0012c038</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Ad Ops Engineer</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14f238cb8b8c5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=f99034f0e149e6e6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Operations Engineer (Cloud)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Stifel</t>
+          <t>Ignite Insurance Systems</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d061193f264addea</t>
+          <t>https://www.indeed.com/viewjob?jk=560d14506d8aa36b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Azure, GCP, Scala, Kafka</t>
+          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,19 +1126,19 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcd17ae9e035b9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=e99b4467c3c6aa55</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer- OrderlyMeds</t>
+          <t>Senior Ad Ops Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>OrderlyMeds</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1147,11 +1147,11 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,124 +1161,124 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb2a73a0846955d</t>
+          <t>https://www.indeed.com/viewjob?jk=f14f238cb8b8c5f1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Azure/Databricks/Python)</t>
+          <t>Operations Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>loanDepot</t>
+          <t>Stifel</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4b1df13928e079d</t>
+          <t>https://www.indeed.com/viewjob?jk=d061193f264addea</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema, dbt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4d88005315e7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=7c4955f2e41966ef</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Database and Dashboard Developer</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Oracle</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Azure, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fee5a2d73882379c</t>
+          <t>https://www.indeed.com/viewjob?jk=fcd17ae9e035b9a9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer (contract)</t>
+          <t>Data Engineer- OrderlyMeds</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>OrderlyMeds</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23956751504b8384</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb2a73a0846955d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Java Software Developer</t>
+          <t>Sr. Data Engineer (Azure/Databricks/Python)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>loanDepot</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c2cee659fe1d0db</t>
+          <t>https://www.indeed.com/viewjob?jk=d4b1df13928e079d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Olson Kundig</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d831e0d8e2c5553f</t>
+          <t>https://www.indeed.com/viewjob?jk=aa4d88005315e7ba</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer III- DevOps Engineer</t>
+          <t>Database and Dashboard Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,29 +1396,29 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=985846920fb69c12</t>
+          <t>https://www.indeed.com/viewjob?jk=fee5a2d73882379c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Solution Architect, Enterprise - Eastern Time Zone</t>
+          <t>Snowflake Data Engineer (contract)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f33106731db1775</t>
+          <t>https://www.indeed.com/viewjob?jk=23956751504b8384</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90d356ab99a57489</t>
+          <t>https://www.indeed.com/viewjob?jk=3f33106731db1775</t>
         </is>
       </c>
     </row>
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15664632526fabdb</t>
+          <t>https://www.indeed.com/viewjob?jk=90d356ab99a57489</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Solution Architect, Enterprise - Eastern Time Zone</t>
+          <t>Solution Architect, Enterprise - Eastern Time Zone</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=507830f63a6d47c9</t>
+          <t>https://www.indeed.com/viewjob?jk=15664632526fabdb</t>
         </is>
       </c>
     </row>
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98d7971656e73b43</t>
+          <t>https://www.indeed.com/viewjob?jk=507830f63a6d47c9</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data &amp; AI Governance Officer</t>
+          <t>Senior Solution Architect, Enterprise - Eastern Time Zone</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Vantage Bank Texas</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,69 +1606,69 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Data Factory, Databricks, ELT, Power BI, Tableau</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c469b183725fde1</t>
+          <t>https://www.indeed.com/viewjob?jk=98d7971656e73b43</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior, Software Engineer</t>
+          <t>Senior Data &amp; AI Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Olson Kundig</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Cassandra</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fcd1c4e67959eea</t>
+          <t>https://www.indeed.com/viewjob?jk=d831e0d8e2c5553f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI Intern</t>
+          <t>Senior, Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, dbt, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Cassandra</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bea47ac5f13bd1f</t>
+          <t>https://www.indeed.com/viewjob?jk=3fcd1c4e67959eea</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Intern</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, dbt, MLflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93144249a4967543</t>
+          <t>https://www.indeed.com/viewjob?jk=7bea47ac5f13bd1f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Research Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bryan, TX, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b3207da19db4ee</t>
+          <t>https://www.indeed.com/viewjob?jk=93144249a4967543</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb85a1b8d1928fd4</t>
+          <t>https://www.indeed.com/viewjob?jk=09b3207da19db4ee</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2a1afc987319b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=6918de34da34b82a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (Cloud Enablement)</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Flexera</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72d1842ef3999b1d</t>
+          <t>https://www.indeed.com/viewjob?jk=b2a1afc987319b9a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Site Reliability Engineer (Cloud Enablement)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Flexera</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5acecf0e4305790</t>
+          <t>https://www.indeed.com/viewjob?jk=72d1842ef3999b1d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f177704478aadbe</t>
+          <t>https://www.indeed.com/viewjob?jk=a5acecf0e4305790</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ArcGIS Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,59 +1966,59 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1186a0273eb12d27</t>
+          <t>https://www.indeed.com/viewjob?jk=9f177704478aadbe</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI/ML Engineering Intern (Summer 2026)</t>
+          <t>ArcGIS Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd3431b51acd4b5</t>
+          <t>https://www.indeed.com/viewjob?jk=1186a0273eb12d27</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI/ML Engineering Intern (Summer 2026)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ventura Foods</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>Redshift, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e93266a037e0c18</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd3431b51acd4b5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Sr. ETL/Python Developer)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RCR Technology</t>
+          <t>Ventura Foods</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4527effc81797bda</t>
+          <t>https://www.indeed.com/viewjob?jk=6e93266a037e0c18</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cloudera Public Cloud Platform Engineer</t>
+          <t>Senior Data Engineer (Sr. ETL/Python Developer)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>RCR Technology</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Plano, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce7428fbc9c89fa9</t>
+          <t>https://www.indeed.com/viewjob?jk=4527effc81797bda</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DevOps &amp; AI Automation Engineer</t>
+          <t>Cloudera Public Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6b296a0ce2f382</t>
+          <t>https://www.indeed.com/viewjob?jk=ce7428fbc9c89fa9</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Development Engineer II (C#/.NET, Azure)</t>
+          <t>Software Engineer - Backend Java</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,42 +2166,42 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Lambda, RDS, Scala, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6c902472d880e18</t>
+          <t>https://www.indeed.com/viewjob?jk=a18ff10136ae42f8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - IICS</t>
+          <t>DevOps &amp; AI Automation Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf36b7e279da791</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6b296a0ce2f382</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - IICS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Banner Health</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Redshift, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8d9928392bc7529</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf36b7e279da791</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>Banner Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,24 +2271,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1834ddbeb8ec8bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=c8d9928392bc7529</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior Software Engineer Data Platform</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a527d30b5c00d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=e64308de1c862cb5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud Automation Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Vantage Bank Texas</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, RDS, Databricks, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f9ce6ba5f081b9</t>
+          <t>https://www.indeed.com/viewjob?jk=1834ddbeb8ec8bb3</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62c75d5f8fbde70d</t>
+          <t>https://www.indeed.com/viewjob?jk=1a527d30b5c00d7d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Medeloop</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a81ed0b08e8f07f7</t>
+          <t>https://www.indeed.com/viewjob?jk=43063b055188ce3c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Sunbit, Inc</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1444a89356fbe315</t>
+          <t>https://www.indeed.com/viewjob?jk=6cc0ba82c4bd25dc</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Web Application Architect 3</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Bloomberg Industry Group</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7846d03774f71aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=9eeb6502ebf78cc0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (171680)</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Clarita, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a860d07867e70be2</t>
+          <t>https://www.indeed.com/viewjob?jk=473b7754552ef179</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Backend Engineer II</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Lancaster, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae2342b890625b11</t>
+          <t>https://www.indeed.com/viewjob?jk=5e872365f29ac108</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Full Stack Developer (JS/TS, AWS)</t>
+          <t>Backend Engineer II</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Low Associates</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>South Bend, IN, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, GCP, Cloud Storage, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45727b1c951a0e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=ae2342b890625b11</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr Business Intelligence Developer - Onsite</t>
+          <t>Full Stack Developer (JS/TS, AWS)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>Low Associates</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>South Bend, IN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, API Gateway, IAM, Azure, GCP, Cloud Storage, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba1611f04cfe11a7</t>
+          <t>https://www.indeed.com/viewjob?jk=45727b1c951a0e5a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>Sunbit, Inc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ff91e3d3905a73</t>
+          <t>https://www.indeed.com/viewjob?jk=1444a89356fbe315</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Sr Business Intelligence Developer - Onsite</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cbee15ac5e5d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=ba1611f04cfe11a7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Machine Learning Engineer (171680)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766ed066e436eb0c</t>
+          <t>https://www.indeed.com/viewjob?jk=a860d07867e70be2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c080bdfd0f5497</t>
+          <t>https://www.indeed.com/viewjob?jk=30ff91e3d3905a73</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AI Data Engineer Senior Consultant</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01aefad23a0eebfc</t>
+          <t>https://www.indeed.com/viewjob?jk=17cbee15ac5e5d6a</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b79af965edb52688</t>
+          <t>https://www.indeed.com/viewjob?jk=766ed066e436eb0c</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe099d836f48656</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c080bdfd0f5497</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8756dcda438f6959</t>
+          <t>https://www.indeed.com/viewjob?jk=01aefad23a0eebfc</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c70b98cc7f980bc</t>
+          <t>https://www.indeed.com/viewjob?jk=b79af965edb52688</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa8671f82044c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe099d836f48656</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bddaca0e62ee366</t>
+          <t>https://www.indeed.com/viewjob?jk=8756dcda438f6959</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4177c81ac5d66b2d</t>
+          <t>https://www.indeed.com/viewjob?jk=3c70b98cc7f980bc</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02c32fad4b2ac01d</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa8671f82044c5a</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=964bc462945e695c</t>
+          <t>https://www.indeed.com/viewjob?jk=9bddaca0e62ee366</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7beb81f1fe47bc19</t>
+          <t>https://www.indeed.com/viewjob?jk=4177c81ac5d66b2d</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3c6d71a96ee8e3e</t>
+          <t>https://www.indeed.com/viewjob?jk=02c32fad4b2ac01d</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e48e8aee6232ce</t>
+          <t>https://www.indeed.com/viewjob?jk=964bc462945e695c</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26cc56905b519e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=7beb81f1fe47bc19</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=416163a4caa0a101</t>
+          <t>https://www.indeed.com/viewjob?jk=a3c6d71a96ee8e3e</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b314b34d858c384</t>
+          <t>https://www.indeed.com/viewjob?jk=85e48e8aee6232ce</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d26c232b74cd8f7</t>
+          <t>https://www.indeed.com/viewjob?jk=26cc56905b519e4a</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0461589d526a9a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=416163a4caa0a101</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a01db0a34a1698ca</t>
+          <t>https://www.indeed.com/viewjob?jk=6b314b34d858c384</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d2979409c83f2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=3d26c232b74cd8f7</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19292a33d87f477b</t>
+          <t>https://www.indeed.com/viewjob?jk=0461589d526a9a5c</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c45b67d1782f41c</t>
+          <t>https://www.indeed.com/viewjob?jk=a01db0a34a1698ca</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e0fdb2d1d8365c</t>
+          <t>https://www.indeed.com/viewjob?jk=1d2979409c83f2a4</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50082798bb6a8951</t>
+          <t>https://www.indeed.com/viewjob?jk=19292a33d87f477b</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff4b550996831857</t>
+          <t>https://www.indeed.com/viewjob?jk=1c45b67d1782f41c</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7a140e56c36bd8e</t>
+          <t>https://www.indeed.com/viewjob?jk=28e0fdb2d1d8365c</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7177f3e2822442b8</t>
+          <t>https://www.indeed.com/viewjob?jk=50082798bb6a8951</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f786bfc01c412f</t>
+          <t>https://www.indeed.com/viewjob?jk=ff4b550996831857</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c31b397857f539a8</t>
+          <t>https://www.indeed.com/viewjob?jk=e7a140e56c36bd8e</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2a59301082a549</t>
+          <t>https://www.indeed.com/viewjob?jk=7177f3e2822442b8</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd442131644c2ae</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f786bfc01c412f</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac49610be5f7c22</t>
+          <t>https://www.indeed.com/viewjob?jk=c31b397857f539a8</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd327a6115535e1</t>
+          <t>https://www.indeed.com/viewjob?jk=df2a59301082a549</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fdf53b11b630cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=abd442131644c2ae</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7ce02753b98a7f</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac49610be5f7c22</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48e68a3d2a669f96</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd327a6115535e1</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=715a8a81ec1663c0</t>
+          <t>https://www.indeed.com/viewjob?jk=6fdf53b11b630cb7</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c61b7a4534477b1</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7ce02753b98a7f</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=714987b40a626f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=48e68a3d2a669f96</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc2483f2dc10aa24</t>
+          <t>https://www.indeed.com/viewjob?jk=715a8a81ec1663c0</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f3867fb9d5fca1</t>
+          <t>https://www.indeed.com/viewjob?jk=8c61b7a4534477b1</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e14441426c0e5912</t>
+          <t>https://www.indeed.com/viewjob?jk=714987b40a626f2c</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de87959267d1c1a1</t>
+          <t>https://www.indeed.com/viewjob?jk=bc2483f2dc10aa24</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157307b309906617</t>
+          <t>https://www.indeed.com/viewjob?jk=41f3867fb9d5fca1</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd2a0badba0820e7</t>
+          <t>https://www.indeed.com/viewjob?jk=e14441426c0e5912</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a1077e0bf1888ba</t>
+          <t>https://www.indeed.com/viewjob?jk=de87959267d1c1a1</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c0316b1d2e51b16</t>
+          <t>https://www.indeed.com/viewjob?jk=157307b309906617</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91b58529dba10c91</t>
+          <t>https://www.indeed.com/viewjob?jk=fd2a0badba0820e7</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbe26208741cfd88</t>
+          <t>https://www.indeed.com/viewjob?jk=3a1077e0bf1888ba</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4deeb487a12f72a</t>
+          <t>https://www.indeed.com/viewjob?jk=8c0316b1d2e51b16</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3088b1f92a7a6242</t>
+          <t>https://www.indeed.com/viewjob?jk=91b58529dba10c91</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>AI Cloud Security and Infrastructure Engineer</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Troutman Pepper Locke</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04325b074eb62665</t>
+          <t>https://www.indeed.com/viewjob?jk=bbe26208741cfd88</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
+          <t>AI Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c20056a5b9ffca80</t>
+          <t>https://www.indeed.com/viewjob?jk=a4deeb487a12f72a</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Analytics Developer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>cloudteam</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, Oozie, YARN</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ae648cd8fe57362</t>
+          <t>https://www.indeed.com/viewjob?jk=3088b1f92a7a6242</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>AI Cloud Security and Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Holland &amp; Knight</t>
+          <t>Troutman Pepper Locke</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Brandon, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abb3ed211255b11</t>
+          <t>https://www.indeed.com/viewjob?jk=04325b074eb62665</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766f2f5e9a7201f1</t>
+          <t>https://www.indeed.com/viewjob?jk=c20056a5b9ffca80</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - III</t>
+          <t>Analytics Developer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>cloudteam</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, Oozie, YARN</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16ddbf61e3ea0b92</t>
+          <t>https://www.indeed.com/viewjob?jk=6ae648cd8fe57362</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - II</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>Holland &amp; Knight</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Brandon, FL, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, Airflow, Git</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43bfe7ca1f6eddb7</t>
+          <t>https://www.indeed.com/viewjob?jk=3abb3ed211255b11</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - I</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2124d09922154cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=766f2f5e9a7201f1</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>GIS Support Engineer</t>
+          <t>Cloud Software Engineer 3 - III</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e24b40c19089ff90</t>
+          <t>https://www.indeed.com/viewjob?jk=16ddbf61e3ea0b92</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Data Engineer - Dallas, TX</t>
+          <t>Cloud Software Engineer 3 - II</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865a46cfbc7cc3f4</t>
+          <t>https://www.indeed.com/viewjob?jk=43bfe7ca1f6eddb7</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Engineer II, AWS Connect</t>
+          <t>Cloud Software Engineer 3 - I</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d1c8d1b8c5a8bd</t>
+          <t>https://www.indeed.com/viewjob?jk=2124d09922154cc4</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SRE Architect</t>
+          <t>GIS Support Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Splunk, CI/CD, Terraform</t>
+          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=907826ed55a037a8</t>
+          <t>https://www.indeed.com/viewjob?jk=e24b40c19089ff90</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Data Engineer - Dallas, TX</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Customers Bank</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Polars, Snowflake, Oracle, SQL Server, Dimensional Modeling, Power BI</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da13b88eee9db315</t>
+          <t>https://www.indeed.com/viewjob?jk=865a46cfbc7cc3f4</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Engineer II, AWS Connect</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>BillGO, Inc.</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, DynamoDB, Star Schema, ELT, Tableau, GitHub Actions</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69713d6be44a4b67</t>
+          <t>https://www.indeed.com/viewjob?jk=16d1c8d1b8c5a8bd</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>BillGO, Inc.</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, DynamoDB, Star Schema, ELT, Tableau, GitHub Actions</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b635a4480602f9</t>
+          <t>https://www.indeed.com/viewjob?jk=69713d6be44a4b67</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Rocket Close</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,42 +5106,42 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fce91f5c39bd4ed</t>
+          <t>https://www.indeed.com/viewjob?jk=10b635a4480602f9</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II</t>
+          <t>SRE Architect</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04a1d1c06680e371</t>
+          <t>https://www.indeed.com/viewjob?jk=907826ed55a037a8</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer (Onsite)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Colony Brands</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Monroe, WI, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f935defc4a70c87e</t>
+          <t>https://www.indeed.com/viewjob?jk=2be9ee403cf20f67</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a31dfca06d884ad</t>
+          <t>https://www.indeed.com/viewjob?jk=156e5a4def2a4a5d</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Analytic Data Engineer (Python/Power BI)</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, ETL, Power BI</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b1cb632eed3bcb</t>
+          <t>https://www.indeed.com/viewjob?jk=100c60fa90e63408</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Sr. Software Engineer II</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec090a150db0c5f8</t>
+          <t>https://www.indeed.com/viewjob?jk=04a1d1c06680e371</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Cloud Data Engineer (Onsite)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Colony Brands</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Monroe, WI, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,34 +5316,34 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fe79bacd5e58f55</t>
+          <t>https://www.indeed.com/viewjob?jk=f935defc4a70c87e</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f09282ebd98b3570</t>
+          <t>https://www.indeed.com/viewjob?jk=b2cdf5f4ac6a6c1a</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1d73f24fc01af9</t>
+          <t>https://www.indeed.com/viewjob?jk=1a31dfca06d884ad</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e4150c94fe908c8</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b1cb632eed3bcb</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Metropolitan Companies</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Wyomissing, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,19 +5466,19 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12c03c3bb6ce8c38</t>
+          <t>https://www.indeed.com/viewjob?jk=ec090a150db0c5f8</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst/Associate - New York</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dd43ffc6d7fda89</t>
+          <t>https://www.indeed.com/viewjob?jk=3fe79bacd5e58f55</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Supervisor, Software Engineering</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Energy Systems Group</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Newburgh, IN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c197f77bdf171e6</t>
+          <t>https://www.indeed.com/viewjob?jk=f09282ebd98b3570</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4296ca379ce33eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1d73f24fc01af9</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,34 +5596,34 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f710f05a18efb3e1</t>
+          <t>https://www.indeed.com/viewjob?jk=7e4150c94fe908c8</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>IS Technical Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Metropolitan Companies</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Wyomissing, PA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=757269b719268379</t>
+          <t>https://www.indeed.com/viewjob?jk=12c03c3bb6ce8c38</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>IS Technical Specialist</t>
+          <t>Senior Software Engineer, Data Migration &amp; Code Generation</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,34 +5666,34 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609b33430f9df835</t>
+          <t>https://www.indeed.com/viewjob?jk=f20bc83aea1de83b</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>IS Technical Specialist</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef377da6b1a8bbfd</t>
+          <t>https://www.indeed.com/viewjob?jk=4296ca379ce33eb3</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>IS Technical Specialist</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,34 +5736,34 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, MySQL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aea6ee79779b03b</t>
+          <t>https://www.indeed.com/viewjob?jk=f710f05a18efb3e1</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>IS Technical Specialist</t>
+          <t>Supervisor, Software Engineering</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Energy Systems Group</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Fairlawn, OH, US USA</t>
+          <t>Newburgh, IN, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da070db6e9060b88</t>
+          <t>https://www.indeed.com/viewjob?jk=9c197f77bdf171e6</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>IS Technical Specialist</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst/Associate - New York</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63d188ef103369c5</t>
+          <t>https://www.indeed.com/viewjob?jk=1dd43ffc6d7fda89</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Software Engineer I - Full Stack</t>
+          <t>IS Technical Specialist</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,34 +5841,34 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, YARN, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e317b1b40c2e7beb</t>
+          <t>https://www.indeed.com/viewjob?jk=757269b719268379</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Cloud Solution Architect</t>
+          <t>IS Technical Specialist</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Applied Information Sciences</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f47703eb8d2843d8</t>
+          <t>https://www.indeed.com/viewjob?jk=609b33430f9df835</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>IS Technical Specialist</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>CleanSlate Technology Group</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation, Jenkins, Git</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,7 +5921,112 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=478788964e131867</t>
+          <t>https://www.indeed.com/viewjob?jk=ef377da6b1a8bbfd</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>IS Technical Specialist</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Huntington Bank</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6aea6ee79779b03b</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>IS Technical Specialist</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Huntington Bank</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Fairlawn, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da070db6e9060b88</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>IS Technical Specialist</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Huntington Bank</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63d188ef103369c5</t>
         </is>
       </c>
     </row>
